--- a/data/exports/黄老师/dist_order_2026-09-14.xlsx
+++ b/data/exports/黄老师/dist_order_2026-09-14.xlsx
@@ -125,11 +125,11 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="0">
-        <v>50423288</v>
+        <v>50435690</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>梦</t>
+          <t>芈月山村</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -154,7 +154,7 @@
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:57:15</t>
+          <t>2026-09-14 09:32:33</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -164,7 +164,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -185,11 +185,11 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="0">
-        <v>50423277</v>
+        <v>50435590</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>欧阳祝明</t>
+          <t>偶尔</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -214,7 +214,7 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:56:23</t>
+          <t>2026-09-14 09:29:31</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -245,11 +245,11 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="0">
-        <v>50423276</v>
+        <v>50435588</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>幸福一生</t>
+          <t>刘住青春</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -274,7 +274,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:56:19</t>
+          <t>2026-09-14 09:29:21</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -305,11 +305,11 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="0">
-        <v>50423272</v>
+        <v>50435586</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>怡瑞《专业木工装修》装门</t>
+          <t>hua</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:56:13</t>
+          <t>2026-09-14 09:29:19</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -365,11 +365,11 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="0">
-        <v>50423262</v>
+        <v>50435585</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>黄元景，18185498848</t>
+          <t>茜茜</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -394,7 +394,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:47</t>
+          <t>2026-09-14 09:29:17</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -425,11 +425,11 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="0">
-        <v>50423257</v>
+        <v>50423288</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>向往神鹰</t>
+          <t>梦</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:33</t>
+          <t>2026-09-13 22:57:15</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -485,11 +485,11 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="0">
-        <v>50423256</v>
+        <v>50423277</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>sunny</t>
+          <t>欧阳祝明</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:29</t>
+          <t>2026-09-13 22:56:23</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -545,11 +545,11 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="0">
-        <v>50423252</v>
+        <v>50423276</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>郑维杰568</t>
+          <t>幸福一生</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:19</t>
+          <t>2026-09-13 22:56:19</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -605,11 +605,11 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="0">
-        <v>50423251</v>
+        <v>50423272</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>博海</t>
+          <t>怡瑞《专业木工装修》装门</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:19</t>
+          <t>2026-09-13 22:56:13</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -665,11 +665,11 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="0">
-        <v>50423247</v>
+        <v>50423262</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>黄元景，18185498848</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:15</t>
+          <t>2026-09-13 22:55:47</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -725,11 +725,11 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="0">
-        <v>50423246</v>
+        <v>50423257</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>巴山夜雨</t>
+          <t>向往神鹰</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:13</t>
+          <t>2026-09-13 22:55:33</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -785,11 +785,11 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="0">
-        <v>50423241</v>
+        <v>50423256</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>🍎禧果</t>
+          <t>sunny</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:09</t>
+          <t>2026-09-13 22:55:29</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -845,11 +845,11 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="0">
-        <v>50413116</v>
+        <v>50423252</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>sisikaokao</t>
+          <t>郑维杰568</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 17:55:11</t>
+          <t>2026-09-13 22:55:19</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
@@ -905,11 +905,11 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="0">
-        <v>50413104</v>
+        <v>50423251</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>阳光灿烂</t>
+          <t>博海</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 17:54:37</t>
+          <t>2026-09-13 22:55:19</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
@@ -965,11 +965,11 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="0">
-        <v>50413102</v>
+        <v>50423247</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>紫樱花🌸</t>
+          <t>雪</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 17:54:37</t>
+          <t>2026-09-13 22:55:15</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
@@ -1025,11 +1025,11 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="0">
-        <v>50405053</v>
+        <v>50423246</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>和棋，</t>
+          <t>巴山夜雨</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:42:07</t>
+          <t>2026-09-13 22:55:13</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -1085,11 +1085,11 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="0">
-        <v>50405036</v>
+        <v>50423241</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>金铲铲</t>
+          <t>🍎禧果</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:17</t>
+          <t>2026-09-13 22:55:09</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -1145,11 +1145,11 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="0">
-        <v>50405034</v>
+        <v>50413116</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>春暖花开</t>
+          <t>sisikaokao</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:11</t>
+          <t>2026-09-13 17:55:11</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="I19" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J19" s="0" t="inlineStr">
@@ -1205,11 +1205,11 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="0">
-        <v>50405028</v>
+        <v>50413104</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>杨生</t>
+          <t>阳光灿烂</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:04</t>
+          <t>2026-09-13 17:54:37</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
@@ -1265,11 +1265,11 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="0">
-        <v>50405026</v>
+        <v>50413102</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>乔</t>
+          <t>紫樱花🌸</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:04</t>
+          <t>2026-09-13 17:54:37</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
@@ -1325,11 +1325,11 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="0">
-        <v>50405025</v>
+        <v>50405053</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>韩寒</t>
+          <t>和棋，</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:03</t>
+          <t>2026-09-13 12:42:07</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1385,11 +1385,11 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="0">
-        <v>50405024</v>
+        <v>50405036</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>笑春风</t>
+          <t>金铲铲</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:03</t>
+          <t>2026-09-13 12:41:17</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
@@ -1440,21 +1440,16 @@
       <c r="L23" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N23" s="0" t="inlineStr">
-        <is>
-          <t>宁波</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="0">
-        <v>50404537</v>
+        <v>50405034</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>Lfz</t>
+          <t>春暖花开</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -1479,7 +1474,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:22:51</t>
+          <t>2026-09-13 12:41:11</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1489,7 +1484,7 @@
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
@@ -1510,11 +1505,11 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="0">
-        <v>50404504</v>
+        <v>50405028</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>年华似锦</t>
+          <t>杨生</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -1539,7 +1534,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:21:53</t>
+          <t>2026-09-13 12:41:04</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="I25" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J25" s="0" t="inlineStr">
@@ -1570,11 +1565,11 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="0">
-        <v>50404498</v>
+        <v>50405026</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>乔</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -1599,7 +1594,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:21:41</t>
+          <t>2026-09-13 12:41:04</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1609,7 +1604,7 @@
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
@@ -1630,11 +1625,11 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="0">
-        <v>50404493</v>
+        <v>50405025</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>爱</t>
+          <t>韩寒</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -1659,7 +1654,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:21:33</t>
+          <t>2026-09-13 12:41:03</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1669,7 +1664,7 @@
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
@@ -1690,11 +1685,11 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="0">
-        <v>50404484</v>
+        <v>50405024</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>Yzzc🌟</t>
+          <t>笑春风</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -1719,7 +1714,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:21:03</t>
+          <t>2026-09-13 12:41:03</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1729,7 +1724,7 @@
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -1745,16 +1740,21 @@
       <c r="L28" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N28" s="0" t="inlineStr">
+        <is>
+          <t>宁波</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="0">
-        <v>50387248</v>
+        <v>50404537</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>阿玉</t>
+          <t>Lfz</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:55:01</t>
+          <t>2026-09-13 12:22:51</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
@@ -1810,11 +1810,11 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="0">
-        <v>50386997</v>
+        <v>50404504</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>两相情缘</t>
+          <t>年华似锦</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:47:27</t>
+          <t>2026-09-13 12:21:53</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -1870,11 +1870,11 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="0">
-        <v>50386996</v>
+        <v>50404498</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>雅阁布（国强）</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:47:21</t>
+          <t>2026-09-13 12:21:41</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
@@ -1930,11 +1930,11 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="0">
-        <v>50386972</v>
+        <v>50404493</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>蓝海</t>
+          <t>爱</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:46:43</t>
+          <t>2026-09-13 12:21:33</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="I32" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J32" s="0" t="inlineStr">
@@ -1990,11 +1990,11 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="0">
-        <v>50386970</v>
+        <v>50404484</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>快乐每一天</t>
+          <t>Yzzc🌟</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:46:39</t>
+          <t>2026-09-13 12:21:03</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
@@ -2050,11 +2050,11 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="0">
-        <v>50386939</v>
+        <v>50387248</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>阿玉</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:43</t>
+          <t>2026-09-12 22:55:01</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
@@ -2110,11 +2110,11 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="0">
-        <v>50386937</v>
+        <v>50386997</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>A余文</t>
+          <t>两相情缘</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:39</t>
+          <t>2026-09-12 22:47:27</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -2170,11 +2170,11 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="0">
-        <v>50386935</v>
+        <v>50386996</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>杨捏捏</t>
+          <t>雅阁布（国强）</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:37</t>
+          <t>2026-09-12 22:47:21</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2230,11 +2230,11 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="0">
-        <v>50386934</v>
+        <v>50386972</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>聪呱呱</t>
+          <t>蓝海</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:37</t>
+          <t>2026-09-12 22:46:43</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
@@ -2290,11 +2290,11 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="0">
-        <v>50386933</v>
+        <v>50386970</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>雪花🌸</t>
+          <t>快乐每一天</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:37</t>
+          <t>2026-09-12 22:46:39</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
@@ -2350,11 +2350,11 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="0">
-        <v>50386932</v>
+        <v>50386939</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>刘月军</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:35</t>
+          <t>2026-09-12 22:45:43</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -2410,11 +2410,11 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="0">
-        <v>50386930</v>
+        <v>50386937</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>Number Life</t>
+          <t>A余文</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:35</t>
+          <t>2026-09-12 22:45:39</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
@@ -2470,11 +2470,11 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="0">
-        <v>50386929</v>
+        <v>50386935</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>刚刚好</t>
+          <t>杨捏捏</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:30</t>
+          <t>2026-09-12 22:45:37</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
@@ -2530,11 +2530,11 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="0">
-        <v>50386919</v>
+        <v>50386934</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>沙漠一滴水</t>
+          <t>聪呱呱</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:25</t>
+          <t>2026-09-12 22:45:37</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -2590,11 +2590,11 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="0">
-        <v>50386916</v>
+        <v>50386933</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>圆通速递王赛18521189541</t>
+          <t>雪花🌸</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:23</t>
+          <t>2026-09-12 22:45:37</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
@@ -2650,11 +2650,11 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="0">
-        <v>50386915</v>
+        <v>50386932</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>🌸N🌸</t>
+          <t>刘月军</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:22</t>
+          <t>2026-09-12 22:45:35</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
@@ -2710,11 +2710,11 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="0">
-        <v>50366693</v>
+        <v>50386930</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>刘普荣</t>
+          <t>Number Life</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 12:49:03</t>
+          <t>2026-09-12 22:45:35</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="I45" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J45" s="0" t="inlineStr">
@@ -2770,11 +2770,11 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="0">
-        <v>50366409</v>
+        <v>50386929</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>努力面前！</t>
+          <t>刚刚好</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 12:39:51</t>
+          <t>2026-09-12 22:45:30</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
@@ -2830,11 +2830,11 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="0">
-        <v>50366405</v>
+        <v>50386919</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>llq</t>
+          <t>沙漠一滴水</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 12:39:47</t>
+          <t>2026-09-12 22:45:25</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
@@ -2890,11 +2890,11 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="0">
-        <v>50359189</v>
+        <v>50386916</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>圆通速递王赛18521189541</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:41:29</t>
+          <t>2026-09-12 22:45:23</t>
         </is>
       </c>
       <c r="H48" s="0" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I48" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J48" s="0" t="inlineStr">
@@ -2950,11 +2950,11 @@
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="0">
-        <v>50359174</v>
+        <v>50386915</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>娟</t>
+          <t>🌸N🌸</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:41:19</t>
+          <t>2026-09-12 22:45:22</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="I49" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J49" s="0" t="inlineStr">
@@ -3010,11 +3010,11 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="0">
-        <v>50359138</v>
+        <v>50366693</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>藏酒</t>
+          <t>刘普荣</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:40:41</t>
+          <t>2026-09-12 12:49:03</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="I50" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J50" s="0" t="inlineStr">
@@ -3070,11 +3070,11 @@
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="0">
-        <v>50359079</v>
+        <v>50366409</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>单</t>
+          <t>努力面前！</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:39:11</t>
+          <t>2026-09-12 12:39:51</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
@@ -3130,11 +3130,11 @@
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="0">
-        <v>50359055</v>
+        <v>50366405</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>一念花开，不负期待</t>
+          <t>llq</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:38:41</t>
+          <t>2026-09-12 12:39:47</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
@@ -3190,11 +3190,11 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="0">
-        <v>50359049</v>
+        <v>50359189</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>AAA张敏</t>
+          <t>雪</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:38:34</t>
+          <t>2026-09-12 09:41:29</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="I53" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J53" s="0" t="inlineStr">
@@ -3250,11 +3250,11 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="0">
-        <v>50359039</v>
+        <v>50359174</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>龙🐉哥阿凯15063798299</t>
+          <t>娟</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:38:23</t>
+          <t>2026-09-12 09:41:19</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="I54" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J54" s="0" t="inlineStr">
@@ -3310,11 +3310,11 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="0">
-        <v>50326097</v>
+        <v>50359138</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>华</t>
+          <t>藏酒</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>2026-09-11 12:32:19</t>
+          <t>2026-09-12 09:40:41</t>
         </is>
       </c>
       <c r="H55" s="0" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="I55" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J55" s="0" t="inlineStr">
@@ -3370,11 +3370,11 @@
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="0">
-        <v>50325826</v>
+        <v>50359079</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>刘爽</t>
+          <t>单</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>2026-09-11 12:22:51</t>
+          <t>2026-09-12 09:39:11</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="I56" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J56" s="0" t="inlineStr">
@@ -3430,11 +3430,11 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="0">
-        <v>50325823</v>
+        <v>50359055</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>辉</t>
+          <t>一念花开，不负期待</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>2026-09-11 12:22:41</t>
+          <t>2026-09-12 09:38:41</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="I57" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J57" s="0" t="inlineStr">
@@ -3490,11 +3490,11 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="0">
-        <v>50325804</v>
+        <v>50359049</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>早上好  °</t>
+          <t>AAA张敏</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>2026-09-11 12:22:09</t>
+          <t>2026-09-12 09:38:34</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="I58" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J58" s="0" t="inlineStr">
@@ -3550,11 +3550,11 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="0">
-        <v>50325790</v>
+        <v>50359039</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>꒰ঌ🤍໒꒱blingbling</t>
+          <t>龙🐉哥阿凯15063798299</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>2026-09-11 12:21:49</t>
+          <t>2026-09-12 09:38:23</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="I59" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J59" s="0" t="inlineStr">
@@ -3610,11 +3610,11 @@
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="0">
-        <v>50297022</v>
+        <v>50326097</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>剑哥（大福）</t>
+          <t>华</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>2026-09-10 17:54:27</t>
+          <t>2026-09-11 12:32:19</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
@@ -3670,11 +3670,11 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="0">
-        <v>50296929</v>
+        <v>50325826</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>Mrs Sun</t>
+          <t>刘爽</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>2026-09-10 17:51:31</t>
+          <t>2026-09-11 12:22:51</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
@@ -3730,11 +3730,11 @@
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="0">
-        <v>50266459</v>
+        <v>50325823</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>小不点</t>
+          <t>辉</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:22:15</t>
+          <t>2026-09-11 12:22:41</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="I62" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
@@ -3790,11 +3790,11 @@
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="0">
-        <v>50266152</v>
+        <v>50325804</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>AAA蝈蝈</t>
+          <t>早上好  °</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:09:54</t>
+          <t>2026-09-11 12:22:09</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I63" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J63" s="0" t="inlineStr">
@@ -3850,11 +3850,11 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="0">
-        <v>50266129</v>
+        <v>50325790</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>꒰ঌ🤍໒꒱blingbling</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:08:45</t>
+          <t>2026-09-11 12:21:49</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="I64" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J64" s="0" t="inlineStr">
@@ -3910,11 +3910,11 @@
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="0">
-        <v>50266113</v>
+        <v>50297022</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>剑哥（大福）</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:08:12</t>
+          <t>2026-09-10 17:54:27</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="I65" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J65" s="0" t="inlineStr">
@@ -3970,11 +3970,11 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="0">
-        <v>50266101</v>
+        <v>50296929</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>阿文</t>
+          <t>Mrs Sun</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:07:45</t>
+          <t>2026-09-10 17:51:31</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="I66" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J66" s="0" t="inlineStr">
@@ -4030,11 +4030,11 @@
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="0">
-        <v>50266092</v>
+        <v>50266459</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>坦然人生</t>
+          <t>小不点</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:07:07</t>
+          <t>2026-09-09 23:22:15</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="I67" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J67" s="0" t="inlineStr">
@@ -4090,11 +4090,11 @@
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="0">
-        <v>50266076</v>
+        <v>50266152</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>幸福生活</t>
+          <t>AAA蝈蝈</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:06:21</t>
+          <t>2026-09-09 23:09:54</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
@@ -4150,11 +4150,11 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="0">
-        <v>50266070</v>
+        <v>50266129</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>一帆风顺</t>
+          <t>April</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:06:09</t>
+          <t>2026-09-09 23:08:45</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
@@ -4210,11 +4210,11 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="0">
-        <v>50266069</v>
+        <v>50266113</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>开源证券 李斌</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:06:05</t>
+          <t>2026-09-09 23:08:12</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="I70" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J70" s="0" t="inlineStr">
@@ -4270,11 +4270,11 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="0">
-        <v>50266068</v>
+        <v>50266101</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>七彩妹</t>
+          <t>阿文</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:06:05</t>
+          <t>2026-09-09 23:07:45</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
@@ -4330,11 +4330,11 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="0">
-        <v>50243460</v>
+        <v>50266092</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>小勤</t>
+          <t>坦然人生</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:30:09</t>
+          <t>2026-09-09 23:07:07</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
@@ -4390,11 +4390,11 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="0">
-        <v>50243459</v>
+        <v>50266076</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>为你守候</t>
+          <t>幸福生活</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:30:09</t>
+          <t>2026-09-09 23:06:21</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
@@ -4450,11 +4450,11 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="0">
-        <v>50243390</v>
+        <v>50266070</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>💦 ~雷💍🌙</t>
+          <t>一帆风顺</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:28:18</t>
+          <t>2026-09-09 23:06:09</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
@@ -4510,11 +4510,11 @@
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="0">
-        <v>50243384</v>
+        <v>50266069</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>滤镜</t>
+          <t>开源证券 李斌</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:28:05</t>
+          <t>2026-09-09 23:06:05</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
@@ -4570,11 +4570,11 @@
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="0">
-        <v>50243382</v>
+        <v>50266068</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>幸运常伴</t>
+          <t>七彩妹</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:27:57</t>
+          <t>2026-09-09 23:06:05</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
@@ -4630,11 +4630,11 @@
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="0">
-        <v>50243378</v>
+        <v>50243460</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>Beate</t>
+          <t>小勤</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:27:53</t>
+          <t>2026-09-09 12:30:09</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -4690,11 +4690,11 @@
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="0">
-        <v>50243377</v>
+        <v>50243459</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>心存善念，善行善念圆梦感恩一切</t>
+          <t>为你守候</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:27:51</t>
+          <t>2026-09-09 12:30:09</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="I78" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J78" s="0" t="inlineStr">
@@ -4745,21 +4745,16 @@
       <c r="L78" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N78" s="0" t="inlineStr">
-        <is>
-          <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="0">
-        <v>50243376</v>
+        <v>50243390</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>迪士尼在逃公主👑</t>
+          <t>💦 ~雷💍🌙</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -4784,7 +4779,7 @@
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:27:46</t>
+          <t>2026-09-09 12:28:18</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
@@ -4815,11 +4810,11 @@
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="0">
-        <v>50243086</v>
+        <v>50243384</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>马永建</t>
+          <t>滤镜</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -4844,7 +4839,7 @@
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:18:59</t>
+          <t>2026-09-09 12:28:05</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -4854,7 +4849,7 @@
       </c>
       <c r="I80" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J80" s="0" t="inlineStr">
@@ -4875,11 +4870,11 @@
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="0">
-        <v>50243069</v>
+        <v>50243382</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>茗香笛月</t>
+          <t>幸运常伴</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -4904,7 +4899,7 @@
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:18:27</t>
+          <t>2026-09-09 12:27:57</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -4914,7 +4909,7 @@
       </c>
       <c r="I81" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J81" s="0" t="inlineStr">
@@ -4935,11 +4930,11 @@
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="0">
-        <v>50236356</v>
+        <v>50243378</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>潮汕贤哥</t>
+          <t>Beate</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -4964,7 +4959,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 09:38:49</t>
+          <t>2026-09-09 12:27:53</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -4995,11 +4990,11 @@
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="0">
-        <v>50236274</v>
+        <v>50243377</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>A珍丽</t>
+          <t>心存善念，善行善念圆梦感恩一切</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -5024,7 +5019,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 09:35:59</t>
+          <t>2026-09-09 12:27:51</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -5034,7 +5029,7 @@
       </c>
       <c r="I83" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J83" s="0" t="inlineStr">
@@ -5050,16 +5045,21 @@
       <c r="L83" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N83" s="0" t="inlineStr">
+        <is>
+          <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="0">
-        <v>50236266</v>
+        <v>50243376</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>秋夜清风</t>
+          <t>迪士尼在逃公主👑</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 09:35:39</t>
+          <t>2026-09-09 12:27:46</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
@@ -5115,11 +5115,11 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="0">
-        <v>50225279</v>
+        <v>50243086</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>family-man</t>
+          <t>马永建</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 23:19:10</t>
+          <t>2026-09-09 12:18:59</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="I85" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J85" s="0" t="inlineStr">
@@ -5175,11 +5175,11 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="0">
-        <v>50225270</v>
+        <v>50243069</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>昨日伊人</t>
+          <t>茗香笛月</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 23:18:01</t>
+          <t>2026-09-09 12:18:27</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="I86" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J86" s="0" t="inlineStr">
@@ -5235,11 +5235,11 @@
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="0">
-        <v>50225133</v>
+        <v>50236356</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>老孙</t>
+          <t>潮汕贤哥</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 23:10:58</t>
+          <t>2026-09-09 09:38:49</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
@@ -5295,11 +5295,11 @@
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="0">
-        <v>50224890</v>
+        <v>50236274</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>刘娟</t>
+          <t>A珍丽</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:59:17</t>
+          <t>2026-09-09 09:35:59</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
@@ -5355,11 +5355,11 @@
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="0">
-        <v>50224884</v>
+        <v>50236266</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>果盈盈</t>
+          <t>秋夜清风</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:59:07</t>
+          <t>2026-09-09 09:35:39</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
@@ -5415,11 +5415,11 @@
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="0">
-        <v>50224877</v>
+        <v>50225279</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>Mr. 庞</t>
+          <t>family-man</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:43</t>
+          <t>2026-09-08 23:19:10</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="I90" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J90" s="0" t="inlineStr">
@@ -5475,11 +5475,11 @@
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="0">
-        <v>50224876</v>
+        <v>50225270</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>最美不过遇见你</t>
+          <t>昨日伊人</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:43</t>
+          <t>2026-09-08 23:18:01</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
@@ -5535,11 +5535,11 @@
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="0">
-        <v>50224875</v>
+        <v>50225133</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>^o^送恩光</t>
+          <t>老孙</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:39</t>
+          <t>2026-09-08 23:10:58</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
@@ -5595,11 +5595,11 @@
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="0">
-        <v>50224874</v>
+        <v>50224890</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>淡墨无殇</t>
+          <t>刘娟</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:37</t>
+          <t>2026-09-08 22:59:17</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
@@ -5655,11 +5655,11 @@
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="0">
-        <v>50224873</v>
+        <v>50224884</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>阳春白雪</t>
+          <t>果盈盈</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:35</t>
+          <t>2026-09-08 22:59:07</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -5715,11 +5715,11 @@
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="0">
-        <v>50224868</v>
+        <v>50224877</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>从未</t>
+          <t>Mr. 庞</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:19</t>
+          <t>2026-09-08 22:58:43</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -5775,11 +5775,11 @@
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="0">
-        <v>50223758</v>
+        <v>50224876</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>FREESA</t>
+          <t>最美不过遇见你</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:20:27</t>
+          <t>2026-09-08 22:58:43</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="I96" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J96" s="0" t="inlineStr">
@@ -5835,11 +5835,11 @@
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="0">
-        <v>50201671</v>
+        <v>50224875</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>黑班长</t>
+          <t>^o^送恩光</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 12:20:09</t>
+          <t>2026-09-08 22:58:39</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="I97" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J97" s="0" t="inlineStr">
@@ -5895,11 +5895,11 @@
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="0">
-        <v>50201580</v>
+        <v>50224874</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>黄智勇18649168223中华老字号皮糖</t>
+          <t>淡墨无殇</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 12:18:43</t>
+          <t>2026-09-08 22:58:37</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="I98" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J98" s="0" t="inlineStr">
@@ -5955,11 +5955,11 @@
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="0">
-        <v>50201564</v>
+        <v>50224873</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>小鱼儿</t>
+          <t>阳春白雪</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 12:18:28</t>
+          <t>2026-09-08 22:58:35</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="I99" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J99" s="0" t="inlineStr">
@@ -6015,11 +6015,11 @@
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="0">
-        <v>50201559</v>
+        <v>50224868</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>语诺</t>
+          <t>从未</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 12:18:17</t>
+          <t>2026-09-08 22:58:19</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="I100" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J100" s="0" t="inlineStr">
@@ -6075,11 +6075,11 @@
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="0">
-        <v>50194907</v>
+        <v>50223758</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>红情雨申</t>
+          <t>FREESA</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 09:26:54</t>
+          <t>2026-09-08 22:20:27</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="I101" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J101" s="0" t="inlineStr">
@@ -6135,11 +6135,11 @@
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="0">
-        <v>50194816</v>
+        <v>50201671</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>沈新丽</t>
+          <t>黑班长</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 09:25:31</t>
+          <t>2026-09-08 12:20:09</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="I102" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J102" s="0" t="inlineStr">
@@ -6195,11 +6195,11 @@
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="0">
-        <v>50194810</v>
+        <v>50201580</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>活在当下、、</t>
+          <t>黄智勇18649168223中华老字号皮糖</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 09:25:21</t>
+          <t>2026-09-08 12:18:43</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="I103" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J103" s="0" t="inlineStr">
@@ -6255,11 +6255,11 @@
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="0">
-        <v>50194790</v>
+        <v>50201564</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>Anne🦋</t>
+          <t>小鱼儿</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 09:24:47</t>
+          <t>2026-09-08 12:18:28</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="I104" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J104" s="0" t="inlineStr">
@@ -6315,11 +6315,11 @@
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="0">
-        <v>50169357</v>
+        <v>50201559</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>枫</t>
+          <t>语诺</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 18:04:20</t>
+          <t>2026-09-08 12:18:17</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -6375,11 +6375,11 @@
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="0">
-        <v>50169102</v>
+        <v>50194907</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>溫柔的我</t>
+          <t>红情雨申</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 17:54:04</t>
+          <t>2026-09-08 09:26:54</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="I106" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J106" s="0" t="inlineStr">
@@ -6435,11 +6435,11 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="0">
-        <v>50169093</v>
+        <v>50194816</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>明月</t>
+          <t>沈新丽</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 17:53:31</t>
+          <t>2026-09-08 09:25:31</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="I107" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J107" s="0" t="inlineStr">
@@ -6495,11 +6495,11 @@
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="0">
-        <v>50169077</v>
+        <v>50194810</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>心照不宣</t>
+          <t>活在当下、、</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 17:53:03</t>
+          <t>2026-09-08 09:25:21</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I108" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J108" s="0" t="inlineStr">
@@ -6555,11 +6555,11 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="0">
-        <v>50158131</v>
+        <v>50194790</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>郭军</t>
+          <t>Anne🦋</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:44:06</t>
+          <t>2026-09-08 09:24:47</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I109" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J109" s="0" t="inlineStr">
@@ -6615,11 +6615,11 @@
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="0">
-        <v>50158087</v>
+        <v>50169357</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>小白杨</t>
+          <t>枫</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:42:51</t>
+          <t>2026-09-07 18:04:20</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
@@ -6675,11 +6675,11 @@
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="0">
-        <v>50158049</v>
+        <v>50169102</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>心之所向，皆为美好。</t>
+          <t>溫柔的我</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:41:48</t>
+          <t>2026-09-07 17:54:04</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
@@ -6735,11 +6735,11 @@
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="0">
-        <v>50158048</v>
+        <v>50169093</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>余生，请多指教</t>
+          <t>明月</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:41:46</t>
+          <t>2026-09-07 17:53:31</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
@@ -6795,11 +6795,11 @@
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="0">
-        <v>50158047</v>
+        <v>50169077</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>刘星</t>
+          <t>心照不宣</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:41:39</t>
+          <t>2026-09-07 17:53:03</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
@@ -6855,11 +6855,11 @@
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="0">
-        <v>50158044</v>
+        <v>50158131</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>赵云鹏㇏</t>
+          <t>郭军</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:41:33</t>
+          <t>2026-09-07 12:44:06</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
@@ -6915,11 +6915,11 @@
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="0">
-        <v>50140343</v>
+        <v>50158087</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>A沙宣（采购号）</t>
+          <t>小白杨</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 23:14:27</t>
+          <t>2026-09-07 12:42:51</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="I115" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J115" s="0" t="inlineStr">
@@ -6975,11 +6975,11 @@
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="0">
-        <v>50139986</v>
+        <v>50158049</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>雪在烧</t>
+          <t>心之所向，皆为美好。</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 23:00:51</t>
+          <t>2026-09-07 12:41:48</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I116" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J116" s="0" t="inlineStr">
@@ -7035,11 +7035,11 @@
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="0">
-        <v>50139951</v>
+        <v>50158048</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>随遇而安</t>
+          <t>余生，请多指教</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:08</t>
+          <t>2026-09-07 12:41:46</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="I117" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J117" s="0" t="inlineStr">
@@ -7095,11 +7095,11 @@
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="0">
-        <v>50139930</v>
+        <v>50158047</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>秋钰</t>
+          <t>刘星</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:58:25</t>
+          <t>2026-09-07 12:41:39</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="I118" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J118" s="0" t="inlineStr">
@@ -7155,11 +7155,11 @@
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="0">
-        <v>50139907</v>
+        <v>50158044</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>旧时明月</t>
+          <t>赵云鹏㇏</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:57:19</t>
+          <t>2026-09-07 12:41:33</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="I119" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J119" s="0" t="inlineStr">
@@ -7215,11 +7215,11 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="0">
-        <v>50139891</v>
+        <v>50140343</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>空白</t>
+          <t>A沙宣（采购号）</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:56:55</t>
+          <t>2026-09-06 23:14:27</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
@@ -7275,11 +7275,11 @@
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="0">
-        <v>50139861</v>
+        <v>50139986</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>休闲快乐</t>
+          <t>雪在烧</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:56:03</t>
+          <t>2026-09-06 23:00:51</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
@@ -7335,11 +7335,11 @@
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="0">
-        <v>50139844</v>
+        <v>50139951</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>এ᭄悦己ꦿ᭄࿐</t>
+          <t>随遇而安</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:35</t>
+          <t>2026-09-06 22:59:08</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I122" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J122" s="0" t="inlineStr">
@@ -7395,11 +7395,11 @@
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="0">
-        <v>50139839</v>
+        <v>50139930</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>ღ᭄冬夏尚品℘࿐</t>
+          <t>秋钰</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:27</t>
+          <t>2026-09-06 22:58:25</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="I123" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J123" s="0" t="inlineStr">
@@ -7455,11 +7455,11 @@
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="0">
-        <v>50139837</v>
+        <v>50139907</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>杨言武</t>
+          <t>旧时明月</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:23</t>
+          <t>2026-09-06 22:57:19</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
@@ -7515,11 +7515,11 @@
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="0">
-        <v>50139835</v>
+        <v>50139891</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>Y.m烟花爆竹🧨🧨🧨</t>
+          <t>空白</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:21</t>
+          <t>2026-09-06 22:56:55</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
@@ -7575,11 +7575,11 @@
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="0">
-        <v>50139832</v>
+        <v>50139861</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>太阳🌞</t>
+          <t>休闲快乐</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:17</t>
+          <t>2026-09-06 22:56:03</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
@@ -7635,11 +7635,11 @@
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="0">
-        <v>50139824</v>
+        <v>50139844</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>安安妈妈</t>
+          <t>এ᭄悦己ꦿ᭄࿐</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:09</t>
+          <t>2026-09-06 22:55:35</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
@@ -7695,11 +7695,11 @@
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="0">
-        <v>50139818</v>
+        <v>50139839</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>静     ²⁰²⁶₆₆₆</t>
+          <t>ღ᭄冬夏尚品℘࿐</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:54:59</t>
+          <t>2026-09-06 22:55:27</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
@@ -7755,11 +7755,11 @@
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="0">
-        <v>50139814</v>
+        <v>50139837</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>曹恒美</t>
+          <t>杨言武</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:54:53</t>
+          <t>2026-09-06 22:55:23</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
@@ -7815,11 +7815,11 @@
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="0">
-        <v>50139813</v>
+        <v>50139835</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>lucky🍀🍀</t>
+          <t>Y.m烟花爆竹🧨🧨🧨</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:54:51</t>
+          <t>2026-09-06 22:55:21</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -7875,11 +7875,11 @@
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="0">
-        <v>50139794</v>
+        <v>50139832</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>太阳🌞</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:54:31</t>
+          <t>2026-09-06 22:55:17</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -7935,11 +7935,11 @@
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="0">
-        <v>50129606</v>
+        <v>50139824</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>A1风轻云淡</t>
+          <t>安安妈妈</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 17:53:57</t>
+          <t>2026-09-06 22:55:09</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I132" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J132" s="0" t="inlineStr">
@@ -7995,11 +7995,11 @@
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="0">
-        <v>50129482</v>
+        <v>50139818</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>一心有你电话号码，</t>
+          <t>静     ²⁰²⁶₆₆₆</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 17:49:45</t>
+          <t>2026-09-06 22:54:59</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I133" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J133" s="0" t="inlineStr">
@@ -8055,11 +8055,11 @@
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="0">
-        <v>50121359</v>
+        <v>50139814</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>amy</t>
+          <t>曹恒美</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:58:35</t>
+          <t>2026-09-06 22:54:53</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="I134" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J134" s="0" t="inlineStr">
@@ -8115,11 +8115,11 @@
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="0">
-        <v>50121001</v>
+        <v>50139813</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>莲花李秀清</t>
+          <t>lucky🍀🍀</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:47:43</t>
+          <t>2026-09-06 22:54:51</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="I135" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J135" s="0" t="inlineStr">
@@ -8175,11 +8175,11 @@
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="0">
-        <v>50120862</v>
+        <v>50139794</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>cobra</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:44:33</t>
+          <t>2026-09-06 22:54:31</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -8235,11 +8235,11 @@
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="0">
-        <v>50120856</v>
+        <v>50129606</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>海边的星空</t>
+          <t>A1风轻云淡</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:44:17</t>
+          <t>2026-09-06 17:53:57</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I137" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J137" s="0" t="inlineStr">
@@ -8295,11 +8295,11 @@
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="0">
-        <v>50120852</v>
+        <v>50129482</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>柠檬黄🍋陈</t>
+          <t>一心有你电话号码，</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:44:09</t>
+          <t>2026-09-06 17:49:45</t>
         </is>
       </c>
       <c r="H138" s="0" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="I138" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J138" s="0" t="inlineStr">
@@ -8355,11 +8355,11 @@
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="0">
-        <v>50120848</v>
+        <v>50121359</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>英子</t>
+          <t>amy</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:44:01</t>
+          <t>2026-09-06 12:58:35</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="I139" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J139" s="0" t="inlineStr">
@@ -8415,11 +8415,11 @@
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="0">
-        <v>50120818</v>
+        <v>50121001</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>peaceful</t>
+          <t>莲花李秀清</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:42:49</t>
+          <t>2026-09-06 12:47:43</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="I140" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J140" s="0" t="inlineStr">
@@ -8475,11 +8475,11 @@
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="0">
-        <v>50120817</v>
+        <v>50120862</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>fj</t>
+          <t>cobra</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:42:49</t>
+          <t>2026-09-06 12:44:33</t>
         </is>
       </c>
       <c r="H141" s="0" t="inlineStr">
@@ -8535,11 +8535,11 @@
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="0">
-        <v>50120806</v>
+        <v>50120856</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>💍小薇🎀💎🌷</t>
+          <t>海边的星空</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G142" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:42:27</t>
+          <t>2026-09-06 12:44:17</t>
         </is>
       </c>
       <c r="H142" s="0" t="inlineStr">
@@ -8595,11 +8595,11 @@
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="0">
-        <v>50120803</v>
+        <v>50120852</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>于小毛</t>
+          <t>柠檬黄🍋陈</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:42:25</t>
+          <t>2026-09-06 12:44:09</t>
         </is>
       </c>
       <c r="H143" s="0" t="inlineStr">
@@ -8655,11 +8655,11 @@
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="0">
-        <v>50116869</v>
+        <v>50120848</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>美义</t>
+          <t>英子</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 10:56:33</t>
+          <t>2026-09-06 12:44:01</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="I144" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J144" s="0" t="inlineStr">
@@ -8715,11 +8715,11 @@
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="0">
-        <v>50114006</v>
+        <v>50120818</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>幸运草</t>
+          <t>peaceful</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 09:45:01</t>
+          <t>2026-09-06 12:42:49</t>
         </is>
       </c>
       <c r="H145" s="0" t="inlineStr">
@@ -8775,11 +8775,11 @@
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="0">
-        <v>50113664</v>
+        <v>50120817</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>执子之手</t>
+          <t>fj</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 09:37:35</t>
+          <t>2026-09-06 12:42:49</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -8835,11 +8835,11 @@
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="0">
-        <v>50113641</v>
+        <v>50120806</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>新视野</t>
+          <t>💍小薇🎀💎🌷</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 09:36:52</t>
+          <t>2026-09-06 12:42:27</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -8895,11 +8895,11 @@
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="0">
-        <v>50113640</v>
+        <v>50120803</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>安静且聆听</t>
+          <t>于小毛</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 09:36:49</t>
+          <t>2026-09-06 12:42:25</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -8950,21 +8950,16 @@
       <c r="L148" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N148" s="0" t="inlineStr">
-        <is>
-          <t>保山</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="0">
-        <v>50113638</v>
+        <v>50116869</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>十月</t>
+          <t>美义</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
@@ -8989,7 +8984,7 @@
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 09:36:45</t>
+          <t>2026-09-06 10:56:33</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -8999,7 +8994,7 @@
       </c>
       <c r="I149" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J149" s="0" t="inlineStr">
@@ -9020,11 +9015,11 @@
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="0">
-        <v>50100338</v>
+        <v>50114006</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>青山绿水</t>
+          <t>幸运草</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -9049,7 +9044,7 @@
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 23:10:04</t>
+          <t>2026-09-06 09:45:01</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -9080,11 +9075,11 @@
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="0">
-        <v>50100035</v>
+        <v>50113664</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>杨</t>
+          <t>执子之手</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
@@ -9109,7 +9104,7 @@
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:57:53</t>
+          <t>2026-09-06 09:37:35</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -9119,7 +9114,7 @@
       </c>
       <c r="I151" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J151" s="0" t="inlineStr">
@@ -9140,11 +9135,11 @@
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="0">
-        <v>50100033</v>
+        <v>50113641</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>雨后彩虹</t>
+          <t>新视野</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
@@ -9169,7 +9164,7 @@
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:57:47</t>
+          <t>2026-09-06 09:36:52</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -9179,7 +9174,7 @@
       </c>
       <c r="I152" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J152" s="0" t="inlineStr">
@@ -9200,11 +9195,11 @@
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="0">
-        <v>50100028</v>
+        <v>50113640</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>首信海报</t>
+          <t>安静且聆听</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -9229,7 +9224,7 @@
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:57:32</t>
+          <t>2026-09-06 09:36:49</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -9239,7 +9234,7 @@
       </c>
       <c r="I153" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J153" s="0" t="inlineStr">
@@ -9255,16 +9250,21 @@
       <c r="L153" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N153" s="0" t="inlineStr">
+        <is>
+          <t>保山</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="0">
-        <v>50099958</v>
+        <v>50113638</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>张君</t>
+          <t>十月</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:55:57</t>
+          <t>2026-09-06 09:36:45</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="I154" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J154" s="0" t="inlineStr">
@@ -9320,11 +9320,11 @@
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="0">
-        <v>50099933</v>
+        <v>50100338</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>耶和华以勒</t>
+          <t>青山绿水</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:55:31</t>
+          <t>2026-09-05 23:10:04</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="I155" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J155" s="0" t="inlineStr">
@@ -9380,11 +9380,11 @@
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="0">
-        <v>50099844</v>
+        <v>50100035</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>平安</t>
+          <t>杨</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:49</t>
+          <t>2026-09-05 22:57:53</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -9440,11 +9440,11 @@
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="0">
-        <v>50099768</v>
+        <v>50100033</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>阳</t>
+          <t>雨后彩虹</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:49:01</t>
+          <t>2026-09-05 22:57:47</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="I157" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J157" s="0" t="inlineStr">
@@ -9500,11 +9500,11 @@
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="0">
-        <v>50099767</v>
+        <v>50100028</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>梦&amp;爷💫</t>
+          <t>首信海报</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:57</t>
+          <t>2026-09-05 22:57:32</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="I158" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J158" s="0" t="inlineStr">
@@ -9560,11 +9560,11 @@
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="0">
-        <v>50099763</v>
+        <v>50099958</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>李丽</t>
+          <t>张君</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:53</t>
+          <t>2026-09-05 22:55:57</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="I159" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J159" s="0" t="inlineStr">
@@ -9620,11 +9620,11 @@
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="0">
-        <v>50099760</v>
+        <v>50099933</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>A选择无悔</t>
+          <t>耶和华以勒</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:46</t>
+          <t>2026-09-05 22:55:31</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="I160" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J160" s="0" t="inlineStr">
@@ -9680,11 +9680,11 @@
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="0">
-        <v>50099759</v>
+        <v>50099844</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>信念</t>
+          <t>平安</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:44</t>
+          <t>2026-09-05 22:51:49</t>
         </is>
       </c>
       <c r="H161" s="0" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="I161" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J161" s="0" t="inlineStr">
@@ -9740,11 +9740,11 @@
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="0">
-        <v>50099757</v>
+        <v>50099768</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>李lee</t>
+          <t>阳</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:41</t>
+          <t>2026-09-05 22:49:01</t>
         </is>
       </c>
       <c r="H162" s="0" t="inlineStr">
@@ -9800,11 +9800,11 @@
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="0">
-        <v>50099755</v>
+        <v>50099767</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>徐飛燕*^O^*</t>
+          <t>梦&amp;爷💫</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="G163" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:39</t>
+          <t>2026-09-05 22:48:57</t>
         </is>
       </c>
       <c r="H163" s="0" t="inlineStr">
@@ -9860,11 +9860,11 @@
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="0">
-        <v>50099752</v>
+        <v>50099763</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>星移*</t>
+          <t>李丽</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="G164" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:35</t>
+          <t>2026-09-05 22:48:53</t>
         </is>
       </c>
       <c r="H164" s="0" t="inlineStr">
@@ -9920,11 +9920,11 @@
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="0">
-        <v>50099749</v>
+        <v>50099760</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>刘勇</t>
+          <t>A选择无悔</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:28</t>
+          <t>2026-09-05 22:48:46</t>
         </is>
       </c>
       <c r="H165" s="0" t="inlineStr">
@@ -9980,11 +9980,11 @@
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="0">
-        <v>50099741</v>
+        <v>50099759</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>碧皓之游</t>
+          <t>信念</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="G166" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:15</t>
+          <t>2026-09-05 22:48:44</t>
         </is>
       </c>
       <c r="H166" s="0" t="inlineStr">
@@ -10040,11 +10040,11 @@
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="0">
-        <v>50099737</v>
+        <v>50099757</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>书心燕语</t>
+          <t>李lee</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="G167" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:03</t>
+          <t>2026-09-05 22:48:41</t>
         </is>
       </c>
       <c r="H167" s="0" t="inlineStr">
@@ -10100,11 +10100,11 @@
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="0">
-        <v>50099733</v>
+        <v>50099755</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>ღ᭄ꦿ微微一笑ღ᭄ꦿ</t>
+          <t>徐飛燕*^O^*</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="G168" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:47:47</t>
+          <t>2026-09-05 22:48:39</t>
         </is>
       </c>
       <c r="H168" s="0" t="inlineStr">
@@ -10160,11 +10160,11 @@
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="0">
-        <v>50080657</v>
+        <v>50099752</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>平红</t>
+          <t>星移*</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:07:13</t>
+          <t>2026-09-05 22:48:35</t>
         </is>
       </c>
       <c r="H169" s="0" t="inlineStr">
@@ -10220,11 +10220,11 @@
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="0">
-        <v>50080582</v>
+        <v>50099749</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>aabb</t>
+          <t>刘勇</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G170" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:05:19</t>
+          <t>2026-09-05 22:48:28</t>
         </is>
       </c>
       <c r="H170" s="0" t="inlineStr">
@@ -10280,11 +10280,11 @@
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="0">
-        <v>50080559</v>
+        <v>50099741</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>自由人</t>
+          <t>碧皓之游</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="G171" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:04:28</t>
+          <t>2026-09-05 22:48:15</t>
         </is>
       </c>
       <c r="H171" s="0" t="inlineStr">
@@ -10340,11 +10340,11 @@
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="0">
-        <v>50080553</v>
+        <v>50099737</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>晶晶</t>
+          <t>书心燕语</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:04:15</t>
+          <t>2026-09-05 22:48:03</t>
         </is>
       </c>
       <c r="H172" s="0" t="inlineStr">
@@ -10400,11 +10400,11 @@
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="0">
-        <v>50080549</v>
+        <v>50099733</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>ღ᭄ꦿ微微一笑ღ᭄ꦿ</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:04:09</t>
+          <t>2026-09-05 22:47:47</t>
         </is>
       </c>
       <c r="H173" s="0" t="inlineStr">
@@ -10460,11 +10460,11 @@
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="0">
-        <v>50080548</v>
+        <v>50080657</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>盘子</t>
+          <t>平红</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:04:08</t>
+          <t>2026-09-05 13:07:13</t>
         </is>
       </c>
       <c r="H174" s="0" t="inlineStr">
@@ -10520,11 +10520,11 @@
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="0">
-        <v>50080547</v>
+        <v>50080582</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>赵满珍C5</t>
+          <t>aabb</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:04:05</t>
+          <t>2026-09-05 13:05:19</t>
         </is>
       </c>
       <c r="H175" s="0" t="inlineStr">
@@ -10580,11 +10580,11 @@
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="0">
-        <v>50080539</v>
+        <v>50080559</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>平平安安</t>
+          <t>自由人</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:51</t>
+          <t>2026-09-05 13:04:28</t>
         </is>
       </c>
       <c r="H176" s="0" t="inlineStr">
@@ -10640,11 +10640,11 @@
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="0">
-        <v>50080538</v>
+        <v>50080553</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>凡事包容</t>
+          <t>晶晶</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:51</t>
+          <t>2026-09-05 13:04:15</t>
         </is>
       </c>
       <c r="H177" s="0" t="inlineStr">
@@ -10700,11 +10700,11 @@
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="0">
-        <v>50080536</v>
+        <v>50080549</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>吴忧无忧</t>
+          <t>abc</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:47</t>
+          <t>2026-09-05 13:04:09</t>
         </is>
       </c>
       <c r="H178" s="0" t="inlineStr">
@@ -10760,11 +10760,11 @@
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="0">
-        <v>50080535</v>
+        <v>50080548</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>小鱼儿</t>
+          <t>盘子</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:43</t>
+          <t>2026-09-05 13:04:08</t>
         </is>
       </c>
       <c r="H179" s="0" t="inlineStr">
@@ -10820,11 +10820,11 @@
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="0">
-        <v>50080525</v>
+        <v>50080547</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>辞芝锦😎</t>
+          <t>赵满珍C5</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:29</t>
+          <t>2026-09-05 13:04:05</t>
         </is>
       </c>
       <c r="H180" s="0" t="inlineStr">
@@ -10880,11 +10880,11 @@
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="0">
-        <v>50080523</v>
+        <v>50080539</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>早陈</t>
+          <t>平平安安</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="G181" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:21</t>
+          <t>2026-09-05 13:03:51</t>
         </is>
       </c>
       <c r="H181" s="0" t="inlineStr">
@@ -10940,11 +10940,11 @@
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="0">
-        <v>50080516</v>
+        <v>50080538</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>星星の恋人</t>
+          <t>凡事包容</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="G182" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:13</t>
+          <t>2026-09-05 13:03:51</t>
         </is>
       </c>
       <c r="H182" s="0" t="inlineStr">
@@ -11000,11 +11000,11 @@
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="0">
-        <v>50080511</v>
+        <v>50080536</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>无咎</t>
+          <t>吴忧无忧</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="G183" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:09</t>
+          <t>2026-09-05 13:03:47</t>
         </is>
       </c>
       <c r="H183" s="0" t="inlineStr">
@@ -11060,11 +11060,11 @@
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="0">
-        <v>50080477</v>
+        <v>50080535</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>刘小虎</t>
+          <t>小鱼儿</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="G184" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:02:37</t>
+          <t>2026-09-05 13:03:43</t>
         </is>
       </c>
       <c r="H184" s="0" t="inlineStr">
@@ -11120,11 +11120,11 @@
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="0">
-        <v>50074867</v>
+        <v>50080525</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>美好人生</t>
+          <t>辞芝锦😎</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="G185" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 10:19:59</t>
+          <t>2026-09-05 13:03:29</t>
         </is>
       </c>
       <c r="H185" s="0" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="I185" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J185" s="0" t="inlineStr">
@@ -11180,11 +11180,11 @@
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="0">
-        <v>50074273</v>
+        <v>50080523</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>周利平</t>
+          <t>早陈</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="G186" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 10:02:26</t>
+          <t>2026-09-05 13:03:21</t>
         </is>
       </c>
       <c r="H186" s="0" t="inlineStr">
@@ -11240,11 +11240,11 @@
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="0">
-        <v>50074103</v>
+        <v>50080516</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>赵香荣</t>
+          <t>星星の恋人</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="G187" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:58:29</t>
+          <t>2026-09-05 13:03:13</t>
         </is>
       </c>
       <c r="H187" s="0" t="inlineStr">
@@ -11300,11 +11300,11 @@
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="0">
-        <v>50074078</v>
+        <v>50080511</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>长风渡℡明</t>
+          <t>无咎</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="G188" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:57:49</t>
+          <t>2026-09-05 13:03:09</t>
         </is>
       </c>
       <c r="H188" s="0" t="inlineStr">
@@ -11360,11 +11360,11 @@
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="0">
-        <v>50074077</v>
+        <v>50080477</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>海阔天空bi</t>
+          <t>刘小虎</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:57:47</t>
+          <t>2026-09-05 13:02:37</t>
         </is>
       </c>
       <c r="H189" s="0" t="inlineStr">
@@ -11420,11 +11420,11 @@
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="0">
-        <v>50074076</v>
+        <v>50074867</v>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>枫叶红</t>
+          <t>美好人生</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="G190" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:57:47</t>
+          <t>2026-09-05 10:19:59</t>
         </is>
       </c>
       <c r="H190" s="0" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="I190" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J190" s="0" t="inlineStr">
@@ -11480,11 +11480,11 @@
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="0">
-        <v>50074071</v>
+        <v>50074273</v>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>思缘</t>
+          <t>周利平</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="G191" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:57:35</t>
+          <t>2026-09-05 10:02:26</t>
         </is>
       </c>
       <c r="H191" s="0" t="inlineStr">
@@ -11540,11 +11540,11 @@
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="0">
-        <v>50074067</v>
+        <v>50074103</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>悠然</t>
+          <t>赵香荣</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="G192" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:57:25</t>
+          <t>2026-09-05 09:58:29</t>
         </is>
       </c>
       <c r="H192" s="0" t="inlineStr">
@@ -11600,11 +11600,11 @@
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="0">
-        <v>50058017</v>
+        <v>50074078</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>索描贾师＃壹皇贰金山玉旗🇨🇳</t>
+          <t>长风渡℡明</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G193" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:16:49</t>
+          <t>2026-09-05 09:57:49</t>
         </is>
       </c>
       <c r="H193" s="0" t="inlineStr">
@@ -11660,11 +11660,11 @@
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="0">
-        <v>50057895</v>
+        <v>50074077</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>南雪</t>
+          <t>海阔天空bi</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G194" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:12:32</t>
+          <t>2026-09-05 09:57:47</t>
         </is>
       </c>
       <c r="H194" s="0" t="inlineStr">
@@ -11715,21 +11715,16 @@
       <c r="L194" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N194" s="0" t="inlineStr">
-        <is>
-          <t>镇江</t>
         </is>
       </c>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="0">
-        <v>50057857</v>
+        <v>50074076</v>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>可心</t>
+          <t>枫叶红</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
@@ -11754,7 +11749,7 @@
       </c>
       <c r="G195" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:10:55</t>
+          <t>2026-09-05 09:57:47</t>
         </is>
       </c>
       <c r="H195" s="0" t="inlineStr">
@@ -11785,11 +11780,11 @@
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="0">
-        <v>50057854</v>
+        <v>50074071</v>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>张苏龙</t>
+          <t>思缘</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
@@ -11814,7 +11809,7 @@
       </c>
       <c r="G196" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:10:51</t>
+          <t>2026-09-05 09:57:35</t>
         </is>
       </c>
       <c r="H196" s="0" t="inlineStr">
@@ -11845,11 +11840,11 @@
     </row>
     <row r="197" spans="1:14">
       <c r="A197" s="0">
-        <v>50057852</v>
+        <v>50074067</v>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>？</t>
+          <t>悠然</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
@@ -11874,7 +11869,7 @@
       </c>
       <c r="G197" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:10:43</t>
+          <t>2026-09-05 09:57:25</t>
         </is>
       </c>
       <c r="H197" s="0" t="inlineStr">
@@ -11905,11 +11900,11 @@
     </row>
     <row r="198" spans="1:14">
       <c r="A198" s="0">
-        <v>50057841</v>
+        <v>50058017</v>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>向往的生活-电信号</t>
+          <t>索描贾师＃壹皇贰金山玉旗🇨🇳</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
@@ -11934,7 +11929,7 @@
       </c>
       <c r="G198" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:10:09</t>
+          <t>2026-09-04 23:16:49</t>
         </is>
       </c>
       <c r="H198" s="0" t="inlineStr">
@@ -11965,11 +11960,11 @@
     </row>
     <row r="199" spans="1:14">
       <c r="A199" s="0">
-        <v>50057839</v>
+        <v>50057895</v>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>金盏花</t>
+          <t>南雪</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
@@ -11994,7 +11989,7 @@
       </c>
       <c r="G199" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:10:03</t>
+          <t>2026-09-04 23:12:32</t>
         </is>
       </c>
       <c r="H199" s="0" t="inlineStr">
@@ -12020,16 +12015,21 @@
       <c r="L199" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N199" s="0" t="inlineStr">
+        <is>
+          <t>镇江</t>
         </is>
       </c>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" s="0">
-        <v>50032697</v>
+        <v>50057857</v>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>小米. ᩚ</t>
+          <t>可心</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="G200" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 12:24:13</t>
+          <t>2026-09-04 23:10:55</t>
         </is>
       </c>
       <c r="H200" s="0" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="I200" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J200" s="0" t="inlineStr">
@@ -12085,11 +12085,11 @@
     </row>
     <row r="201" spans="1:14">
       <c r="A201" s="0">
-        <v>50032693</v>
+        <v>50057854</v>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>海岸</t>
+          <t>张苏龙</t>
         </is>
       </c>
       <c r="C201" s="0" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="G201" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 12:24:11</t>
+          <t>2026-09-04 23:10:51</t>
         </is>
       </c>
       <c r="H201" s="0" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="I201" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J201" s="0" t="inlineStr">
@@ -12145,11 +12145,11 @@
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="0">
-        <v>50032683</v>
+        <v>50057852</v>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>陆建军</t>
+          <t>？</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="G202" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 12:23:53</t>
+          <t>2026-09-04 23:10:43</t>
         </is>
       </c>
       <c r="H202" s="0" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="I202" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J202" s="0" t="inlineStr">
@@ -12205,11 +12205,11 @@
     </row>
     <row r="203" spans="1:14">
       <c r="A203" s="0">
-        <v>50015883</v>
+        <v>50057841</v>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>A00金华义乌叉车出租电15268650979</t>
+          <t>向往的生活-电信号</t>
         </is>
       </c>
       <c r="C203" s="0" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="G203" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:18:02</t>
+          <t>2026-09-04 23:10:09</t>
         </is>
       </c>
       <c r="H203" s="0" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="I203" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J203" s="0" t="inlineStr">
@@ -12265,11 +12265,11 @@
     </row>
     <row r="204" spans="1:14">
       <c r="A204" s="0">
-        <v>50015882</v>
+        <v>50057839</v>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>建程仓储中心 张川</t>
+          <t>金盏花</t>
         </is>
       </c>
       <c r="C204" s="0" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="G204" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:18:02</t>
+          <t>2026-09-04 23:10:03</t>
         </is>
       </c>
       <c r="H204" s="0" t="inlineStr">
@@ -12325,11 +12325,11 @@
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="0">
-        <v>50015784</v>
+        <v>50032697</v>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>天空</t>
+          <t>小米. ᩚ</t>
         </is>
       </c>
       <c r="C205" s="0" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="G205" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:41</t>
+          <t>2026-09-04 12:24:13</t>
         </is>
       </c>
       <c r="H205" s="0" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="I205" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J205" s="0" t="inlineStr">
@@ -12385,11 +12385,11 @@
     </row>
     <row r="206" spans="1:14">
       <c r="A206" s="0">
-        <v>50015778</v>
+        <v>50032693</v>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>小龙女</t>
+          <t>海岸</t>
         </is>
       </c>
       <c r="C206" s="0" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="G206" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:21</t>
+          <t>2026-09-04 12:24:11</t>
         </is>
       </c>
       <c r="H206" s="0" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="I206" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J206" s="0" t="inlineStr">
@@ -12445,11 +12445,11 @@
     </row>
     <row r="207" spans="1:14">
       <c r="A207" s="0">
-        <v>50015776</v>
+        <v>50032683</v>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>桥梁</t>
+          <t>陆建军</t>
         </is>
       </c>
       <c r="C207" s="0" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G207" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:15</t>
+          <t>2026-09-04 12:23:53</t>
         </is>
       </c>
       <c r="H207" s="0" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="I207" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J207" s="0" t="inlineStr">
@@ -12505,11 +12505,11 @@
     </row>
     <row r="208" spans="1:14">
       <c r="A208" s="0">
-        <v>50015775</v>
+        <v>50015883</v>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>彩云之南</t>
+          <t>A00金华义乌叉车出租电15268650979</t>
         </is>
       </c>
       <c r="C208" s="0" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="G208" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:13</t>
+          <t>2026-09-03 23:18:02</t>
         </is>
       </c>
       <c r="H208" s="0" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="I208" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J208" s="0" t="inlineStr">
@@ -12565,11 +12565,11 @@
     </row>
     <row r="209" spans="1:14">
       <c r="A209" s="0">
-        <v>50015774</v>
+        <v>50015882</v>
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>楊精蓄銳༒</t>
+          <t>建程仓储中心 张川</t>
         </is>
       </c>
       <c r="C209" s="0" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="G209" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:11</t>
+          <t>2026-09-03 23:18:02</t>
         </is>
       </c>
       <c r="H209" s="0" t="inlineStr">
@@ -12625,11 +12625,11 @@
     </row>
     <row r="210" spans="1:14">
       <c r="A210" s="0">
-        <v>50015772</v>
+        <v>50015784</v>
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>不倒翁</t>
+          <t>天空</t>
         </is>
       </c>
       <c r="C210" s="0" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="G210" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:07</t>
+          <t>2026-09-03 23:10:41</t>
         </is>
       </c>
       <c r="H210" s="0" t="inlineStr">
@@ -12685,11 +12685,11 @@
     </row>
     <row r="211" spans="1:14">
       <c r="A211" s="0">
-        <v>50015770</v>
+        <v>50015778</v>
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>一江春水</t>
+          <t>小龙女</t>
         </is>
       </c>
       <c r="C211" s="0" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="G211" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:05</t>
+          <t>2026-09-03 23:10:21</t>
         </is>
       </c>
       <c r="H211" s="0" t="inlineStr">
@@ -12745,11 +12745,11 @@
     </row>
     <row r="212" spans="1:14">
       <c r="A212" s="0">
-        <v>50015767</v>
+        <v>50015776</v>
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>微笑</t>
+          <t>桥梁</t>
         </is>
       </c>
       <c r="C212" s="0" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="G212" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:03</t>
+          <t>2026-09-03 23:10:15</t>
         </is>
       </c>
       <c r="H212" s="0" t="inlineStr">
@@ -12805,11 +12805,11 @@
     </row>
     <row r="213" spans="1:14">
       <c r="A213" s="0">
-        <v>50015763</v>
+        <v>50015775</v>
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>北斗星</t>
+          <t>彩云之南</t>
         </is>
       </c>
       <c r="C213" s="0" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="G213" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:09:39</t>
+          <t>2026-09-03 23:10:13</t>
         </is>
       </c>
       <c r="H213" s="0" t="inlineStr">
@@ -12865,11 +12865,11 @@
     </row>
     <row r="214" spans="1:14">
       <c r="A214" s="0">
-        <v>49989442</v>
+        <v>50015774</v>
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>冬梅花儿开王丽君</t>
+          <t>楊精蓄銳༒</t>
         </is>
       </c>
       <c r="C214" s="0" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="G214" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 12:23:43</t>
+          <t>2026-09-03 23:10:11</t>
         </is>
       </c>
       <c r="H214" s="0" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="I214" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J214" s="0" t="inlineStr">
@@ -12925,11 +12925,11 @@
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="0">
-        <v>49989431</v>
+        <v>50015772</v>
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>风声</t>
+          <t>不倒翁</t>
         </is>
       </c>
       <c r="C215" s="0" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="G215" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 12:23:25</t>
+          <t>2026-09-03 23:10:07</t>
         </is>
       </c>
       <c r="H215" s="0" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="I215" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J215" s="0" t="inlineStr">
@@ -12985,11 +12985,11 @@
     </row>
     <row r="216" spans="1:14">
       <c r="A216" s="0">
-        <v>49989419</v>
+        <v>50015770</v>
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>胡宾</t>
+          <t>一江春水</t>
         </is>
       </c>
       <c r="C216" s="0" t="inlineStr">
@@ -13014,7 +13014,7 @@
       </c>
       <c r="G216" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 12:23:13</t>
+          <t>2026-09-03 23:10:05</t>
         </is>
       </c>
       <c r="H216" s="0" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="I216" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J216" s="0" t="inlineStr">
@@ -13045,11 +13045,11 @@
     </row>
     <row r="217" spans="1:14">
       <c r="A217" s="0">
-        <v>49989410</v>
+        <v>50015767</v>
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
-          <t>永远</t>
+          <t>微笑</t>
         </is>
       </c>
       <c r="C217" s="0" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="G217" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 12:23:03</t>
+          <t>2026-09-03 23:10:03</t>
         </is>
       </c>
       <c r="H217" s="0" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="I217" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J217" s="0" t="inlineStr">
@@ -13105,11 +13105,11 @@
     </row>
     <row r="218" spans="1:14">
       <c r="A218" s="0">
-        <v>49984259</v>
+        <v>50015763</v>
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
-          <t>好运包张</t>
+          <t>北斗星</t>
         </is>
       </c>
       <c r="C218" s="0" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="G218" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 09:55:37</t>
+          <t>2026-09-03 23:09:39</t>
         </is>
       </c>
       <c r="H218" s="0" t="inlineStr">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="I218" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J218" s="0" t="inlineStr">
@@ -13165,11 +13165,11 @@
     </row>
     <row r="219" spans="1:14">
       <c r="A219" s="0">
-        <v>49984055</v>
+        <v>49989442</v>
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
-          <t>点点星辰</t>
+          <t>冬梅花儿开王丽君</t>
         </is>
       </c>
       <c r="C219" s="0" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="G219" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 09:49:33</t>
+          <t>2026-09-03 12:23:43</t>
         </is>
       </c>
       <c r="H219" s="0" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="I219" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J219" s="0" t="inlineStr">
@@ -13225,11 +13225,11 @@
     </row>
     <row r="220" spans="1:14">
       <c r="A220" s="0">
-        <v>49983134</v>
+        <v>49989431</v>
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
-          <t>Zhangrruzhen张如真</t>
+          <t>风声</t>
         </is>
       </c>
       <c r="C220" s="0" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="G220" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 09:25:21</t>
+          <t>2026-09-03 12:23:25</t>
         </is>
       </c>
       <c r="H220" s="0" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="I220" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J220" s="0" t="inlineStr">
@@ -13285,11 +13285,11 @@
     </row>
     <row r="221" spans="1:14">
       <c r="A221" s="0">
-        <v>49971209</v>
+        <v>49989419</v>
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
-          <t>顺丰顺水</t>
+          <t>胡宾</t>
         </is>
       </c>
       <c r="C221" s="0" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="G221" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:29:41</t>
+          <t>2026-09-03 12:23:13</t>
         </is>
       </c>
       <c r="H221" s="0" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="I221" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J221" s="0" t="inlineStr">
@@ -13345,11 +13345,11 @@
     </row>
     <row r="222" spans="1:14">
       <c r="A222" s="0">
-        <v>49970732</v>
+        <v>49989410</v>
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
-          <t>China 🇨🇳</t>
+          <t>永远</t>
         </is>
       </c>
       <c r="C222" s="0" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="G222" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:13:53</t>
+          <t>2026-09-03 12:23:03</t>
         </is>
       </c>
       <c r="H222" s="0" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="I222" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J222" s="0" t="inlineStr">
@@ -13405,11 +13405,11 @@
     </row>
     <row r="223" spans="1:14">
       <c r="A223" s="0">
-        <v>49970712</v>
+        <v>49984259</v>
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
-          <t>月色琴弦</t>
+          <t>好运包张</t>
         </is>
       </c>
       <c r="C223" s="0" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="G223" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:13:07</t>
+          <t>2026-09-03 09:55:37</t>
         </is>
       </c>
       <c r="H223" s="0" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="I223" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J223" s="0" t="inlineStr">
@@ -13465,11 +13465,11 @@
     </row>
     <row r="224" spans="1:14">
       <c r="A224" s="0">
-        <v>49970699</v>
+        <v>49984055</v>
       </c>
       <c r="B224" s="0" t="inlineStr">
         <is>
-          <t>铜铃</t>
+          <t>点点星辰</t>
         </is>
       </c>
       <c r="C224" s="0" t="inlineStr">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="G224" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:12:49</t>
+          <t>2026-09-03 09:49:33</t>
         </is>
       </c>
       <c r="H224" s="0" t="inlineStr">
@@ -13525,11 +13525,11 @@
     </row>
     <row r="225" spans="1:14">
       <c r="A225" s="0">
-        <v>49970698</v>
+        <v>49983134</v>
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
-          <t>东风吹</t>
+          <t>Zhangrruzhen张如真</t>
         </is>
       </c>
       <c r="C225" s="0" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="G225" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:12:47</t>
+          <t>2026-09-03 09:25:21</t>
         </is>
       </c>
       <c r="H225" s="0" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="I225" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J225" s="0" t="inlineStr">
@@ -13585,11 +13585,11 @@
     </row>
     <row r="226" spans="1:14">
       <c r="A226" s="0">
-        <v>49970683</v>
+        <v>49971209</v>
       </c>
       <c r="B226" s="0" t="inlineStr">
         <is>
-          <t>杨永强</t>
+          <t>顺丰顺水</t>
         </is>
       </c>
       <c r="C226" s="0" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="G226" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:12:17</t>
+          <t>2026-09-02 23:29:41</t>
         </is>
       </c>
       <c r="H226" s="0" t="inlineStr">
@@ -13645,11 +13645,11 @@
     </row>
     <row r="227" spans="1:14">
       <c r="A227" s="0">
-        <v>49970662</v>
+        <v>49970732</v>
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
-          <t>盈丰</t>
+          <t>China 🇨🇳</t>
         </is>
       </c>
       <c r="C227" s="0" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="G227" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:11:33</t>
+          <t>2026-09-02 23:13:53</t>
         </is>
       </c>
       <c r="H227" s="0" t="inlineStr">
@@ -13705,11 +13705,11 @@
     </row>
     <row r="228" spans="1:14">
       <c r="A228" s="0">
-        <v>49970652</v>
+        <v>49970712</v>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>YAN</t>
+          <t>月色琴弦</t>
         </is>
       </c>
       <c r="C228" s="0" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="G228" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:11:15</t>
+          <t>2026-09-02 23:13:07</t>
         </is>
       </c>
       <c r="H228" s="0" t="inlineStr">
@@ -13765,11 +13765,11 @@
     </row>
     <row r="229" spans="1:14">
       <c r="A229" s="0">
-        <v>49970649</v>
+        <v>49970699</v>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>彩虹（宋荷娣）</t>
+          <t>铜铃</t>
         </is>
       </c>
       <c r="C229" s="0" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="G229" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:11:11</t>
+          <t>2026-09-02 23:12:49</t>
         </is>
       </c>
       <c r="H229" s="0" t="inlineStr">
@@ -13825,11 +13825,11 @@
     </row>
     <row r="230" spans="1:14">
       <c r="A230" s="0">
-        <v>49970648</v>
+        <v>49970698</v>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
-          <t>天知心</t>
+          <t>东风吹</t>
         </is>
       </c>
       <c r="C230" s="0" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="G230" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:11:08</t>
+          <t>2026-09-02 23:12:47</t>
         </is>
       </c>
       <c r="H230" s="0" t="inlineStr">
@@ -13885,11 +13885,11 @@
     </row>
     <row r="231" spans="1:14">
       <c r="A231" s="0">
-        <v>49970643</v>
+        <v>49970683</v>
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
-          <t>好运来</t>
+          <t>杨永强</t>
         </is>
       </c>
       <c r="C231" s="0" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="G231" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:10:55</t>
+          <t>2026-09-02 23:12:17</t>
         </is>
       </c>
       <c r="H231" s="0" t="inlineStr">
@@ -13945,11 +13945,11 @@
     </row>
     <row r="232" spans="1:14">
       <c r="A232" s="0">
-        <v>49937566</v>
+        <v>49970662</v>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
-          <t>简单sincerity</t>
+          <t>盈丰</t>
         </is>
       </c>
       <c r="C232" s="0" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="G232" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 10:10:33</t>
+          <t>2026-09-02 23:11:33</t>
         </is>
       </c>
       <c r="H232" s="0" t="inlineStr">
@@ -14005,11 +14005,11 @@
     </row>
     <row r="233" spans="1:14">
       <c r="A233" s="0">
-        <v>49937187</v>
+        <v>49970652</v>
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
-          <t>莲子</t>
+          <t>YAN</t>
         </is>
       </c>
       <c r="C233" s="0" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="G233" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:58:56</t>
+          <t>2026-09-02 23:11:15</t>
         </is>
       </c>
       <c r="H233" s="0" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="I233" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J233" s="0" t="inlineStr">
@@ -14065,11 +14065,11 @@
     </row>
     <row r="234" spans="1:14">
       <c r="A234" s="0">
-        <v>49937101</v>
+        <v>49970649</v>
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
-          <t>蓉儿</t>
+          <t>彩虹（宋荷娣）</t>
         </is>
       </c>
       <c r="C234" s="0" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="G234" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:56:16</t>
+          <t>2026-09-02 23:11:11</t>
         </is>
       </c>
       <c r="H234" s="0" t="inlineStr">
@@ -14125,11 +14125,11 @@
     </row>
     <row r="235" spans="1:14">
       <c r="A235" s="0">
-        <v>49937098</v>
+        <v>49970648</v>
       </c>
       <c r="B235" s="0" t="inlineStr">
         <is>
-          <t>瀚林2368</t>
+          <t>天知心</t>
         </is>
       </c>
       <c r="C235" s="0" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="G235" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:56:15</t>
+          <t>2026-09-02 23:11:08</t>
         </is>
       </c>
       <c r="H235" s="0" t="inlineStr">
@@ -14185,11 +14185,11 @@
     </row>
     <row r="236" spans="1:14">
       <c r="A236" s="0">
-        <v>49937081</v>
+        <v>49970643</v>
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
-          <t>🔱 花中之美</t>
+          <t>好运来</t>
         </is>
       </c>
       <c r="C236" s="0" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="G236" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:55:47</t>
+          <t>2026-09-02 23:10:55</t>
         </is>
       </c>
       <c r="H236" s="0" t="inlineStr">
@@ -14245,11 +14245,11 @@
     </row>
     <row r="237" spans="1:14">
       <c r="A237" s="0">
-        <v>49937066</v>
+        <v>49937566</v>
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
-          <t>雨情</t>
+          <t>简单sincerity</t>
         </is>
       </c>
       <c r="C237" s="0" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="G237" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:55:27</t>
+          <t>2026-09-02 10:10:33</t>
         </is>
       </c>
       <c r="H237" s="0" t="inlineStr">
@@ -14305,11 +14305,11 @@
     </row>
     <row r="238" spans="1:14">
       <c r="A238" s="0">
-        <v>49937061</v>
+        <v>49937187</v>
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
-          <t>Sunny 🎈瑶</t>
+          <t>莲子</t>
         </is>
       </c>
       <c r="C238" s="0" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="G238" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:55:23</t>
+          <t>2026-09-02 09:58:56</t>
         </is>
       </c>
       <c r="H238" s="0" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="I238" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J238" s="0" t="inlineStr">
@@ -14365,11 +14365,11 @@
     </row>
     <row r="239" spans="1:14">
       <c r="A239" s="0">
-        <v>49887876</v>
+        <v>49937101</v>
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
-          <t>鱼靖儿</t>
+          <t>蓉儿</t>
         </is>
       </c>
       <c r="C239" s="0" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="G239" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:23:11</t>
+          <t>2026-09-02 09:56:16</t>
         </is>
       </c>
       <c r="H239" s="0" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I239" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J239" s="0" t="inlineStr">
@@ -14425,11 +14425,11 @@
     </row>
     <row r="240" spans="1:14">
       <c r="A240" s="0">
-        <v>49887478</v>
+        <v>49937098</v>
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
-          <t>风调雨顺</t>
+          <t>瀚林2368</t>
         </is>
       </c>
       <c r="C240" s="0" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="G240" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:10:17</t>
+          <t>2026-09-02 09:56:15</t>
         </is>
       </c>
       <c r="H240" s="0" t="inlineStr">
@@ -14485,11 +14485,11 @@
     </row>
     <row r="241" spans="1:14">
       <c r="A241" s="0">
-        <v>49887447</v>
+        <v>49937081</v>
       </c>
       <c r="B241" s="0" t="inlineStr">
         <is>
-          <t>中国艺人</t>
+          <t>🔱 花中之美</t>
         </is>
       </c>
       <c r="C241" s="0" t="inlineStr">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="G241" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:08:44</t>
+          <t>2026-09-02 09:55:47</t>
         </is>
       </c>
       <c r="H241" s="0" t="inlineStr">
@@ -14545,11 +14545,11 @@
     </row>
     <row r="242" spans="1:14">
       <c r="A242" s="0">
-        <v>49887439</v>
+        <v>49937066</v>
       </c>
       <c r="B242" s="0" t="inlineStr">
         <is>
-          <t>黄晓玲</t>
+          <t>雨情</t>
         </is>
       </c>
       <c r="C242" s="0" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G242" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:08:17</t>
+          <t>2026-09-02 09:55:27</t>
         </is>
       </c>
       <c r="H242" s="0" t="inlineStr">
@@ -14605,11 +14605,11 @@
     </row>
     <row r="243" spans="1:14">
       <c r="A243" s="0">
-        <v>49887437</v>
+        <v>49937061</v>
       </c>
       <c r="B243" s="0" t="inlineStr">
         <is>
-          <t>随缘</t>
+          <t>Sunny 🎈瑶</t>
         </is>
       </c>
       <c r="C243" s="0" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="G243" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:08:07</t>
+          <t>2026-09-02 09:55:23</t>
         </is>
       </c>
       <c r="H243" s="0" t="inlineStr">
@@ -14665,11 +14665,11 @@
     </row>
     <row r="244" spans="1:14">
       <c r="A244" s="0">
-        <v>49887416</v>
+        <v>49887876</v>
       </c>
       <c r="B244" s="0" t="inlineStr">
         <is>
-          <t>刘秋红</t>
+          <t>鱼靖儿</t>
         </is>
       </c>
       <c r="C244" s="0" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="G244" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:07:31</t>
+          <t>2026-08-31 23:23:11</t>
         </is>
       </c>
       <c r="H244" s="0" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="I244" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J244" s="0" t="inlineStr">
@@ -14725,11 +14725,11 @@
     </row>
     <row r="245" spans="1:14">
       <c r="A245" s="0">
-        <v>49887403</v>
+        <v>49887478</v>
       </c>
       <c r="B245" s="0" t="inlineStr">
         <is>
-          <t>Mr.</t>
+          <t>风调雨顺</t>
         </is>
       </c>
       <c r="C245" s="0" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="G245" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:07:05</t>
+          <t>2026-08-31 23:10:17</t>
         </is>
       </c>
       <c r="H245" s="0" t="inlineStr">
@@ -14785,11 +14785,11 @@
     </row>
     <row r="246" spans="1:14">
       <c r="A246" s="0">
-        <v>49887401</v>
+        <v>49887447</v>
       </c>
       <c r="B246" s="0" t="inlineStr">
         <is>
-          <t>万事如意</t>
+          <t>中国艺人</t>
         </is>
       </c>
       <c r="C246" s="0" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="G246" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:07:03</t>
+          <t>2026-08-31 23:08:44</t>
         </is>
       </c>
       <c r="H246" s="0" t="inlineStr">
@@ -14845,11 +14845,11 @@
     </row>
     <row r="247" spans="1:14">
       <c r="A247" s="0">
-        <v>49887400</v>
+        <v>49887439</v>
       </c>
       <c r="B247" s="0" t="inlineStr">
         <is>
-          <t>💋诺墨</t>
+          <t>黄晓玲</t>
         </is>
       </c>
       <c r="C247" s="0" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="G247" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:07:01</t>
+          <t>2026-08-31 23:08:17</t>
         </is>
       </c>
       <c r="H247" s="0" t="inlineStr">
@@ -14905,11 +14905,11 @@
     </row>
     <row r="248" spans="1:14">
       <c r="A248" s="0">
-        <v>49887399</v>
+        <v>49887437</v>
       </c>
       <c r="B248" s="0" t="inlineStr">
         <is>
-          <t>听风</t>
+          <t>随缘</t>
         </is>
       </c>
       <c r="C248" s="0" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="G248" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:06:59</t>
+          <t>2026-08-31 23:08:07</t>
         </is>
       </c>
       <c r="H248" s="0" t="inlineStr">
@@ -14965,11 +14965,11 @@
     </row>
     <row r="249" spans="1:14">
       <c r="A249" s="0">
-        <v>49845584</v>
+        <v>49887416</v>
       </c>
       <c r="B249" s="0" t="inlineStr">
         <is>
-          <t>彭汉平13024282926</t>
+          <t>刘秋红</t>
         </is>
       </c>
       <c r="C249" s="0" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="G249" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:18:55</t>
+          <t>2026-08-31 23:07:31</t>
         </is>
       </c>
       <c r="H249" s="0" t="inlineStr">
@@ -15025,11 +15025,11 @@
     </row>
     <row r="250" spans="1:14">
       <c r="A250" s="0">
-        <v>49845487</v>
+        <v>49887403</v>
       </c>
       <c r="B250" s="0" t="inlineStr">
         <is>
-          <t>Z国华</t>
+          <t>Mr.</t>
         </is>
       </c>
       <c r="C250" s="0" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="G250" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:15:49</t>
+          <t>2026-08-31 23:07:05</t>
         </is>
       </c>
       <c r="H250" s="0" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="I250" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J250" s="0" t="inlineStr">
@@ -15085,11 +15085,11 @@
     </row>
     <row r="251" spans="1:14">
       <c r="A251" s="0">
-        <v>49845407</v>
+        <v>49887401</v>
       </c>
       <c r="B251" s="0" t="inlineStr">
         <is>
-          <t>月亮🌛</t>
+          <t>万事如意</t>
         </is>
       </c>
       <c r="C251" s="0" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="G251" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:12:33</t>
+          <t>2026-08-31 23:07:03</t>
         </is>
       </c>
       <c r="H251" s="0" t="inlineStr">
@@ -15145,11 +15145,11 @@
     </row>
     <row r="252" spans="1:14">
       <c r="A252" s="0">
-        <v>49845398</v>
+        <v>49887400</v>
       </c>
       <c r="B252" s="0" t="inlineStr">
         <is>
-          <t>老树</t>
+          <t>💋诺墨</t>
         </is>
       </c>
       <c r="C252" s="0" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="G252" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:12:03</t>
+          <t>2026-08-31 23:07:01</t>
         </is>
       </c>
       <c r="H252" s="0" t="inlineStr">
@@ -15205,11 +15205,11 @@
     </row>
     <row r="253" spans="1:14">
       <c r="A253" s="0">
-        <v>49845391</v>
+        <v>49887399</v>
       </c>
       <c r="B253" s="0" t="inlineStr">
         <is>
-          <t>八哥</t>
+          <t>听风</t>
         </is>
       </c>
       <c r="C253" s="0" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="G253" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:11:45</t>
+          <t>2026-08-31 23:06:59</t>
         </is>
       </c>
       <c r="H253" s="0" t="inlineStr">
@@ -15265,11 +15265,11 @@
     </row>
     <row r="254" spans="1:14">
       <c r="A254" s="0">
-        <v>49845380</v>
+        <v>49845584</v>
       </c>
       <c r="B254" s="0" t="inlineStr">
         <is>
-          <t>铲车主出租15352562068</t>
+          <t>彭汉平13024282926</t>
         </is>
       </c>
       <c r="C254" s="0" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="G254" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:11:29</t>
+          <t>2026-08-30 23:18:55</t>
         </is>
       </c>
       <c r="H254" s="0" t="inlineStr">
@@ -15325,11 +15325,11 @@
     </row>
     <row r="255" spans="1:14">
       <c r="A255" s="0">
-        <v>49845376</v>
+        <v>49845487</v>
       </c>
       <c r="B255" s="0" t="inlineStr">
         <is>
-          <t>刘萍</t>
+          <t>Z国华</t>
         </is>
       </c>
       <c r="C255" s="0" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G255" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:11:15</t>
+          <t>2026-08-30 23:15:49</t>
         </is>
       </c>
       <c r="H255" s="0" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="I255" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J255" s="0" t="inlineStr">
@@ -15385,11 +15385,11 @@
     </row>
     <row r="256" spans="1:14">
       <c r="A256" s="0">
-        <v>49845374</v>
+        <v>49845407</v>
       </c>
       <c r="B256" s="0" t="inlineStr">
         <is>
-          <t>空谷幽兰</t>
+          <t>月亮🌛</t>
         </is>
       </c>
       <c r="C256" s="0" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="G256" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:11:07</t>
+          <t>2026-08-30 23:12:33</t>
         </is>
       </c>
       <c r="H256" s="0" t="inlineStr">
@@ -15445,11 +15445,11 @@
     </row>
     <row r="257" spans="1:14">
       <c r="A257" s="0">
-        <v>49845373</v>
+        <v>49845398</v>
       </c>
       <c r="B257" s="0" t="inlineStr">
         <is>
-          <t>泽浩羊</t>
+          <t>老树</t>
         </is>
       </c>
       <c r="C257" s="0" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="G257" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:11:05</t>
+          <t>2026-08-30 23:12:03</t>
         </is>
       </c>
       <c r="H257" s="0" t="inlineStr">
@@ -15505,11 +15505,11 @@
     </row>
     <row r="258" spans="1:14">
       <c r="A258" s="0">
-        <v>49845367</v>
+        <v>49845391</v>
       </c>
       <c r="B258" s="0" t="inlineStr">
         <is>
-          <t>峰回路转</t>
+          <t>八哥</t>
         </is>
       </c>
       <c r="C258" s="0" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="G258" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:10:55</t>
+          <t>2026-08-30 23:11:45</t>
         </is>
       </c>
       <c r="H258" s="0" t="inlineStr">
@@ -15565,11 +15565,11 @@
     </row>
     <row r="259" spans="1:14">
       <c r="A259" s="0">
-        <v>49845366</v>
+        <v>49845380</v>
       </c>
       <c r="B259" s="0" t="inlineStr">
         <is>
-          <t>超儿</t>
+          <t>铲车主出租15352562068</t>
         </is>
       </c>
       <c r="C259" s="0" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="G259" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:10:51</t>
+          <t>2026-08-30 23:11:29</t>
         </is>
       </c>
       <c r="H259" s="0" t="inlineStr">
@@ -15625,11 +15625,11 @@
     </row>
     <row r="260" spans="1:14">
       <c r="A260" s="0">
-        <v>49845365</v>
+        <v>49845376</v>
       </c>
       <c r="B260" s="0" t="inlineStr">
         <is>
-          <t>传</t>
+          <t>刘萍</t>
         </is>
       </c>
       <c r="C260" s="0" t="inlineStr">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="G260" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:10:49</t>
+          <t>2026-08-30 23:11:15</t>
         </is>
       </c>
       <c r="H260" s="0" t="inlineStr">
@@ -15685,11 +15685,11 @@
     </row>
     <row r="261" spans="1:14">
       <c r="A261" s="0">
-        <v>49845360</v>
+        <v>49845374</v>
       </c>
       <c r="B261" s="0" t="inlineStr">
         <is>
-          <t>悟歌</t>
+          <t>空谷幽兰</t>
         </is>
       </c>
       <c r="C261" s="0" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="G261" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:10:43</t>
+          <t>2026-08-30 23:11:07</t>
         </is>
       </c>
       <c r="H261" s="0" t="inlineStr">
@@ -15745,11 +15745,11 @@
     </row>
     <row r="262" spans="1:14">
       <c r="A262" s="0">
-        <v>49845342</v>
+        <v>49845373</v>
       </c>
       <c r="B262" s="0" t="inlineStr">
         <is>
-          <t>丽丽</t>
+          <t>泽浩羊</t>
         </is>
       </c>
       <c r="C262" s="0" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="G262" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:10:15</t>
+          <t>2026-08-30 23:11:05</t>
         </is>
       </c>
       <c r="H262" s="0" t="inlineStr">
@@ -15805,11 +15805,11 @@
     </row>
     <row r="263" spans="1:14">
       <c r="A263" s="0">
-        <v>49826011</v>
+        <v>49845367</v>
       </c>
       <c r="B263" s="0" t="inlineStr">
         <is>
-          <t>王前卫</t>
+          <t>峰回路转</t>
         </is>
       </c>
       <c r="C263" s="0" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="G263" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:57:27</t>
+          <t>2026-08-30 23:10:55</t>
         </is>
       </c>
       <c r="H263" s="0" t="inlineStr">
@@ -15865,11 +15865,11 @@
     </row>
     <row r="264" spans="1:14">
       <c r="A264" s="0">
-        <v>49825720</v>
+        <v>49845366</v>
       </c>
       <c r="B264" s="0" t="inlineStr">
         <is>
-          <t>老A</t>
+          <t>超儿</t>
         </is>
       </c>
       <c r="C264" s="0" t="inlineStr">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="G264" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:46:02</t>
+          <t>2026-08-30 23:10:51</t>
         </is>
       </c>
       <c r="H264" s="0" t="inlineStr">
@@ -15925,11 +15925,11 @@
     </row>
     <row r="265" spans="1:14">
       <c r="A265" s="0">
-        <v>49825676</v>
+        <v>49845365</v>
       </c>
       <c r="B265" s="0" t="inlineStr">
         <is>
-          <t>蓝天</t>
+          <t>传</t>
         </is>
       </c>
       <c r="C265" s="0" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="G265" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:44:05</t>
+          <t>2026-08-30 23:10:49</t>
         </is>
       </c>
       <c r="H265" s="0" t="inlineStr">
@@ -15985,11 +15985,11 @@
     </row>
     <row r="266" spans="1:14">
       <c r="A266" s="0">
-        <v>49825650</v>
+        <v>49845360</v>
       </c>
       <c r="B266" s="0" t="inlineStr">
         <is>
-          <t>爱芳</t>
+          <t>悟歌</t>
         </is>
       </c>
       <c r="C266" s="0" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="G266" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:43:11</t>
+          <t>2026-08-30 23:10:43</t>
         </is>
       </c>
       <c r="H266" s="0" t="inlineStr">
@@ -16045,11 +16045,11 @@
     </row>
     <row r="267" spans="1:14">
       <c r="A267" s="0">
-        <v>49825642</v>
+        <v>49845342</v>
       </c>
       <c r="B267" s="0" t="inlineStr">
         <is>
-          <t>银杏树</t>
+          <t>丽丽</t>
         </is>
       </c>
       <c r="C267" s="0" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G267" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:55</t>
+          <t>2026-08-30 23:10:15</t>
         </is>
       </c>
       <c r="H267" s="0" t="inlineStr">
@@ -16105,11 +16105,11 @@
     </row>
     <row r="268" spans="1:14">
       <c r="A268" s="0">
-        <v>49825640</v>
+        <v>49826011</v>
       </c>
       <c r="B268" s="0" t="inlineStr">
         <is>
-          <t>遵命有福（杨凤）</t>
+          <t>王前卫</t>
         </is>
       </c>
       <c r="C268" s="0" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="G268" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:49</t>
+          <t>2026-08-30 12:57:27</t>
         </is>
       </c>
       <c r="H268" s="0" t="inlineStr">
@@ -16165,11 +16165,11 @@
     </row>
     <row r="269" spans="1:14">
       <c r="A269" s="0">
-        <v>49825639</v>
+        <v>49825720</v>
       </c>
       <c r="B269" s="0" t="inlineStr">
         <is>
-          <t>申华</t>
+          <t>老A</t>
         </is>
       </c>
       <c r="C269" s="0" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="G269" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:49</t>
+          <t>2026-08-30 12:46:02</t>
         </is>
       </c>
       <c r="H269" s="0" t="inlineStr">
@@ -16225,11 +16225,11 @@
     </row>
     <row r="270" spans="1:14">
       <c r="A270" s="0">
-        <v>49825637</v>
+        <v>49825676</v>
       </c>
       <c r="B270" s="0" t="inlineStr">
         <is>
-          <t>陈月焓</t>
+          <t>蓝天</t>
         </is>
       </c>
       <c r="C270" s="0" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="G270" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:47</t>
+          <t>2026-08-30 12:44:05</t>
         </is>
       </c>
       <c r="H270" s="0" t="inlineStr">
@@ -16285,11 +16285,11 @@
     </row>
     <row r="271" spans="1:14">
       <c r="A271" s="0">
-        <v>49825635</v>
+        <v>49825650</v>
       </c>
       <c r="B271" s="0" t="inlineStr">
         <is>
-          <t>小镇生活&amp;&amp;杜震</t>
+          <t>爱芳</t>
         </is>
       </c>
       <c r="C271" s="0" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="G271" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:43</t>
+          <t>2026-08-30 12:43:11</t>
         </is>
       </c>
       <c r="H271" s="0" t="inlineStr">
@@ -16345,11 +16345,11 @@
     </row>
     <row r="272" spans="1:14">
       <c r="A272" s="0">
-        <v>49825628</v>
+        <v>49825642</v>
       </c>
       <c r="B272" s="0" t="inlineStr">
         <is>
-          <t>Taᴗaoᥫᩣ</t>
+          <t>银杏树</t>
         </is>
       </c>
       <c r="C272" s="0" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="G272" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:35</t>
+          <t>2026-08-30 12:42:55</t>
         </is>
       </c>
       <c r="H272" s="0" t="inlineStr">
@@ -16405,11 +16405,11 @@
     </row>
     <row r="273" spans="1:14">
       <c r="A273" s="0">
-        <v>49782066</v>
+        <v>49825640</v>
       </c>
       <c r="B273" s="0" t="inlineStr">
         <is>
-          <t>前程似锦</t>
+          <t>遵命有福（杨凤）</t>
         </is>
       </c>
       <c r="C273" s="0" t="inlineStr">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="G273" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 09:07:29</t>
+          <t>2026-08-30 12:42:49</t>
         </is>
       </c>
       <c r="H273" s="0" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="I273" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J273" s="0" t="inlineStr">
@@ -16465,11 +16465,11 @@
     </row>
     <row r="274" spans="1:14">
       <c r="A274" s="0">
-        <v>49771027</v>
+        <v>49825639</v>
       </c>
       <c r="B274" s="0" t="inlineStr">
         <is>
-          <t>非比</t>
+          <t>申华</t>
         </is>
       </c>
       <c r="C274" s="0" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="G274" s="0" t="inlineStr">
         <is>
-          <t>2026-08-28 23:30:09</t>
+          <t>2026-08-30 12:42:49</t>
         </is>
       </c>
       <c r="H274" s="0" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="I274" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J274" s="0" t="inlineStr">
@@ -16525,11 +16525,11 @@
     </row>
     <row r="275" spans="1:14">
       <c r="A275" s="0">
-        <v>49673360</v>
+        <v>49825637</v>
       </c>
       <c r="B275" s="0" t="inlineStr">
         <is>
-          <t>德行天下</t>
+          <t>陈月焓</t>
         </is>
       </c>
       <c r="C275" s="0" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="G275" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26 12:19:03</t>
+          <t>2026-08-30 12:42:47</t>
         </is>
       </c>
       <c r="H275" s="0" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="I275" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J275" s="0" t="inlineStr">
@@ -16585,11 +16585,11 @@
     </row>
     <row r="276" spans="1:14">
       <c r="A276" s="0">
-        <v>49673352</v>
+        <v>49825635</v>
       </c>
       <c r="B276" s="0" t="inlineStr">
         <is>
-          <t>余盛将至2026</t>
+          <t>小镇生活&amp;&amp;杜震</t>
         </is>
       </c>
       <c r="C276" s="0" t="inlineStr">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="G276" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26 12:18:49</t>
+          <t>2026-08-30 12:42:43</t>
         </is>
       </c>
       <c r="H276" s="0" t="inlineStr">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="I276" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J276" s="0" t="inlineStr">
@@ -16645,11 +16645,11 @@
     </row>
     <row r="277" spans="1:14">
       <c r="A277" s="0">
-        <v>49673350</v>
+        <v>49825628</v>
       </c>
       <c r="B277" s="0" t="inlineStr">
         <is>
-          <t>山居客</t>
+          <t>Taᴗaoᥫᩣ</t>
         </is>
       </c>
       <c r="C277" s="0" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="G277" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26 12:18:47</t>
+          <t>2026-08-30 12:42:35</t>
         </is>
       </c>
       <c r="H277" s="0" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="I277" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J277" s="0" t="inlineStr">
@@ -16705,11 +16705,11 @@
     </row>
     <row r="278" spans="1:14">
       <c r="A278" s="0">
-        <v>49673349</v>
+        <v>49782066</v>
       </c>
       <c r="B278" s="0" t="inlineStr">
         <is>
-          <t>白云</t>
+          <t>前程似锦</t>
         </is>
       </c>
       <c r="C278" s="0" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="G278" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26 12:18:45</t>
+          <t>2026-08-29 09:07:29</t>
         </is>
       </c>
       <c r="H278" s="0" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="I278" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J278" s="0" t="inlineStr">
@@ -16765,11 +16765,11 @@
     </row>
     <row r="279" spans="1:14">
       <c r="A279" s="0">
-        <v>49646935</v>
+        <v>49771027</v>
       </c>
       <c r="B279" s="0" t="inlineStr">
         <is>
-          <t>马跃荣</t>
+          <t>非比</t>
         </is>
       </c>
       <c r="C279" s="0" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="G279" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 18:15:59</t>
+          <t>2026-08-28 23:30:09</t>
         </is>
       </c>
       <c r="H279" s="0" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="I279" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J279" s="0" t="inlineStr">
@@ -16825,11 +16825,11 @@
     </row>
     <row r="280" spans="1:14">
       <c r="A280" s="0">
-        <v>49646933</v>
+        <v>49673360</v>
       </c>
       <c r="B280" s="0" t="inlineStr">
         <is>
-          <t>@吴</t>
+          <t>德行天下</t>
         </is>
       </c>
       <c r="C280" s="0" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="G280" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 18:15:56</t>
+          <t>2026-08-26 12:19:03</t>
         </is>
       </c>
       <c r="H280" s="0" t="inlineStr">
@@ -16885,11 +16885,11 @@
     </row>
     <row r="281" spans="1:14">
       <c r="A281" s="0">
-        <v>49646901</v>
+        <v>49673352</v>
       </c>
       <c r="B281" s="0" t="inlineStr">
         <is>
-          <t>龙安：富华／</t>
+          <t>余盛将至2026</t>
         </is>
       </c>
       <c r="C281" s="0" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="G281" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 18:14:28</t>
+          <t>2026-08-26 12:18:49</t>
         </is>
       </c>
       <c r="H281" s="0" t="inlineStr">
@@ -16945,11 +16945,11 @@
     </row>
     <row r="282" spans="1:14">
       <c r="A282" s="0">
-        <v>49646876</v>
+        <v>49673350</v>
       </c>
       <c r="B282" s="0" t="inlineStr">
         <is>
-          <t>冬日暖阳🌻</t>
+          <t>山居客</t>
         </is>
       </c>
       <c r="C282" s="0" t="inlineStr">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="G282" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 18:13:37</t>
+          <t>2026-08-26 12:18:47</t>
         </is>
       </c>
       <c r="H282" s="0" t="inlineStr">
@@ -17005,11 +17005,11 @@
     </row>
     <row r="283" spans="1:14">
       <c r="A283" s="0">
-        <v>49646867</v>
+        <v>49673349</v>
       </c>
       <c r="B283" s="0" t="inlineStr">
         <is>
-          <t>寒雨</t>
+          <t>白云</t>
         </is>
       </c>
       <c r="C283" s="0" t="inlineStr">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="G283" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 18:13:15</t>
+          <t>2026-08-26 12:18:45</t>
         </is>
       </c>
       <c r="H283" s="0" t="inlineStr">
@@ -17065,11 +17065,11 @@
     </row>
     <row r="284" spans="1:14">
       <c r="A284" s="0">
-        <v>49636232</v>
+        <v>49646935</v>
       </c>
       <c r="B284" s="0" t="inlineStr">
         <is>
-          <t>平安</t>
+          <t>马跃荣</t>
         </is>
       </c>
       <c r="C284" s="0" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="G284" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 13:20:15</t>
+          <t>2026-08-25 18:15:59</t>
         </is>
       </c>
       <c r="H284" s="0" t="inlineStr">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="I284" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J284" s="0" t="inlineStr">
@@ -17125,11 +17125,11 @@
     </row>
     <row r="285" spans="1:14">
       <c r="A285" s="0">
-        <v>49636184</v>
+        <v>49646933</v>
       </c>
       <c r="B285" s="0" t="inlineStr">
         <is>
-          <t>古道西风</t>
+          <t>@吴</t>
         </is>
       </c>
       <c r="C285" s="0" t="inlineStr">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="G285" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 13:18:55</t>
+          <t>2026-08-25 18:15:56</t>
         </is>
       </c>
       <c r="H285" s="0" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="I285" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J285" s="0" t="inlineStr">
@@ -17185,11 +17185,11 @@
     </row>
     <row r="286" spans="1:14">
       <c r="A286" s="0">
-        <v>49636170</v>
+        <v>49646901</v>
       </c>
       <c r="B286" s="0" t="inlineStr">
         <is>
-          <t>周海龙</t>
+          <t>龙安：富华／</t>
         </is>
       </c>
       <c r="C286" s="0" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="G286" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 13:18:33</t>
+          <t>2026-08-25 18:14:28</t>
         </is>
       </c>
       <c r="H286" s="0" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="I286" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J286" s="0" t="inlineStr">
@@ -17245,11 +17245,11 @@
     </row>
     <row r="287" spans="1:14">
       <c r="A287" s="0">
-        <v>49636157</v>
+        <v>49646876</v>
       </c>
       <c r="B287" s="0" t="inlineStr">
         <is>
-          <t>锦妍</t>
+          <t>冬日暖阳🌻</t>
         </is>
       </c>
       <c r="C287" s="0" t="inlineStr">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="G287" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 13:18:07</t>
+          <t>2026-08-25 18:13:37</t>
         </is>
       </c>
       <c r="H287" s="0" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="I287" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J287" s="0" t="inlineStr">
@@ -17305,11 +17305,11 @@
     </row>
     <row r="288" spans="1:14">
       <c r="A288" s="0">
-        <v>49593974</v>
+        <v>49646867</v>
       </c>
       <c r="B288" s="0" t="inlineStr">
         <is>
-          <t>兰兰</t>
+          <t>寒雨</t>
         </is>
       </c>
       <c r="C288" s="0" t="inlineStr">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="G288" s="0" t="inlineStr">
         <is>
-          <t>2026-08-24 12:59:53</t>
+          <t>2026-08-25 18:13:15</t>
         </is>
       </c>
       <c r="H288" s="0" t="inlineStr">
@@ -17344,7 +17344,7 @@
       </c>
       <c r="I288" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J288" s="0" t="inlineStr">
@@ -17365,11 +17365,11 @@
     </row>
     <row r="289" spans="1:14">
       <c r="A289" s="0">
-        <v>49593671</v>
+        <v>49636232</v>
       </c>
       <c r="B289" s="0" t="inlineStr">
         <is>
-          <t>准备1号</t>
+          <t>平安</t>
         </is>
       </c>
       <c r="C289" s="0" t="inlineStr">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="G289" s="0" t="inlineStr">
         <is>
-          <t>2026-08-24 12:49:27</t>
+          <t>2026-08-25 13:20:15</t>
         </is>
       </c>
       <c r="H289" s="0" t="inlineStr">
@@ -17425,11 +17425,11 @@
     </row>
     <row r="290" spans="1:14">
       <c r="A290" s="0">
-        <v>49535916</v>
+        <v>49636184</v>
       </c>
       <c r="B290" s="0" t="inlineStr">
         <is>
-          <t>真诚</t>
+          <t>古道西风</t>
         </is>
       </c>
       <c r="C290" s="0" t="inlineStr">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="G290" s="0" t="inlineStr">
         <is>
-          <t>2026-08-22 23:46:23</t>
+          <t>2026-08-25 13:18:55</t>
         </is>
       </c>
       <c r="H290" s="0" t="inlineStr">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="I290" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J290" s="0" t="inlineStr">
@@ -17485,11 +17485,11 @@
     </row>
     <row r="291" spans="1:14">
       <c r="A291" s="0">
-        <v>49535653</v>
+        <v>49636170</v>
       </c>
       <c r="B291" s="0" t="inlineStr">
         <is>
-          <t>如意家电13368134456维修</t>
+          <t>周海龙</t>
         </is>
       </c>
       <c r="C291" s="0" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="G291" s="0" t="inlineStr">
         <is>
-          <t>2026-08-22 23:28:25</t>
+          <t>2026-08-25 13:18:33</t>
         </is>
       </c>
       <c r="H291" s="0" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="I291" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J291" s="0" t="inlineStr">
@@ -17545,11 +17545,11 @@
     </row>
     <row r="292" spans="1:14">
       <c r="A292" s="0">
-        <v>49535650</v>
+        <v>49636157</v>
       </c>
       <c r="B292" s="0" t="inlineStr">
         <is>
-          <t>莺莺</t>
+          <t>锦妍</t>
         </is>
       </c>
       <c r="C292" s="0" t="inlineStr">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="G292" s="0" t="inlineStr">
         <is>
-          <t>2026-08-22 23:27:55</t>
+          <t>2026-08-25 13:18:07</t>
         </is>
       </c>
       <c r="H292" s="0" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="I292" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J292" s="0" t="inlineStr">
@@ -17600,21 +17600,16 @@
       <c r="L292" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N292" s="0" t="inlineStr">
-        <is>
-          <t>黄浦</t>
         </is>
       </c>
     </row>
     <row r="293" spans="1:14">
       <c r="A293" s="0">
-        <v>49508265</v>
+        <v>49593974</v>
       </c>
       <c r="B293" s="0" t="inlineStr">
         <is>
-          <t>爱猫🐱 咪</t>
+          <t>兰兰</t>
         </is>
       </c>
       <c r="C293" s="0" t="inlineStr">
@@ -17639,7 +17634,7 @@
       </c>
       <c r="G293" s="0" t="inlineStr">
         <is>
-          <t>2026-08-22 09:53:41</t>
+          <t>2026-08-24 12:59:53</t>
         </is>
       </c>
       <c r="H293" s="0" t="inlineStr">
@@ -17670,11 +17665,11 @@
     </row>
     <row r="294" spans="1:14">
       <c r="A294" s="0">
-        <v>49493414</v>
+        <v>49593671</v>
       </c>
       <c r="B294" s="0" t="inlineStr">
         <is>
-          <t>惠平</t>
+          <t>准备1号</t>
         </is>
       </c>
       <c r="C294" s="0" t="inlineStr">
@@ -17699,7 +17694,7 @@
       </c>
       <c r="G294" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 22:53:02</t>
+          <t>2026-08-24 12:49:27</t>
         </is>
       </c>
       <c r="H294" s="0" t="inlineStr">
@@ -17730,11 +17725,11 @@
     </row>
     <row r="295" spans="1:14">
       <c r="A295" s="0">
-        <v>49493126</v>
+        <v>49535916</v>
       </c>
       <c r="B295" s="0" t="inlineStr">
         <is>
-          <t>刘盼昭</t>
+          <t>真诚</t>
         </is>
       </c>
       <c r="C295" s="0" t="inlineStr">
@@ -17759,7 +17754,7 @@
       </c>
       <c r="G295" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 22:44:53</t>
+          <t>2026-08-22 23:46:23</t>
         </is>
       </c>
       <c r="H295" s="0" t="inlineStr">
@@ -17790,11 +17785,11 @@
     </row>
     <row r="296" spans="1:14">
       <c r="A296" s="0">
-        <v>49492499</v>
+        <v>49535653</v>
       </c>
       <c r="B296" s="0" t="inlineStr">
         <is>
-          <t>红霞</t>
+          <t>如意家电13368134456维修</t>
         </is>
       </c>
       <c r="C296" s="0" t="inlineStr">
@@ -17819,7 +17814,7 @@
       </c>
       <c r="G296" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 22:29:43</t>
+          <t>2026-08-22 23:28:25</t>
         </is>
       </c>
       <c r="H296" s="0" t="inlineStr">
@@ -17850,11 +17845,11 @@
     </row>
     <row r="297" spans="1:14">
       <c r="A297" s="0">
-        <v>49455301</v>
+        <v>49535650</v>
       </c>
       <c r="B297" s="0" t="inlineStr">
         <is>
-          <t>周开平</t>
+          <t>莺莺</t>
         </is>
       </c>
       <c r="C297" s="0" t="inlineStr">
@@ -17879,7 +17874,7 @@
       </c>
       <c r="G297" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 22:46:59</t>
+          <t>2026-08-22 23:27:55</t>
         </is>
       </c>
       <c r="H297" s="0" t="inlineStr">
@@ -17905,16 +17900,21 @@
       <c r="L297" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N297" s="0" t="inlineStr">
+        <is>
+          <t>黄浦</t>
         </is>
       </c>
     </row>
     <row r="298" spans="1:14">
       <c r="A298" s="0">
-        <v>49432023</v>
+        <v>49508265</v>
       </c>
       <c r="B298" s="0" t="inlineStr">
         <is>
-          <t>花生米</t>
+          <t>爱猫🐱 咪</t>
         </is>
       </c>
       <c r="C298" s="0" t="inlineStr">
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G298" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:45</t>
+          <t>2026-08-22 09:53:41</t>
         </is>
       </c>
       <c r="H298" s="0" t="inlineStr">
@@ -17970,11 +17970,11 @@
     </row>
     <row r="299" spans="1:14">
       <c r="A299" s="0">
-        <v>49415939</v>
+        <v>49493414</v>
       </c>
       <c r="B299" s="0" t="inlineStr">
         <is>
-          <t>杨梅芳</t>
+          <t>惠平</t>
         </is>
       </c>
       <c r="C299" s="0" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="G299" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:48:58</t>
+          <t>2026-08-21 22:53:02</t>
         </is>
       </c>
       <c r="H299" s="0" t="inlineStr">
@@ -18009,17 +18009,17 @@
       </c>
       <c r="I299" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J299" s="0" t="inlineStr">
         <is>
-          <t>安迪钢琴-多个点击报名-0元</t>
+          <t>安迪钢琴-获客助手专用</t>
         </is>
       </c>
       <c r="K299" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L299" s="0" t="inlineStr">
@@ -18030,11 +18030,11 @@
     </row>
     <row r="300" spans="1:14">
       <c r="A300" s="0">
-        <v>49415918</v>
+        <v>49493126</v>
       </c>
       <c r="B300" s="0" t="inlineStr">
         <is>
-          <t>心语无言</t>
+          <t>刘盼昭</t>
         </is>
       </c>
       <c r="C300" s="0" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="G300" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:48:24</t>
+          <t>2026-08-21 22:44:53</t>
         </is>
       </c>
       <c r="H300" s="0" t="inlineStr">
@@ -18069,17 +18069,17 @@
       </c>
       <c r="I300" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J300" s="0" t="inlineStr">
         <is>
-          <t>安迪钢琴-多个点击报名-0元</t>
+          <t>安迪钢琴-获客助手专用</t>
         </is>
       </c>
       <c r="K300" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L300" s="0" t="inlineStr">
@@ -18090,11 +18090,11 @@
     </row>
     <row r="301" spans="1:14">
       <c r="A301" s="0">
-        <v>49415913</v>
+        <v>49492499</v>
       </c>
       <c r="B301" s="0" t="inlineStr">
         <is>
-          <t>安好</t>
+          <t>红霞</t>
         </is>
       </c>
       <c r="C301" s="0" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="G301" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:48:18</t>
+          <t>2026-08-21 22:29:43</t>
         </is>
       </c>
       <c r="H301" s="0" t="inlineStr">
@@ -18129,17 +18129,17 @@
       </c>
       <c r="I301" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J301" s="0" t="inlineStr">
         <is>
-          <t>安迪钢琴-多个点击报名-0元</t>
+          <t>安迪钢琴-获客助手专用</t>
         </is>
       </c>
       <c r="K301" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L301" s="0" t="inlineStr">
@@ -18150,11 +18150,11 @@
     </row>
     <row r="302" spans="1:14">
       <c r="A302" s="0">
-        <v>49415890</v>
+        <v>49455301</v>
       </c>
       <c r="B302" s="0" t="inlineStr">
         <is>
-          <t>雨夜聆风</t>
+          <t>周开平</t>
         </is>
       </c>
       <c r="C302" s="0" t="inlineStr">
@@ -18179,7 +18179,7 @@
       </c>
       <c r="G302" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:47:56</t>
+          <t>2026-08-20 22:46:59</t>
         </is>
       </c>
       <c r="H302" s="0" t="inlineStr">
@@ -18189,37 +18189,32 @@
       </c>
       <c r="I302" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J302" s="0" t="inlineStr">
         <is>
-          <t>安迪钢琴-多个点击报名-0元</t>
+          <t>安迪钢琴-获客助手专用</t>
         </is>
       </c>
       <c r="K302" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L302" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N302" s="0" t="inlineStr">
-        <is>
-          <t>宜春</t>
         </is>
       </c>
     </row>
     <row r="303" spans="1:14">
       <c r="A303" s="0">
-        <v>49415874</v>
+        <v>49432023</v>
       </c>
       <c r="B303" s="0" t="inlineStr">
         <is>
-          <t>飘</t>
+          <t>花生米</t>
         </is>
       </c>
       <c r="C303" s="0" t="inlineStr">
@@ -18244,7 +18239,7 @@
       </c>
       <c r="G303" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:47:40</t>
+          <t>2026-08-20 11:55:45</t>
         </is>
       </c>
       <c r="H303" s="0" t="inlineStr">
@@ -18254,17 +18249,17 @@
       </c>
       <c r="I303" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J303" s="0" t="inlineStr">
         <is>
-          <t>安迪钢琴-多个点击报名-0元</t>
+          <t>安迪钢琴-获客助手专用</t>
         </is>
       </c>
       <c r="K303" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L303" s="0" t="inlineStr">
@@ -18275,11 +18270,11 @@
     </row>
     <row r="304" spans="1:14">
       <c r="A304" s="0">
-        <v>49415871</v>
+        <v>49415939</v>
       </c>
       <c r="B304" s="0" t="inlineStr">
         <is>
-          <t>庆</t>
+          <t>杨梅芳</t>
         </is>
       </c>
       <c r="C304" s="0" t="inlineStr">
@@ -18304,7 +18299,7 @@
       </c>
       <c r="G304" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:47:36</t>
+          <t>2026-08-19 22:48:58</t>
         </is>
       </c>
       <c r="H304" s="0" t="inlineStr">
@@ -18335,59 +18330,364 @@
     </row>
     <row r="305" spans="1:14">
       <c r="A305" s="0">
+        <v>49415918</v>
+      </c>
+      <c r="B305" s="0" t="inlineStr">
+        <is>
+          <t>心语无言</t>
+        </is>
+      </c>
+      <c r="C305" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D305" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E305" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F305" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G305" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:48:24</t>
+        </is>
+      </c>
+      <c r="H305" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I305" s="0" t="inlineStr">
+        <is>
+          <t>黄老师-抖音01</t>
+        </is>
+      </c>
+      <c r="J305" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-多个点击报名-0元</t>
+        </is>
+      </c>
+      <c r="K305" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L305" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" spans="1:14">
+      <c r="A306" s="0">
+        <v>49415913</v>
+      </c>
+      <c r="B306" s="0" t="inlineStr">
+        <is>
+          <t>安好</t>
+        </is>
+      </c>
+      <c r="C306" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D306" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E306" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F306" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G306" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:48:18</t>
+        </is>
+      </c>
+      <c r="H306" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I306" s="0" t="inlineStr">
+        <is>
+          <t>黄老师-抖音01</t>
+        </is>
+      </c>
+      <c r="J306" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-多个点击报名-0元</t>
+        </is>
+      </c>
+      <c r="K306" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L306" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" spans="1:14">
+      <c r="A307" s="0">
+        <v>49415890</v>
+      </c>
+      <c r="B307" s="0" t="inlineStr">
+        <is>
+          <t>雨夜聆风</t>
+        </is>
+      </c>
+      <c r="C307" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D307" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E307" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F307" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G307" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:47:56</t>
+        </is>
+      </c>
+      <c r="H307" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I307" s="0" t="inlineStr">
+        <is>
+          <t>黄老师-抖音01</t>
+        </is>
+      </c>
+      <c r="J307" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-多个点击报名-0元</t>
+        </is>
+      </c>
+      <c r="K307" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L307" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="N307" s="0" t="inlineStr">
+        <is>
+          <t>宜春</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" spans="1:14">
+      <c r="A308" s="0">
+        <v>49415874</v>
+      </c>
+      <c r="B308" s="0" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="C308" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D308" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E308" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F308" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G308" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:47:40</t>
+        </is>
+      </c>
+      <c r="H308" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I308" s="0" t="inlineStr">
+        <is>
+          <t>黄老师-抖音01</t>
+        </is>
+      </c>
+      <c r="J308" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-多个点击报名-0元</t>
+        </is>
+      </c>
+      <c r="K308" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L308" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" spans="1:14">
+      <c r="A309" s="0">
+        <v>49415871</v>
+      </c>
+      <c r="B309" s="0" t="inlineStr">
+        <is>
+          <t>庆</t>
+        </is>
+      </c>
+      <c r="C309" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D309" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E309" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F309" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G309" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:47:36</t>
+        </is>
+      </c>
+      <c r="H309" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I309" s="0" t="inlineStr">
+        <is>
+          <t>黄老师-抖音01</t>
+        </is>
+      </c>
+      <c r="J309" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-多个点击报名-0元</t>
+        </is>
+      </c>
+      <c r="K309" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L309" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" spans="1:14">
+      <c r="A310" s="0">
         <v>49415867</v>
       </c>
-      <c r="B305" s="0" t="inlineStr">
+      <c r="B310" s="0" t="inlineStr">
         <is>
           <t>HYQ</t>
         </is>
       </c>
-      <c r="C305" s="0" t="inlineStr">
-        <is>
-          <t>6天0基础钢琴入门课</t>
-        </is>
-      </c>
-      <c r="D305" s="0" t="inlineStr">
-        <is>
-          <t>训练营</t>
-        </is>
-      </c>
-      <c r="E305" s="0" t="inlineStr">
-        <is>
-          <t>￥0</t>
-        </is>
-      </c>
-      <c r="F305" s="0" t="inlineStr">
-        <is>
-          <t>￥0</t>
-        </is>
-      </c>
-      <c r="G305" s="0" t="inlineStr">
+      <c r="C310" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D310" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E310" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F310" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G310" s="0" t="inlineStr">
         <is>
           <t>2026-08-19 22:47:33</t>
         </is>
       </c>
-      <c r="H305" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I305" s="0" t="inlineStr">
-        <is>
-          <t>黄老师-抖音01</t>
-        </is>
-      </c>
-      <c r="J305" s="0" t="inlineStr">
+      <c r="H310" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I310" s="0" t="inlineStr">
+        <is>
+          <t>黄老师-抖音01</t>
+        </is>
+      </c>
+      <c r="J310" s="0" t="inlineStr">
         <is>
           <t>安迪钢琴-多个点击报名-0元</t>
         </is>
       </c>
-      <c r="K305" s="0" t="inlineStr">
+      <c r="K310" s="0" t="inlineStr">
         <is>
           <t>微信支付</t>
         </is>
       </c>
-      <c r="L305" s="0" t="inlineStr">
+      <c r="L310" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>

--- a/data/exports/黄老师/dist_order_2026-09-14.xlsx
+++ b/data/exports/黄老师/dist_order_2026-09-14.xlsx
@@ -125,11 +125,11 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="0">
-        <v>50435690</v>
+        <v>50441481</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>芈月山村</t>
+          <t>🌴🏠花好月圆🌺</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -154,7 +154,7 @@
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2026-09-14 09:32:33</t>
+          <t>2026-09-14 12:27:21</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -164,7 +164,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -185,11 +185,11 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="0">
-        <v>50435590</v>
+        <v>50441417</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>偶尔</t>
+          <t>顺德口腔医院刘凤华</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -214,7 +214,7 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>2026-09-14 09:29:31</t>
+          <t>2026-09-14 12:25:31</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -224,7 +224,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -245,11 +245,11 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="0">
-        <v>50435588</v>
+        <v>50441359</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>刘住青春</t>
+          <t>沉默彼岸</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -274,7 +274,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>2026-09-14 09:29:21</t>
+          <t>2026-09-14 12:23:55</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -284,7 +284,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -305,11 +305,11 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="0">
-        <v>50435586</v>
+        <v>50435690</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>hua</t>
+          <t>芈月山村</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>2026-09-14 09:29:19</t>
+          <t>2026-09-14 09:32:33</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -344,7 +344,7 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
@@ -365,11 +365,11 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="0">
-        <v>50435585</v>
+        <v>50435590</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>茜茜</t>
+          <t>偶尔</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -394,7 +394,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>2026-09-14 09:29:17</t>
+          <t>2026-09-14 09:29:31</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -425,11 +425,11 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="0">
-        <v>50423288</v>
+        <v>50435588</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>梦</t>
+          <t>刘住青春</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:57:15</t>
+          <t>2026-09-14 09:29:21</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -485,11 +485,11 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="0">
-        <v>50423277</v>
+        <v>50435586</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>欧阳祝明</t>
+          <t>hua</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:56:23</t>
+          <t>2026-09-14 09:29:19</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -545,11 +545,11 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="0">
-        <v>50423276</v>
+        <v>50435585</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>幸福一生</t>
+          <t>茜茜</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:56:19</t>
+          <t>2026-09-14 09:29:17</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -605,11 +605,11 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="0">
-        <v>50423272</v>
+        <v>50423288</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>怡瑞《专业木工装修》装门</t>
+          <t>梦</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:56:13</t>
+          <t>2026-09-13 22:57:15</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -665,11 +665,11 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="0">
-        <v>50423262</v>
+        <v>50423277</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>黄元景，18185498848</t>
+          <t>欧阳祝明</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:47</t>
+          <t>2026-09-13 22:56:23</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -725,11 +725,11 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="0">
-        <v>50423257</v>
+        <v>50423276</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>向往神鹰</t>
+          <t>幸福一生</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:33</t>
+          <t>2026-09-13 22:56:19</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -785,11 +785,11 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="0">
-        <v>50423256</v>
+        <v>50423272</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>sunny</t>
+          <t>怡瑞《专业木工装修》装门</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:29</t>
+          <t>2026-09-13 22:56:13</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -845,11 +845,11 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="0">
-        <v>50423252</v>
+        <v>50423262</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>郑维杰568</t>
+          <t>黄元景，18185498848</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:19</t>
+          <t>2026-09-13 22:55:47</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -905,11 +905,11 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="0">
-        <v>50423251</v>
+        <v>50423257</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>博海</t>
+          <t>向往神鹰</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:19</t>
+          <t>2026-09-13 22:55:33</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -965,11 +965,11 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="0">
-        <v>50423247</v>
+        <v>50423256</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>sunny</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:15</t>
+          <t>2026-09-13 22:55:29</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -1025,11 +1025,11 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="0">
-        <v>50423246</v>
+        <v>50423252</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>巴山夜雨</t>
+          <t>郑维杰568</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:13</t>
+          <t>2026-09-13 22:55:19</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -1085,11 +1085,11 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="0">
-        <v>50423241</v>
+        <v>50423251</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>🍎禧果</t>
+          <t>博海</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 22:55:09</t>
+          <t>2026-09-13 22:55:19</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -1145,11 +1145,11 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="0">
-        <v>50413116</v>
+        <v>50423247</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>sisikaokao</t>
+          <t>雪</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 17:55:11</t>
+          <t>2026-09-13 22:55:15</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="I19" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J19" s="0" t="inlineStr">
@@ -1205,11 +1205,11 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="0">
-        <v>50413104</v>
+        <v>50423246</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>阳光灿烂</t>
+          <t>巴山夜雨</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 17:54:37</t>
+          <t>2026-09-13 22:55:13</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
@@ -1265,11 +1265,11 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="0">
-        <v>50413102</v>
+        <v>50423241</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>紫樱花🌸</t>
+          <t>🍎禧果</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 17:54:37</t>
+          <t>2026-09-13 22:55:09</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
@@ -1325,11 +1325,11 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="0">
-        <v>50405053</v>
+        <v>50413116</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>和棋，</t>
+          <t>sisikaokao</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:42:07</t>
+          <t>2026-09-13 17:55:11</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
@@ -1385,11 +1385,11 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="0">
-        <v>50405036</v>
+        <v>50413104</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>金铲铲</t>
+          <t>阳光灿烂</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:17</t>
+          <t>2026-09-13 17:54:37</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
@@ -1445,11 +1445,11 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="0">
-        <v>50405034</v>
+        <v>50413102</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>春暖花开</t>
+          <t>紫樱花🌸</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:11</t>
+          <t>2026-09-13 17:54:37</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
@@ -1505,11 +1505,11 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="0">
-        <v>50405028</v>
+        <v>50405053</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>杨生</t>
+          <t>和棋，</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:04</t>
+          <t>2026-09-13 12:42:07</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1565,11 +1565,11 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="0">
-        <v>50405026</v>
+        <v>50405036</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>乔</t>
+          <t>金铲铲</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:04</t>
+          <t>2026-09-13 12:41:17</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1625,11 +1625,11 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="0">
-        <v>50405025</v>
+        <v>50405034</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>韩寒</t>
+          <t>春暖花开</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:03</t>
+          <t>2026-09-13 12:41:11</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1685,11 +1685,11 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="0">
-        <v>50405024</v>
+        <v>50405028</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>笑春风</t>
+          <t>杨生</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:41:03</t>
+          <t>2026-09-13 12:41:04</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1740,21 +1740,16 @@
       <c r="L28" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N28" s="0" t="inlineStr">
-        <is>
-          <t>宁波</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="0">
-        <v>50404537</v>
+        <v>50405026</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>Lfz</t>
+          <t>乔</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -1779,7 +1774,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:22:51</t>
+          <t>2026-09-13 12:41:04</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -1789,7 +1784,7 @@
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
@@ -1810,11 +1805,11 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="0">
-        <v>50404504</v>
+        <v>50405025</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>年华似锦</t>
+          <t>韩寒</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -1839,7 +1834,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:21:53</t>
+          <t>2026-09-13 12:41:03</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -1849,7 +1844,7 @@
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -1870,11 +1865,11 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="0">
-        <v>50404498</v>
+        <v>50405024</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>笑春风</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -1899,7 +1894,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:21:41</t>
+          <t>2026-09-13 12:41:03</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -1909,7 +1904,7 @@
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
@@ -1925,16 +1920,21 @@
       <c r="L31" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N31" s="0" t="inlineStr">
+        <is>
+          <t>宁波</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="0">
-        <v>50404493</v>
+        <v>50404537</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>爱</t>
+          <t>Lfz</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:21:33</t>
+          <t>2026-09-13 12:22:51</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -1990,11 +1990,11 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="0">
-        <v>50404484</v>
+        <v>50404504</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>Yzzc🌟</t>
+          <t>年华似锦</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>2026-09-13 12:21:03</t>
+          <t>2026-09-13 12:21:53</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -2050,11 +2050,11 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="0">
-        <v>50387248</v>
+        <v>50404498</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>阿玉</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:55:01</t>
+          <t>2026-09-13 12:21:41</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
@@ -2110,11 +2110,11 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="0">
-        <v>50386997</v>
+        <v>50404493</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>两相情缘</t>
+          <t>爱</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:47:27</t>
+          <t>2026-09-13 12:21:33</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
@@ -2170,11 +2170,11 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="0">
-        <v>50386996</v>
+        <v>50404484</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>雅阁布（国强）</t>
+          <t>Yzzc🌟</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:47:21</t>
+          <t>2026-09-13 12:21:03</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
@@ -2230,11 +2230,11 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="0">
-        <v>50386972</v>
+        <v>50387248</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>蓝海</t>
+          <t>阿玉</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:46:43</t>
+          <t>2026-09-12 22:55:01</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
@@ -2290,11 +2290,11 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="0">
-        <v>50386970</v>
+        <v>50386997</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>快乐每一天</t>
+          <t>两相情缘</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:46:39</t>
+          <t>2026-09-12 22:47:27</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
@@ -2350,11 +2350,11 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="0">
-        <v>50386939</v>
+        <v>50386996</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>雅阁布（国强）</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:43</t>
+          <t>2026-09-12 22:47:21</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -2410,11 +2410,11 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="0">
-        <v>50386937</v>
+        <v>50386972</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>A余文</t>
+          <t>蓝海</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:39</t>
+          <t>2026-09-12 22:46:43</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
@@ -2470,11 +2470,11 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="0">
-        <v>50386935</v>
+        <v>50386970</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>杨捏捏</t>
+          <t>快乐每一天</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:37</t>
+          <t>2026-09-12 22:46:39</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J41" s="0" t="inlineStr">
@@ -2530,11 +2530,11 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="0">
-        <v>50386934</v>
+        <v>50386939</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>聪呱呱</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:37</t>
+          <t>2026-09-12 22:45:43</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -2590,11 +2590,11 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="0">
-        <v>50386933</v>
+        <v>50386937</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>雪花🌸</t>
+          <t>A余文</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:37</t>
+          <t>2026-09-12 22:45:39</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
@@ -2650,11 +2650,11 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="0">
-        <v>50386932</v>
+        <v>50386935</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>刘月军</t>
+          <t>杨捏捏</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:35</t>
+          <t>2026-09-12 22:45:37</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
@@ -2710,11 +2710,11 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="0">
-        <v>50386930</v>
+        <v>50386934</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>Number Life</t>
+          <t>聪呱呱</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:35</t>
+          <t>2026-09-12 22:45:37</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
@@ -2770,11 +2770,11 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="0">
-        <v>50386929</v>
+        <v>50386933</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>刚刚好</t>
+          <t>雪花🌸</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:30</t>
+          <t>2026-09-12 22:45:37</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
@@ -2830,11 +2830,11 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="0">
-        <v>50386919</v>
+        <v>50386932</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>沙漠一滴水</t>
+          <t>刘月军</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:25</t>
+          <t>2026-09-12 22:45:35</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
@@ -2890,11 +2890,11 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="0">
-        <v>50386916</v>
+        <v>50386930</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>圆通速递王赛18521189541</t>
+          <t>Number Life</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:23</t>
+          <t>2026-09-12 22:45:35</t>
         </is>
       </c>
       <c r="H48" s="0" t="inlineStr">
@@ -2950,11 +2950,11 @@
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="0">
-        <v>50386915</v>
+        <v>50386929</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>🌸N🌸</t>
+          <t>刚刚好</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 22:45:22</t>
+          <t>2026-09-12 22:45:30</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
@@ -3010,11 +3010,11 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="0">
-        <v>50366693</v>
+        <v>50386919</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>刘普荣</t>
+          <t>沙漠一滴水</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 12:49:03</t>
+          <t>2026-09-12 22:45:25</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="I50" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J50" s="0" t="inlineStr">
@@ -3070,11 +3070,11 @@
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="0">
-        <v>50366409</v>
+        <v>50386916</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>努力面前！</t>
+          <t>圆通速递王赛18521189541</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 12:39:51</t>
+          <t>2026-09-12 22:45:23</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
@@ -3130,11 +3130,11 @@
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="0">
-        <v>50366405</v>
+        <v>50386915</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>llq</t>
+          <t>🌸N🌸</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 12:39:47</t>
+          <t>2026-09-12 22:45:22</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
@@ -3190,11 +3190,11 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="0">
-        <v>50359189</v>
+        <v>50366693</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>刘普荣</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:41:29</t>
+          <t>2026-09-12 12:49:03</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -3250,11 +3250,11 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="0">
-        <v>50359174</v>
+        <v>50366409</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>娟</t>
+          <t>努力面前！</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:41:19</t>
+          <t>2026-09-12 12:39:51</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="I54" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J54" s="0" t="inlineStr">
@@ -3310,11 +3310,11 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="0">
-        <v>50359138</v>
+        <v>50366405</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>藏酒</t>
+          <t>llq</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:40:41</t>
+          <t>2026-09-12 12:39:47</t>
         </is>
       </c>
       <c r="H55" s="0" t="inlineStr">
@@ -3370,11 +3370,11 @@
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="0">
-        <v>50359079</v>
+        <v>50359189</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>单</t>
+          <t>雪</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:39:11</t>
+          <t>2026-09-12 09:41:29</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="I56" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J56" s="0" t="inlineStr">
@@ -3430,11 +3430,11 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="0">
-        <v>50359055</v>
+        <v>50359174</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>一念花开，不负期待</t>
+          <t>娟</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:38:41</t>
+          <t>2026-09-12 09:41:19</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="I57" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J57" s="0" t="inlineStr">
@@ -3490,11 +3490,11 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="0">
-        <v>50359049</v>
+        <v>50359138</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>AAA张敏</t>
+          <t>藏酒</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:38:34</t>
+          <t>2026-09-12 09:40:41</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
@@ -3550,11 +3550,11 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="0">
-        <v>50359039</v>
+        <v>50359079</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>龙🐉哥阿凯15063798299</t>
+          <t>单</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>2026-09-12 09:38:23</t>
+          <t>2026-09-12 09:39:11</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -3610,11 +3610,11 @@
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="0">
-        <v>50326097</v>
+        <v>50359055</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>华</t>
+          <t>一念花开，不负期待</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>2026-09-11 12:32:19</t>
+          <t>2026-09-12 09:38:41</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="I60" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J60" s="0" t="inlineStr">
@@ -3670,11 +3670,11 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="0">
-        <v>50325826</v>
+        <v>50359049</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>刘爽</t>
+          <t>AAA张敏</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>2026-09-11 12:22:51</t>
+          <t>2026-09-12 09:38:34</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I61" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J61" s="0" t="inlineStr">
@@ -3730,11 +3730,11 @@
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="0">
-        <v>50325823</v>
+        <v>50359039</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>辉</t>
+          <t>龙🐉哥阿凯15063798299</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>2026-09-11 12:22:41</t>
+          <t>2026-09-12 09:38:23</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="I62" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
@@ -3790,11 +3790,11 @@
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="0">
-        <v>50325804</v>
+        <v>50326097</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>早上好  °</t>
+          <t>华</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>2026-09-11 12:22:09</t>
+          <t>2026-09-11 12:32:19</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
@@ -3850,11 +3850,11 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="0">
-        <v>50325790</v>
+        <v>50325826</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>꒰ঌ🤍໒꒱blingbling</t>
+          <t>刘爽</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>2026-09-11 12:21:49</t>
+          <t>2026-09-11 12:22:51</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
@@ -3910,11 +3910,11 @@
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="0">
-        <v>50297022</v>
+        <v>50325823</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>剑哥（大福）</t>
+          <t>辉</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>2026-09-10 17:54:27</t>
+          <t>2026-09-11 12:22:41</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
@@ -3970,11 +3970,11 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="0">
-        <v>50296929</v>
+        <v>50325804</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>Mrs Sun</t>
+          <t>早上好  °</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>2026-09-10 17:51:31</t>
+          <t>2026-09-11 12:22:09</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -4030,11 +4030,11 @@
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="0">
-        <v>50266459</v>
+        <v>50325790</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>小不点</t>
+          <t>꒰ঌ🤍໒꒱blingbling</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:22:15</t>
+          <t>2026-09-11 12:21:49</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="I67" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J67" s="0" t="inlineStr">
@@ -4090,11 +4090,11 @@
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="0">
-        <v>50266152</v>
+        <v>50297022</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>AAA蝈蝈</t>
+          <t>剑哥（大福）</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:09:54</t>
+          <t>2026-09-10 17:54:27</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="I68" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J68" s="0" t="inlineStr">
@@ -4150,11 +4150,11 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="0">
-        <v>50266129</v>
+        <v>50296929</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Mrs Sun</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:08:45</t>
+          <t>2026-09-10 17:51:31</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="I69" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J69" s="0" t="inlineStr">
@@ -4210,11 +4210,11 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="0">
-        <v>50266113</v>
+        <v>50266459</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>小不点</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:08:12</t>
+          <t>2026-09-09 23:22:15</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
@@ -4270,11 +4270,11 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="0">
-        <v>50266101</v>
+        <v>50266152</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>阿文</t>
+          <t>AAA蝈蝈</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:07:45</t>
+          <t>2026-09-09 23:09:54</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
@@ -4330,11 +4330,11 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="0">
-        <v>50266092</v>
+        <v>50266129</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>坦然人生</t>
+          <t>April</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:07:07</t>
+          <t>2026-09-09 23:08:45</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
@@ -4390,11 +4390,11 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="0">
-        <v>50266076</v>
+        <v>50266113</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>幸福生活</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:06:21</t>
+          <t>2026-09-09 23:08:12</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="I73" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J73" s="0" t="inlineStr">
@@ -4450,11 +4450,11 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="0">
-        <v>50266070</v>
+        <v>50266101</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>一帆风顺</t>
+          <t>阿文</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:06:09</t>
+          <t>2026-09-09 23:07:45</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
@@ -4510,11 +4510,11 @@
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="0">
-        <v>50266069</v>
+        <v>50266092</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>开源证券 李斌</t>
+          <t>坦然人生</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:06:05</t>
+          <t>2026-09-09 23:07:07</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
@@ -4570,11 +4570,11 @@
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="0">
-        <v>50266068</v>
+        <v>50266076</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>七彩妹</t>
+          <t>幸福生活</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 23:06:05</t>
+          <t>2026-09-09 23:06:21</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
@@ -4630,11 +4630,11 @@
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="0">
-        <v>50243460</v>
+        <v>50266070</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>小勤</t>
+          <t>一帆风顺</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:30:09</t>
+          <t>2026-09-09 23:06:09</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -4690,11 +4690,11 @@
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="0">
-        <v>50243459</v>
+        <v>50266069</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>为你守候</t>
+          <t>开源证券 李斌</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:30:09</t>
+          <t>2026-09-09 23:06:05</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -4750,11 +4750,11 @@
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="0">
-        <v>50243390</v>
+        <v>50266068</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>💦 ~雷💍🌙</t>
+          <t>七彩妹</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:28:18</t>
+          <t>2026-09-09 23:06:05</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
@@ -4810,11 +4810,11 @@
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="0">
-        <v>50243384</v>
+        <v>50243460</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>滤镜</t>
+          <t>小勤</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:28:05</t>
+          <t>2026-09-09 12:30:09</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -4870,11 +4870,11 @@
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="0">
-        <v>50243382</v>
+        <v>50243459</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>幸运常伴</t>
+          <t>为你守候</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:27:57</t>
+          <t>2026-09-09 12:30:09</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -4930,11 +4930,11 @@
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="0">
-        <v>50243378</v>
+        <v>50243390</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>Beate</t>
+          <t>💦 ~雷💍🌙</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:27:53</t>
+          <t>2026-09-09 12:28:18</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -4990,11 +4990,11 @@
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="0">
-        <v>50243377</v>
+        <v>50243384</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>心存善念，善行善念圆梦感恩一切</t>
+          <t>滤镜</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:27:51</t>
+          <t>2026-09-09 12:28:05</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="I83" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J83" s="0" t="inlineStr">
@@ -5045,21 +5045,16 @@
       <c r="L83" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N83" s="0" t="inlineStr">
-        <is>
-          <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="0">
-        <v>50243376</v>
+        <v>50243382</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>迪士尼在逃公主👑</t>
+          <t>幸运常伴</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -5084,7 +5079,7 @@
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:27:46</t>
+          <t>2026-09-09 12:27:57</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
@@ -5115,11 +5110,11 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="0">
-        <v>50243086</v>
+        <v>50243378</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>马永建</t>
+          <t>Beate</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -5144,7 +5139,7 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:18:59</t>
+          <t>2026-09-09 12:27:53</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
@@ -5154,7 +5149,7 @@
       </c>
       <c r="I85" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J85" s="0" t="inlineStr">
@@ -5175,11 +5170,11 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="0">
-        <v>50243069</v>
+        <v>50243377</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>茗香笛月</t>
+          <t>心存善念，善行善念圆梦感恩一切</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -5204,7 +5199,7 @@
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 12:18:27</t>
+          <t>2026-09-09 12:27:51</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
@@ -5214,7 +5209,7 @@
       </c>
       <c r="I86" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J86" s="0" t="inlineStr">
@@ -5230,16 +5225,21 @@
       <c r="L86" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N86" s="0" t="inlineStr">
+        <is>
+          <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="0">
-        <v>50236356</v>
+        <v>50243376</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>潮汕贤哥</t>
+          <t>迪士尼在逃公主👑</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 09:38:49</t>
+          <t>2026-09-09 12:27:46</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
@@ -5295,11 +5295,11 @@
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="0">
-        <v>50236274</v>
+        <v>50243086</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>A珍丽</t>
+          <t>马永建</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 09:35:59</t>
+          <t>2026-09-09 12:18:59</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="I88" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J88" s="0" t="inlineStr">
@@ -5355,11 +5355,11 @@
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="0">
-        <v>50236266</v>
+        <v>50243069</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>秋夜清风</t>
+          <t>茗香笛月</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>2026-09-09 09:35:39</t>
+          <t>2026-09-09 12:18:27</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="I89" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J89" s="0" t="inlineStr">
@@ -5415,11 +5415,11 @@
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="0">
-        <v>50225279</v>
+        <v>50236356</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>family-man</t>
+          <t>潮汕贤哥</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 23:19:10</t>
+          <t>2026-09-09 09:38:49</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="I90" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J90" s="0" t="inlineStr">
@@ -5475,11 +5475,11 @@
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="0">
-        <v>50225270</v>
+        <v>50236274</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>昨日伊人</t>
+          <t>A珍丽</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 23:18:01</t>
+          <t>2026-09-09 09:35:59</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
@@ -5535,11 +5535,11 @@
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="0">
-        <v>50225133</v>
+        <v>50236266</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>老孙</t>
+          <t>秋夜清风</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 23:10:58</t>
+          <t>2026-09-09 09:35:39</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
@@ -5595,11 +5595,11 @@
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="0">
-        <v>50224890</v>
+        <v>50225279</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>刘娟</t>
+          <t>family-man</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:59:17</t>
+          <t>2026-09-08 23:19:10</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="I93" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J93" s="0" t="inlineStr">
@@ -5655,11 +5655,11 @@
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="0">
-        <v>50224884</v>
+        <v>50225270</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>果盈盈</t>
+          <t>昨日伊人</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:59:07</t>
+          <t>2026-09-08 23:18:01</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -5715,11 +5715,11 @@
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="0">
-        <v>50224877</v>
+        <v>50225133</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>Mr. 庞</t>
+          <t>老孙</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:43</t>
+          <t>2026-09-08 23:10:58</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -5775,11 +5775,11 @@
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="0">
-        <v>50224876</v>
+        <v>50224890</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>最美不过遇见你</t>
+          <t>刘娟</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:43</t>
+          <t>2026-09-08 22:59:17</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -5835,11 +5835,11 @@
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="0">
-        <v>50224875</v>
+        <v>50224884</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>^o^送恩光</t>
+          <t>果盈盈</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:39</t>
+          <t>2026-09-08 22:59:07</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -5895,11 +5895,11 @@
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="0">
-        <v>50224874</v>
+        <v>50224877</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>淡墨无殇</t>
+          <t>Mr. 庞</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:37</t>
+          <t>2026-09-08 22:58:43</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
@@ -5955,11 +5955,11 @@
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="0">
-        <v>50224873</v>
+        <v>50224876</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>阳春白雪</t>
+          <t>最美不过遇见你</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:35</t>
+          <t>2026-09-08 22:58:43</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
@@ -6015,11 +6015,11 @@
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="0">
-        <v>50224868</v>
+        <v>50224875</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>从未</t>
+          <t>^o^送恩光</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:58:19</t>
+          <t>2026-09-08 22:58:39</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
@@ -6075,11 +6075,11 @@
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="0">
-        <v>50223758</v>
+        <v>50224874</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>FREESA</t>
+          <t>淡墨无殇</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 22:20:27</t>
+          <t>2026-09-08 22:58:37</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="I101" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J101" s="0" t="inlineStr">
@@ -6135,11 +6135,11 @@
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="0">
-        <v>50201671</v>
+        <v>50224873</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>黑班长</t>
+          <t>阳春白雪</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 12:20:09</t>
+          <t>2026-09-08 22:58:35</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="I102" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J102" s="0" t="inlineStr">
@@ -6195,11 +6195,11 @@
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="0">
-        <v>50201580</v>
+        <v>50224868</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>黄智勇18649168223中华老字号皮糖</t>
+          <t>从未</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 12:18:43</t>
+          <t>2026-09-08 22:58:19</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="I103" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J103" s="0" t="inlineStr">
@@ -6255,11 +6255,11 @@
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="0">
-        <v>50201564</v>
+        <v>50223758</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>小鱼儿</t>
+          <t>FREESA</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 12:18:28</t>
+          <t>2026-09-08 22:20:27</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="I104" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J104" s="0" t="inlineStr">
@@ -6315,11 +6315,11 @@
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="0">
-        <v>50201559</v>
+        <v>50201671</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>语诺</t>
+          <t>黑班长</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 12:18:17</t>
+          <t>2026-09-08 12:20:09</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -6375,11 +6375,11 @@
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="0">
-        <v>50194907</v>
+        <v>50201580</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>红情雨申</t>
+          <t>黄智勇18649168223中华老字号皮糖</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 09:26:54</t>
+          <t>2026-09-08 12:18:43</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="I106" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J106" s="0" t="inlineStr">
@@ -6435,11 +6435,11 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="0">
-        <v>50194816</v>
+        <v>50201564</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>沈新丽</t>
+          <t>小鱼儿</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 09:25:31</t>
+          <t>2026-09-08 12:18:28</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="I107" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J107" s="0" t="inlineStr">
@@ -6495,11 +6495,11 @@
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="0">
-        <v>50194810</v>
+        <v>50201559</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>活在当下、、</t>
+          <t>语诺</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 09:25:21</t>
+          <t>2026-09-08 12:18:17</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I108" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J108" s="0" t="inlineStr">
@@ -6555,11 +6555,11 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="0">
-        <v>50194790</v>
+        <v>50194907</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>Anne🦋</t>
+          <t>红情雨申</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>2026-09-08 09:24:47</t>
+          <t>2026-09-08 09:26:54</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
@@ -6615,11 +6615,11 @@
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="0">
-        <v>50169357</v>
+        <v>50194816</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>枫</t>
+          <t>沈新丽</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 18:04:20</t>
+          <t>2026-09-08 09:25:31</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="I110" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J110" s="0" t="inlineStr">
@@ -6675,11 +6675,11 @@
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="0">
-        <v>50169102</v>
+        <v>50194810</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>溫柔的我</t>
+          <t>活在当下、、</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 17:54:04</t>
+          <t>2026-09-08 09:25:21</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="I111" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J111" s="0" t="inlineStr">
@@ -6735,11 +6735,11 @@
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="0">
-        <v>50169093</v>
+        <v>50194790</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>明月</t>
+          <t>Anne🦋</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 17:53:31</t>
+          <t>2026-09-08 09:24:47</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="I112" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J112" s="0" t="inlineStr">
@@ -6795,11 +6795,11 @@
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="0">
-        <v>50169077</v>
+        <v>50169357</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>心照不宣</t>
+          <t>枫</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 17:53:03</t>
+          <t>2026-09-07 18:04:20</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
@@ -6855,11 +6855,11 @@
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="0">
-        <v>50158131</v>
+        <v>50169102</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>郭军</t>
+          <t>溫柔的我</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:44:06</t>
+          <t>2026-09-07 17:54:04</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
@@ -6915,11 +6915,11 @@
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="0">
-        <v>50158087</v>
+        <v>50169093</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>小白杨</t>
+          <t>明月</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:42:51</t>
+          <t>2026-09-07 17:53:31</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
@@ -6975,11 +6975,11 @@
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="0">
-        <v>50158049</v>
+        <v>50169077</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>心之所向，皆为美好。</t>
+          <t>心照不宣</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:41:48</t>
+          <t>2026-09-07 17:53:03</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -7035,11 +7035,11 @@
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="0">
-        <v>50158048</v>
+        <v>50158131</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>余生，请多指教</t>
+          <t>郭军</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:41:46</t>
+          <t>2026-09-07 12:44:06</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -7095,11 +7095,11 @@
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="0">
-        <v>50158047</v>
+        <v>50158087</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>刘星</t>
+          <t>小白杨</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:41:39</t>
+          <t>2026-09-07 12:42:51</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -7155,11 +7155,11 @@
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="0">
-        <v>50158044</v>
+        <v>50158049</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>赵云鹏㇏</t>
+          <t>心之所向，皆为美好。</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07 12:41:33</t>
+          <t>2026-09-07 12:41:48</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -7215,11 +7215,11 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="0">
-        <v>50140343</v>
+        <v>50158048</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>A沙宣（采购号）</t>
+          <t>余生，请多指教</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 23:14:27</t>
+          <t>2026-09-07 12:41:46</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I120" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J120" s="0" t="inlineStr">
@@ -7275,11 +7275,11 @@
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="0">
-        <v>50139986</v>
+        <v>50158047</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>雪在烧</t>
+          <t>刘星</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 23:00:51</t>
+          <t>2026-09-07 12:41:39</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="I121" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J121" s="0" t="inlineStr">
@@ -7335,11 +7335,11 @@
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="0">
-        <v>50139951</v>
+        <v>50158044</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>随遇而安</t>
+          <t>赵云鹏㇏</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:08</t>
+          <t>2026-09-07 12:41:33</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I122" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J122" s="0" t="inlineStr">
@@ -7395,11 +7395,11 @@
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="0">
-        <v>50139930</v>
+        <v>50140343</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>秋钰</t>
+          <t>A沙宣（采购号）</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:58:25</t>
+          <t>2026-09-06 23:14:27</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="I123" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J123" s="0" t="inlineStr">
@@ -7455,11 +7455,11 @@
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="0">
-        <v>50139907</v>
+        <v>50139986</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>旧时明月</t>
+          <t>雪在烧</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:57:19</t>
+          <t>2026-09-06 23:00:51</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
@@ -7515,11 +7515,11 @@
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="0">
-        <v>50139891</v>
+        <v>50139951</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>空白</t>
+          <t>随遇而安</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:56:55</t>
+          <t>2026-09-06 22:59:08</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="I125" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J125" s="0" t="inlineStr">
@@ -7575,11 +7575,11 @@
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="0">
-        <v>50139861</v>
+        <v>50139930</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>休闲快乐</t>
+          <t>秋钰</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:56:03</t>
+          <t>2026-09-06 22:58:25</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I126" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J126" s="0" t="inlineStr">
@@ -7635,11 +7635,11 @@
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="0">
-        <v>50139844</v>
+        <v>50139907</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>এ᭄悦己ꦿ᭄࿐</t>
+          <t>旧时明月</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:35</t>
+          <t>2026-09-06 22:57:19</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
@@ -7695,11 +7695,11 @@
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="0">
-        <v>50139839</v>
+        <v>50139891</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>ღ᭄冬夏尚品℘࿐</t>
+          <t>空白</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:27</t>
+          <t>2026-09-06 22:56:55</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
@@ -7755,11 +7755,11 @@
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="0">
-        <v>50139837</v>
+        <v>50139861</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>杨言武</t>
+          <t>休闲快乐</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:23</t>
+          <t>2026-09-06 22:56:03</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
@@ -7815,11 +7815,11 @@
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="0">
-        <v>50139835</v>
+        <v>50139844</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>Y.m烟花爆竹🧨🧨🧨</t>
+          <t>এ᭄悦己ꦿ᭄࿐</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:21</t>
+          <t>2026-09-06 22:55:35</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -7875,11 +7875,11 @@
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="0">
-        <v>50139832</v>
+        <v>50139839</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>太阳🌞</t>
+          <t>ღ᭄冬夏尚品℘࿐</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:17</t>
+          <t>2026-09-06 22:55:27</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -7935,11 +7935,11 @@
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="0">
-        <v>50139824</v>
+        <v>50139837</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>安安妈妈</t>
+          <t>杨言武</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:55:09</t>
+          <t>2026-09-06 22:55:23</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -7995,11 +7995,11 @@
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="0">
-        <v>50139818</v>
+        <v>50139835</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>静     ²⁰²⁶₆₆₆</t>
+          <t>Y.m烟花爆竹🧨🧨🧨</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:54:59</t>
+          <t>2026-09-06 22:55:21</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -8055,11 +8055,11 @@
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="0">
-        <v>50139814</v>
+        <v>50139832</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>曹恒美</t>
+          <t>太阳🌞</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:54:53</t>
+          <t>2026-09-06 22:55:17</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
@@ -8115,11 +8115,11 @@
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="0">
-        <v>50139813</v>
+        <v>50139824</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>lucky🍀🍀</t>
+          <t>安安妈妈</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:54:51</t>
+          <t>2026-09-06 22:55:09</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -8175,11 +8175,11 @@
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="0">
-        <v>50139794</v>
+        <v>50139818</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>静     ²⁰²⁶₆₆₆</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 22:54:31</t>
+          <t>2026-09-06 22:54:59</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -8235,11 +8235,11 @@
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="0">
-        <v>50129606</v>
+        <v>50139814</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>A1风轻云淡</t>
+          <t>曹恒美</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 17:53:57</t>
+          <t>2026-09-06 22:54:53</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I137" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J137" s="0" t="inlineStr">
@@ -8295,11 +8295,11 @@
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="0">
-        <v>50129482</v>
+        <v>50139813</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>一心有你电话号码，</t>
+          <t>lucky🍀🍀</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 17:49:45</t>
+          <t>2026-09-06 22:54:51</t>
         </is>
       </c>
       <c r="H138" s="0" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="I138" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J138" s="0" t="inlineStr">
@@ -8355,11 +8355,11 @@
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="0">
-        <v>50121359</v>
+        <v>50139794</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>amy</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:58:35</t>
+          <t>2026-09-06 22:54:31</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="I139" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J139" s="0" t="inlineStr">
@@ -8415,11 +8415,11 @@
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="0">
-        <v>50121001</v>
+        <v>50129606</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>莲花李秀清</t>
+          <t>A1风轻云淡</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:47:43</t>
+          <t>2026-09-06 17:53:57</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="I140" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J140" s="0" t="inlineStr">
@@ -8475,11 +8475,11 @@
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="0">
-        <v>50120862</v>
+        <v>50129482</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>cobra</t>
+          <t>一心有你电话号码，</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:44:33</t>
+          <t>2026-09-06 17:49:45</t>
         </is>
       </c>
       <c r="H141" s="0" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="I141" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J141" s="0" t="inlineStr">
@@ -8535,11 +8535,11 @@
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="0">
-        <v>50120856</v>
+        <v>50121359</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>海边的星空</t>
+          <t>amy</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G142" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:44:17</t>
+          <t>2026-09-06 12:58:35</t>
         </is>
       </c>
       <c r="H142" s="0" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="I142" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J142" s="0" t="inlineStr">
@@ -8595,11 +8595,11 @@
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="0">
-        <v>50120852</v>
+        <v>50121001</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>柠檬黄🍋陈</t>
+          <t>莲花李秀清</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:44:09</t>
+          <t>2026-09-06 12:47:43</t>
         </is>
       </c>
       <c r="H143" s="0" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="I143" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J143" s="0" t="inlineStr">
@@ -8655,11 +8655,11 @@
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="0">
-        <v>50120848</v>
+        <v>50120862</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>英子</t>
+          <t>cobra</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:44:01</t>
+          <t>2026-09-06 12:44:33</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -8715,11 +8715,11 @@
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="0">
-        <v>50120818</v>
+        <v>50120856</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>peaceful</t>
+          <t>海边的星空</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:42:49</t>
+          <t>2026-09-06 12:44:17</t>
         </is>
       </c>
       <c r="H145" s="0" t="inlineStr">
@@ -8775,11 +8775,11 @@
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="0">
-        <v>50120817</v>
+        <v>50120852</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>fj</t>
+          <t>柠檬黄🍋陈</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:42:49</t>
+          <t>2026-09-06 12:44:09</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -8835,11 +8835,11 @@
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="0">
-        <v>50120806</v>
+        <v>50120848</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>💍小薇🎀💎🌷</t>
+          <t>英子</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:42:27</t>
+          <t>2026-09-06 12:44:01</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -8895,11 +8895,11 @@
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="0">
-        <v>50120803</v>
+        <v>50120818</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>于小毛</t>
+          <t>peaceful</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 12:42:25</t>
+          <t>2026-09-06 12:42:49</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -8955,11 +8955,11 @@
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="0">
-        <v>50116869</v>
+        <v>50120817</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>美义</t>
+          <t>fj</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 10:56:33</t>
+          <t>2026-09-06 12:42:49</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="I149" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J149" s="0" t="inlineStr">
@@ -9015,11 +9015,11 @@
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="0">
-        <v>50114006</v>
+        <v>50120806</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>幸运草</t>
+          <t>💍小薇🎀💎🌷</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 09:45:01</t>
+          <t>2026-09-06 12:42:27</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -9075,11 +9075,11 @@
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="0">
-        <v>50113664</v>
+        <v>50120803</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>执子之手</t>
+          <t>于小毛</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 09:37:35</t>
+          <t>2026-09-06 12:42:25</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -9135,11 +9135,11 @@
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="0">
-        <v>50113641</v>
+        <v>50116869</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>新视野</t>
+          <t>美义</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 09:36:52</t>
+          <t>2026-09-06 10:56:33</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="I152" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J152" s="0" t="inlineStr">
@@ -9195,11 +9195,11 @@
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="0">
-        <v>50113640</v>
+        <v>50114006</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>安静且聆听</t>
+          <t>幸运草</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 09:36:49</t>
+          <t>2026-09-06 09:45:01</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -9250,21 +9250,16 @@
       <c r="L153" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N153" s="0" t="inlineStr">
-        <is>
-          <t>保山</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="0">
-        <v>50113638</v>
+        <v>50113664</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>十月</t>
+          <t>执子之手</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
@@ -9289,7 +9284,7 @@
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06 09:36:45</t>
+          <t>2026-09-06 09:37:35</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -9320,11 +9315,11 @@
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="0">
-        <v>50100338</v>
+        <v>50113641</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>青山绿水</t>
+          <t>新视野</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
@@ -9349,7 +9344,7 @@
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 23:10:04</t>
+          <t>2026-09-06 09:36:52</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -9380,11 +9375,11 @@
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="0">
-        <v>50100035</v>
+        <v>50113640</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>杨</t>
+          <t>安静且聆听</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -9409,7 +9404,7 @@
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:57:53</t>
+          <t>2026-09-06 09:36:49</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -9419,7 +9414,7 @@
       </c>
       <c r="I156" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J156" s="0" t="inlineStr">
@@ -9435,16 +9430,21 @@
       <c r="L156" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N156" s="0" t="inlineStr">
+        <is>
+          <t>保山</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="0">
-        <v>50100033</v>
+        <v>50113638</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>雨后彩虹</t>
+          <t>十月</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:57:47</t>
+          <t>2026-09-06 09:36:45</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="I157" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J157" s="0" t="inlineStr">
@@ -9500,11 +9500,11 @@
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="0">
-        <v>50100028</v>
+        <v>50100338</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>首信海报</t>
+          <t>青山绿水</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:57:32</t>
+          <t>2026-09-05 23:10:04</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="I158" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J158" s="0" t="inlineStr">
@@ -9560,11 +9560,11 @@
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="0">
-        <v>50099958</v>
+        <v>50100035</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>张君</t>
+          <t>杨</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:55:57</t>
+          <t>2026-09-05 22:57:53</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -9620,11 +9620,11 @@
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="0">
-        <v>50099933</v>
+        <v>50100033</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>耶和华以勒</t>
+          <t>雨后彩虹</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:55:31</t>
+          <t>2026-09-05 22:57:47</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -9680,11 +9680,11 @@
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="0">
-        <v>50099844</v>
+        <v>50100028</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>平安</t>
+          <t>首信海报</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:49</t>
+          <t>2026-09-05 22:57:32</t>
         </is>
       </c>
       <c r="H161" s="0" t="inlineStr">
@@ -9740,11 +9740,11 @@
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="0">
-        <v>50099768</v>
+        <v>50099958</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>阳</t>
+          <t>张君</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:49:01</t>
+          <t>2026-09-05 22:55:57</t>
         </is>
       </c>
       <c r="H162" s="0" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="I162" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J162" s="0" t="inlineStr">
@@ -9800,11 +9800,11 @@
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="0">
-        <v>50099767</v>
+        <v>50099933</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>梦&amp;爷💫</t>
+          <t>耶和华以勒</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="G163" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:57</t>
+          <t>2026-09-05 22:55:31</t>
         </is>
       </c>
       <c r="H163" s="0" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="I163" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J163" s="0" t="inlineStr">
@@ -9860,11 +9860,11 @@
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="0">
-        <v>50099763</v>
+        <v>50099844</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>李丽</t>
+          <t>平安</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="G164" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:53</t>
+          <t>2026-09-05 22:51:49</t>
         </is>
       </c>
       <c r="H164" s="0" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="I164" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J164" s="0" t="inlineStr">
@@ -9920,11 +9920,11 @@
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="0">
-        <v>50099760</v>
+        <v>50099768</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>A选择无悔</t>
+          <t>阳</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:46</t>
+          <t>2026-09-05 22:49:01</t>
         </is>
       </c>
       <c r="H165" s="0" t="inlineStr">
@@ -9980,11 +9980,11 @@
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="0">
-        <v>50099759</v>
+        <v>50099767</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>信念</t>
+          <t>梦&amp;爷💫</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="G166" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:44</t>
+          <t>2026-09-05 22:48:57</t>
         </is>
       </c>
       <c r="H166" s="0" t="inlineStr">
@@ -10040,11 +10040,11 @@
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="0">
-        <v>50099757</v>
+        <v>50099763</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>李lee</t>
+          <t>李丽</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="G167" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:41</t>
+          <t>2026-09-05 22:48:53</t>
         </is>
       </c>
       <c r="H167" s="0" t="inlineStr">
@@ -10100,11 +10100,11 @@
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="0">
-        <v>50099755</v>
+        <v>50099760</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>徐飛燕*^O^*</t>
+          <t>A选择无悔</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="G168" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:39</t>
+          <t>2026-09-05 22:48:46</t>
         </is>
       </c>
       <c r="H168" s="0" t="inlineStr">
@@ -10160,11 +10160,11 @@
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="0">
-        <v>50099752</v>
+        <v>50099759</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>星移*</t>
+          <t>信念</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:35</t>
+          <t>2026-09-05 22:48:44</t>
         </is>
       </c>
       <c r="H169" s="0" t="inlineStr">
@@ -10220,11 +10220,11 @@
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="0">
-        <v>50099749</v>
+        <v>50099757</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>刘勇</t>
+          <t>李lee</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G170" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:28</t>
+          <t>2026-09-05 22:48:41</t>
         </is>
       </c>
       <c r="H170" s="0" t="inlineStr">
@@ -10280,11 +10280,11 @@
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="0">
-        <v>50099741</v>
+        <v>50099755</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>碧皓之游</t>
+          <t>徐飛燕*^O^*</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="G171" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:15</t>
+          <t>2026-09-05 22:48:39</t>
         </is>
       </c>
       <c r="H171" s="0" t="inlineStr">
@@ -10340,11 +10340,11 @@
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="0">
-        <v>50099737</v>
+        <v>50099752</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>书心燕语</t>
+          <t>星移*</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:03</t>
+          <t>2026-09-05 22:48:35</t>
         </is>
       </c>
       <c r="H172" s="0" t="inlineStr">
@@ -10400,11 +10400,11 @@
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="0">
-        <v>50099733</v>
+        <v>50099749</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>ღ᭄ꦿ微微一笑ღ᭄ꦿ</t>
+          <t>刘勇</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 22:47:47</t>
+          <t>2026-09-05 22:48:28</t>
         </is>
       </c>
       <c r="H173" s="0" t="inlineStr">
@@ -10460,11 +10460,11 @@
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="0">
-        <v>50080657</v>
+        <v>50099741</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>平红</t>
+          <t>碧皓之游</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:07:13</t>
+          <t>2026-09-05 22:48:15</t>
         </is>
       </c>
       <c r="H174" s="0" t="inlineStr">
@@ -10520,11 +10520,11 @@
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="0">
-        <v>50080582</v>
+        <v>50099737</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>aabb</t>
+          <t>书心燕语</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:05:19</t>
+          <t>2026-09-05 22:48:03</t>
         </is>
       </c>
       <c r="H175" s="0" t="inlineStr">
@@ -10580,11 +10580,11 @@
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="0">
-        <v>50080559</v>
+        <v>50099733</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>自由人</t>
+          <t>ღ᭄ꦿ微微一笑ღ᭄ꦿ</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:04:28</t>
+          <t>2026-09-05 22:47:47</t>
         </is>
       </c>
       <c r="H176" s="0" t="inlineStr">
@@ -10640,11 +10640,11 @@
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="0">
-        <v>50080553</v>
+        <v>50080657</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>晶晶</t>
+          <t>平红</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:04:15</t>
+          <t>2026-09-05 13:07:13</t>
         </is>
       </c>
       <c r="H177" s="0" t="inlineStr">
@@ -10700,11 +10700,11 @@
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="0">
-        <v>50080549</v>
+        <v>50080582</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>aabb</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:04:09</t>
+          <t>2026-09-05 13:05:19</t>
         </is>
       </c>
       <c r="H178" s="0" t="inlineStr">
@@ -10760,11 +10760,11 @@
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="0">
-        <v>50080548</v>
+        <v>50080559</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>盘子</t>
+          <t>自由人</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:04:08</t>
+          <t>2026-09-05 13:04:28</t>
         </is>
       </c>
       <c r="H179" s="0" t="inlineStr">
@@ -10820,11 +10820,11 @@
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="0">
-        <v>50080547</v>
+        <v>50080553</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>赵满珍C5</t>
+          <t>晶晶</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:04:05</t>
+          <t>2026-09-05 13:04:15</t>
         </is>
       </c>
       <c r="H180" s="0" t="inlineStr">
@@ -10880,11 +10880,11 @@
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="0">
-        <v>50080539</v>
+        <v>50080549</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>平平安安</t>
+          <t>abc</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="G181" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:51</t>
+          <t>2026-09-05 13:04:09</t>
         </is>
       </c>
       <c r="H181" s="0" t="inlineStr">
@@ -10940,11 +10940,11 @@
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="0">
-        <v>50080538</v>
+        <v>50080548</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>凡事包容</t>
+          <t>盘子</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="G182" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:51</t>
+          <t>2026-09-05 13:04:08</t>
         </is>
       </c>
       <c r="H182" s="0" t="inlineStr">
@@ -11000,11 +11000,11 @@
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="0">
-        <v>50080536</v>
+        <v>50080547</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>吴忧无忧</t>
+          <t>赵满珍C5</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="G183" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:47</t>
+          <t>2026-09-05 13:04:05</t>
         </is>
       </c>
       <c r="H183" s="0" t="inlineStr">
@@ -11060,11 +11060,11 @@
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="0">
-        <v>50080535</v>
+        <v>50080539</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>小鱼儿</t>
+          <t>平平安安</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="G184" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:43</t>
+          <t>2026-09-05 13:03:51</t>
         </is>
       </c>
       <c r="H184" s="0" t="inlineStr">
@@ -11120,11 +11120,11 @@
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="0">
-        <v>50080525</v>
+        <v>50080538</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>辞芝锦😎</t>
+          <t>凡事包容</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="G185" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:29</t>
+          <t>2026-09-05 13:03:51</t>
         </is>
       </c>
       <c r="H185" s="0" t="inlineStr">
@@ -11180,11 +11180,11 @@
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="0">
-        <v>50080523</v>
+        <v>50080536</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>早陈</t>
+          <t>吴忧无忧</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="G186" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:21</t>
+          <t>2026-09-05 13:03:47</t>
         </is>
       </c>
       <c r="H186" s="0" t="inlineStr">
@@ -11240,11 +11240,11 @@
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="0">
-        <v>50080516</v>
+        <v>50080535</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>星星の恋人</t>
+          <t>小鱼儿</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="G187" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:13</t>
+          <t>2026-09-05 13:03:43</t>
         </is>
       </c>
       <c r="H187" s="0" t="inlineStr">
@@ -11300,11 +11300,11 @@
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="0">
-        <v>50080511</v>
+        <v>50080525</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>无咎</t>
+          <t>辞芝锦😎</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="G188" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:03:09</t>
+          <t>2026-09-05 13:03:29</t>
         </is>
       </c>
       <c r="H188" s="0" t="inlineStr">
@@ -11360,11 +11360,11 @@
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="0">
-        <v>50080477</v>
+        <v>50080523</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>刘小虎</t>
+          <t>早陈</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 13:02:37</t>
+          <t>2026-09-05 13:03:21</t>
         </is>
       </c>
       <c r="H189" s="0" t="inlineStr">
@@ -11420,11 +11420,11 @@
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="0">
-        <v>50074867</v>
+        <v>50080516</v>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>美好人生</t>
+          <t>星星の恋人</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="G190" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 10:19:59</t>
+          <t>2026-09-05 13:03:13</t>
         </is>
       </c>
       <c r="H190" s="0" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="I190" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J190" s="0" t="inlineStr">
@@ -11480,11 +11480,11 @@
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="0">
-        <v>50074273</v>
+        <v>50080511</v>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>周利平</t>
+          <t>无咎</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="G191" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 10:02:26</t>
+          <t>2026-09-05 13:03:09</t>
         </is>
       </c>
       <c r="H191" s="0" t="inlineStr">
@@ -11540,11 +11540,11 @@
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="0">
-        <v>50074103</v>
+        <v>50080477</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>赵香荣</t>
+          <t>刘小虎</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="G192" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:58:29</t>
+          <t>2026-09-05 13:02:37</t>
         </is>
       </c>
       <c r="H192" s="0" t="inlineStr">
@@ -11600,11 +11600,11 @@
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="0">
-        <v>50074078</v>
+        <v>50074867</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>长风渡℡明</t>
+          <t>美好人生</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G193" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:57:49</t>
+          <t>2026-09-05 10:19:59</t>
         </is>
       </c>
       <c r="H193" s="0" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="I193" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J193" s="0" t="inlineStr">
@@ -11660,11 +11660,11 @@
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="0">
-        <v>50074077</v>
+        <v>50074273</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>海阔天空bi</t>
+          <t>周利平</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G194" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:57:47</t>
+          <t>2026-09-05 10:02:26</t>
         </is>
       </c>
       <c r="H194" s="0" t="inlineStr">
@@ -11720,11 +11720,11 @@
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="0">
-        <v>50074076</v>
+        <v>50074103</v>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>枫叶红</t>
+          <t>赵香荣</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="G195" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:57:47</t>
+          <t>2026-09-05 09:58:29</t>
         </is>
       </c>
       <c r="H195" s="0" t="inlineStr">
@@ -11780,11 +11780,11 @@
     </row>
     <row r="196" spans="1:14">
       <c r="A196" s="0">
-        <v>50074071</v>
+        <v>50074078</v>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>思缘</t>
+          <t>长风渡℡明</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G196" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:57:35</t>
+          <t>2026-09-05 09:57:49</t>
         </is>
       </c>
       <c r="H196" s="0" t="inlineStr">
@@ -11840,11 +11840,11 @@
     </row>
     <row r="197" spans="1:14">
       <c r="A197" s="0">
-        <v>50074067</v>
+        <v>50074077</v>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>悠然</t>
+          <t>海阔天空bi</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="G197" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05 09:57:25</t>
+          <t>2026-09-05 09:57:47</t>
         </is>
       </c>
       <c r="H197" s="0" t="inlineStr">
@@ -11900,11 +11900,11 @@
     </row>
     <row r="198" spans="1:14">
       <c r="A198" s="0">
-        <v>50058017</v>
+        <v>50074076</v>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>索描贾师＃壹皇贰金山玉旗🇨🇳</t>
+          <t>枫叶红</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="G198" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:16:49</t>
+          <t>2026-09-05 09:57:47</t>
         </is>
       </c>
       <c r="H198" s="0" t="inlineStr">
@@ -11960,11 +11960,11 @@
     </row>
     <row r="199" spans="1:14">
       <c r="A199" s="0">
-        <v>50057895</v>
+        <v>50074071</v>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>南雪</t>
+          <t>思缘</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G199" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:12:32</t>
+          <t>2026-09-05 09:57:35</t>
         </is>
       </c>
       <c r="H199" s="0" t="inlineStr">
@@ -12015,21 +12015,16 @@
       <c r="L199" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N199" s="0" t="inlineStr">
-        <is>
-          <t>镇江</t>
         </is>
       </c>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" s="0">
-        <v>50057857</v>
+        <v>50074067</v>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>可心</t>
+          <t>悠然</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
@@ -12054,7 +12049,7 @@
       </c>
       <c r="G200" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:10:55</t>
+          <t>2026-09-05 09:57:25</t>
         </is>
       </c>
       <c r="H200" s="0" t="inlineStr">
@@ -12085,11 +12080,11 @@
     </row>
     <row r="201" spans="1:14">
       <c r="A201" s="0">
-        <v>50057854</v>
+        <v>50058017</v>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>张苏龙</t>
+          <t>索描贾师＃壹皇贰金山玉旗🇨🇳</t>
         </is>
       </c>
       <c r="C201" s="0" t="inlineStr">
@@ -12114,7 +12109,7 @@
       </c>
       <c r="G201" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:10:51</t>
+          <t>2026-09-04 23:16:49</t>
         </is>
       </c>
       <c r="H201" s="0" t="inlineStr">
@@ -12145,11 +12140,11 @@
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="0">
-        <v>50057852</v>
+        <v>50057895</v>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>？</t>
+          <t>南雪</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
@@ -12174,7 +12169,7 @@
       </c>
       <c r="G202" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:10:43</t>
+          <t>2026-09-04 23:12:32</t>
         </is>
       </c>
       <c r="H202" s="0" t="inlineStr">
@@ -12200,16 +12195,21 @@
       <c r="L202" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N202" s="0" t="inlineStr">
+        <is>
+          <t>镇江</t>
         </is>
       </c>
     </row>
     <row r="203" spans="1:14">
       <c r="A203" s="0">
-        <v>50057841</v>
+        <v>50057857</v>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>向往的生活-电信号</t>
+          <t>可心</t>
         </is>
       </c>
       <c r="C203" s="0" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="G203" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:10:09</t>
+          <t>2026-09-04 23:10:55</t>
         </is>
       </c>
       <c r="H203" s="0" t="inlineStr">
@@ -12265,11 +12265,11 @@
     </row>
     <row r="204" spans="1:14">
       <c r="A204" s="0">
-        <v>50057839</v>
+        <v>50057854</v>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>金盏花</t>
+          <t>张苏龙</t>
         </is>
       </c>
       <c r="C204" s="0" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="G204" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 23:10:03</t>
+          <t>2026-09-04 23:10:51</t>
         </is>
       </c>
       <c r="H204" s="0" t="inlineStr">
@@ -12325,11 +12325,11 @@
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="0">
-        <v>50032697</v>
+        <v>50057852</v>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>小米. ᩚ</t>
+          <t>？</t>
         </is>
       </c>
       <c r="C205" s="0" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="G205" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 12:24:13</t>
+          <t>2026-09-04 23:10:43</t>
         </is>
       </c>
       <c r="H205" s="0" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="I205" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J205" s="0" t="inlineStr">
@@ -12385,11 +12385,11 @@
     </row>
     <row r="206" spans="1:14">
       <c r="A206" s="0">
-        <v>50032693</v>
+        <v>50057841</v>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>海岸</t>
+          <t>向往的生活-电信号</t>
         </is>
       </c>
       <c r="C206" s="0" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="G206" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 12:24:11</t>
+          <t>2026-09-04 23:10:09</t>
         </is>
       </c>
       <c r="H206" s="0" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="I206" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J206" s="0" t="inlineStr">
@@ -12445,11 +12445,11 @@
     </row>
     <row r="207" spans="1:14">
       <c r="A207" s="0">
-        <v>50032683</v>
+        <v>50057839</v>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>陆建军</t>
+          <t>金盏花</t>
         </is>
       </c>
       <c r="C207" s="0" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G207" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 12:23:53</t>
+          <t>2026-09-04 23:10:03</t>
         </is>
       </c>
       <c r="H207" s="0" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="I207" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J207" s="0" t="inlineStr">
@@ -12505,11 +12505,11 @@
     </row>
     <row r="208" spans="1:14">
       <c r="A208" s="0">
-        <v>50015883</v>
+        <v>50032697</v>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>A00金华义乌叉车出租电15268650979</t>
+          <t>小米. ᩚ</t>
         </is>
       </c>
       <c r="C208" s="0" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="G208" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:18:02</t>
+          <t>2026-09-04 12:24:13</t>
         </is>
       </c>
       <c r="H208" s="0" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="I208" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J208" s="0" t="inlineStr">
@@ -12565,11 +12565,11 @@
     </row>
     <row r="209" spans="1:14">
       <c r="A209" s="0">
-        <v>50015882</v>
+        <v>50032693</v>
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>建程仓储中心 张川</t>
+          <t>海岸</t>
         </is>
       </c>
       <c r="C209" s="0" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="G209" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:18:02</t>
+          <t>2026-09-04 12:24:11</t>
         </is>
       </c>
       <c r="H209" s="0" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="I209" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J209" s="0" t="inlineStr">
@@ -12625,11 +12625,11 @@
     </row>
     <row r="210" spans="1:14">
       <c r="A210" s="0">
-        <v>50015784</v>
+        <v>50032683</v>
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>天空</t>
+          <t>陆建军</t>
         </is>
       </c>
       <c r="C210" s="0" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="G210" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:41</t>
+          <t>2026-09-04 12:23:53</t>
         </is>
       </c>
       <c r="H210" s="0" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="I210" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J210" s="0" t="inlineStr">
@@ -12685,11 +12685,11 @@
     </row>
     <row r="211" spans="1:14">
       <c r="A211" s="0">
-        <v>50015778</v>
+        <v>50015883</v>
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>小龙女</t>
+          <t>A00金华义乌叉车出租电15268650979</t>
         </is>
       </c>
       <c r="C211" s="0" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="G211" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:21</t>
+          <t>2026-09-03 23:18:02</t>
         </is>
       </c>
       <c r="H211" s="0" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="I211" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J211" s="0" t="inlineStr">
@@ -12745,11 +12745,11 @@
     </row>
     <row r="212" spans="1:14">
       <c r="A212" s="0">
-        <v>50015776</v>
+        <v>50015882</v>
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>桥梁</t>
+          <t>建程仓储中心 张川</t>
         </is>
       </c>
       <c r="C212" s="0" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="G212" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:15</t>
+          <t>2026-09-03 23:18:02</t>
         </is>
       </c>
       <c r="H212" s="0" t="inlineStr">
@@ -12805,11 +12805,11 @@
     </row>
     <row r="213" spans="1:14">
       <c r="A213" s="0">
-        <v>50015775</v>
+        <v>50015784</v>
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>彩云之南</t>
+          <t>天空</t>
         </is>
       </c>
       <c r="C213" s="0" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="G213" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:13</t>
+          <t>2026-09-03 23:10:41</t>
         </is>
       </c>
       <c r="H213" s="0" t="inlineStr">
@@ -12865,11 +12865,11 @@
     </row>
     <row r="214" spans="1:14">
       <c r="A214" s="0">
-        <v>50015774</v>
+        <v>50015778</v>
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>楊精蓄銳༒</t>
+          <t>小龙女</t>
         </is>
       </c>
       <c r="C214" s="0" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="G214" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:11</t>
+          <t>2026-09-03 23:10:21</t>
         </is>
       </c>
       <c r="H214" s="0" t="inlineStr">
@@ -12925,11 +12925,11 @@
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="0">
-        <v>50015772</v>
+        <v>50015776</v>
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>不倒翁</t>
+          <t>桥梁</t>
         </is>
       </c>
       <c r="C215" s="0" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="G215" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:07</t>
+          <t>2026-09-03 23:10:15</t>
         </is>
       </c>
       <c r="H215" s="0" t="inlineStr">
@@ -12985,11 +12985,11 @@
     </row>
     <row r="216" spans="1:14">
       <c r="A216" s="0">
-        <v>50015770</v>
+        <v>50015775</v>
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>一江春水</t>
+          <t>彩云之南</t>
         </is>
       </c>
       <c r="C216" s="0" t="inlineStr">
@@ -13014,7 +13014,7 @@
       </c>
       <c r="G216" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:05</t>
+          <t>2026-09-03 23:10:13</t>
         </is>
       </c>
       <c r="H216" s="0" t="inlineStr">
@@ -13045,11 +13045,11 @@
     </row>
     <row r="217" spans="1:14">
       <c r="A217" s="0">
-        <v>50015767</v>
+        <v>50015774</v>
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
-          <t>微笑</t>
+          <t>楊精蓄銳༒</t>
         </is>
       </c>
       <c r="C217" s="0" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="G217" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:10:03</t>
+          <t>2026-09-03 23:10:11</t>
         </is>
       </c>
       <c r="H217" s="0" t="inlineStr">
@@ -13105,11 +13105,11 @@
     </row>
     <row r="218" spans="1:14">
       <c r="A218" s="0">
-        <v>50015763</v>
+        <v>50015772</v>
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
-          <t>北斗星</t>
+          <t>不倒翁</t>
         </is>
       </c>
       <c r="C218" s="0" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="G218" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 23:09:39</t>
+          <t>2026-09-03 23:10:07</t>
         </is>
       </c>
       <c r="H218" s="0" t="inlineStr">
@@ -13165,11 +13165,11 @@
     </row>
     <row r="219" spans="1:14">
       <c r="A219" s="0">
-        <v>49989442</v>
+        <v>50015770</v>
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
-          <t>冬梅花儿开王丽君</t>
+          <t>一江春水</t>
         </is>
       </c>
       <c r="C219" s="0" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="G219" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 12:23:43</t>
+          <t>2026-09-03 23:10:05</t>
         </is>
       </c>
       <c r="H219" s="0" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="I219" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J219" s="0" t="inlineStr">
@@ -13225,11 +13225,11 @@
     </row>
     <row r="220" spans="1:14">
       <c r="A220" s="0">
-        <v>49989431</v>
+        <v>50015767</v>
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
-          <t>风声</t>
+          <t>微笑</t>
         </is>
       </c>
       <c r="C220" s="0" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="G220" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 12:23:25</t>
+          <t>2026-09-03 23:10:03</t>
         </is>
       </c>
       <c r="H220" s="0" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="I220" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J220" s="0" t="inlineStr">
@@ -13285,11 +13285,11 @@
     </row>
     <row r="221" spans="1:14">
       <c r="A221" s="0">
-        <v>49989419</v>
+        <v>50015763</v>
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
-          <t>胡宾</t>
+          <t>北斗星</t>
         </is>
       </c>
       <c r="C221" s="0" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="G221" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 12:23:13</t>
+          <t>2026-09-03 23:09:39</t>
         </is>
       </c>
       <c r="H221" s="0" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="I221" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J221" s="0" t="inlineStr">
@@ -13345,11 +13345,11 @@
     </row>
     <row r="222" spans="1:14">
       <c r="A222" s="0">
-        <v>49989410</v>
+        <v>49989442</v>
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
-          <t>永远</t>
+          <t>冬梅花儿开王丽君</t>
         </is>
       </c>
       <c r="C222" s="0" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="G222" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 12:23:03</t>
+          <t>2026-09-03 12:23:43</t>
         </is>
       </c>
       <c r="H222" s="0" t="inlineStr">
@@ -13405,11 +13405,11 @@
     </row>
     <row r="223" spans="1:14">
       <c r="A223" s="0">
-        <v>49984259</v>
+        <v>49989431</v>
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
-          <t>好运包张</t>
+          <t>风声</t>
         </is>
       </c>
       <c r="C223" s="0" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="G223" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 09:55:37</t>
+          <t>2026-09-03 12:23:25</t>
         </is>
       </c>
       <c r="H223" s="0" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="I223" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J223" s="0" t="inlineStr">
@@ -13465,11 +13465,11 @@
     </row>
     <row r="224" spans="1:14">
       <c r="A224" s="0">
-        <v>49984055</v>
+        <v>49989419</v>
       </c>
       <c r="B224" s="0" t="inlineStr">
         <is>
-          <t>点点星辰</t>
+          <t>胡宾</t>
         </is>
       </c>
       <c r="C224" s="0" t="inlineStr">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="G224" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 09:49:33</t>
+          <t>2026-09-03 12:23:13</t>
         </is>
       </c>
       <c r="H224" s="0" t="inlineStr">
@@ -13504,7 +13504,7 @@
       </c>
       <c r="I224" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J224" s="0" t="inlineStr">
@@ -13525,11 +13525,11 @@
     </row>
     <row r="225" spans="1:14">
       <c r="A225" s="0">
-        <v>49983134</v>
+        <v>49989410</v>
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
-          <t>Zhangrruzhen张如真</t>
+          <t>永远</t>
         </is>
       </c>
       <c r="C225" s="0" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="G225" s="0" t="inlineStr">
         <is>
-          <t>2026-09-03 09:25:21</t>
+          <t>2026-09-03 12:23:03</t>
         </is>
       </c>
       <c r="H225" s="0" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="I225" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J225" s="0" t="inlineStr">
@@ -13585,11 +13585,11 @@
     </row>
     <row r="226" spans="1:14">
       <c r="A226" s="0">
-        <v>49971209</v>
+        <v>49984259</v>
       </c>
       <c r="B226" s="0" t="inlineStr">
         <is>
-          <t>顺丰顺水</t>
+          <t>好运包张</t>
         </is>
       </c>
       <c r="C226" s="0" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="G226" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:29:41</t>
+          <t>2026-09-03 09:55:37</t>
         </is>
       </c>
       <c r="H226" s="0" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="I226" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J226" s="0" t="inlineStr">
@@ -13645,11 +13645,11 @@
     </row>
     <row r="227" spans="1:14">
       <c r="A227" s="0">
-        <v>49970732</v>
+        <v>49984055</v>
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
-          <t>China 🇨🇳</t>
+          <t>点点星辰</t>
         </is>
       </c>
       <c r="C227" s="0" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="G227" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:13:53</t>
+          <t>2026-09-03 09:49:33</t>
         </is>
       </c>
       <c r="H227" s="0" t="inlineStr">
@@ -13705,11 +13705,11 @@
     </row>
     <row r="228" spans="1:14">
       <c r="A228" s="0">
-        <v>49970712</v>
+        <v>49983134</v>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>月色琴弦</t>
+          <t>Zhangrruzhen张如真</t>
         </is>
       </c>
       <c r="C228" s="0" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="G228" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:13:07</t>
+          <t>2026-09-03 09:25:21</t>
         </is>
       </c>
       <c r="H228" s="0" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="I228" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J228" s="0" t="inlineStr">
@@ -13765,11 +13765,11 @@
     </row>
     <row r="229" spans="1:14">
       <c r="A229" s="0">
-        <v>49970699</v>
+        <v>49971209</v>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>铜铃</t>
+          <t>顺丰顺水</t>
         </is>
       </c>
       <c r="C229" s="0" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="G229" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:12:49</t>
+          <t>2026-09-02 23:29:41</t>
         </is>
       </c>
       <c r="H229" s="0" t="inlineStr">
@@ -13825,11 +13825,11 @@
     </row>
     <row r="230" spans="1:14">
       <c r="A230" s="0">
-        <v>49970698</v>
+        <v>49970732</v>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
-          <t>东风吹</t>
+          <t>China 🇨🇳</t>
         </is>
       </c>
       <c r="C230" s="0" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="G230" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:12:47</t>
+          <t>2026-09-02 23:13:53</t>
         </is>
       </c>
       <c r="H230" s="0" t="inlineStr">
@@ -13885,11 +13885,11 @@
     </row>
     <row r="231" spans="1:14">
       <c r="A231" s="0">
-        <v>49970683</v>
+        <v>49970712</v>
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
-          <t>杨永强</t>
+          <t>月色琴弦</t>
         </is>
       </c>
       <c r="C231" s="0" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="G231" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:12:17</t>
+          <t>2026-09-02 23:13:07</t>
         </is>
       </c>
       <c r="H231" s="0" t="inlineStr">
@@ -13945,11 +13945,11 @@
     </row>
     <row r="232" spans="1:14">
       <c r="A232" s="0">
-        <v>49970662</v>
+        <v>49970699</v>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
-          <t>盈丰</t>
+          <t>铜铃</t>
         </is>
       </c>
       <c r="C232" s="0" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="G232" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:11:33</t>
+          <t>2026-09-02 23:12:49</t>
         </is>
       </c>
       <c r="H232" s="0" t="inlineStr">
@@ -14005,11 +14005,11 @@
     </row>
     <row r="233" spans="1:14">
       <c r="A233" s="0">
-        <v>49970652</v>
+        <v>49970698</v>
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
-          <t>YAN</t>
+          <t>东风吹</t>
         </is>
       </c>
       <c r="C233" s="0" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="G233" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:11:15</t>
+          <t>2026-09-02 23:12:47</t>
         </is>
       </c>
       <c r="H233" s="0" t="inlineStr">
@@ -14065,11 +14065,11 @@
     </row>
     <row r="234" spans="1:14">
       <c r="A234" s="0">
-        <v>49970649</v>
+        <v>49970683</v>
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
-          <t>彩虹（宋荷娣）</t>
+          <t>杨永强</t>
         </is>
       </c>
       <c r="C234" s="0" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="G234" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:11:11</t>
+          <t>2026-09-02 23:12:17</t>
         </is>
       </c>
       <c r="H234" s="0" t="inlineStr">
@@ -14125,11 +14125,11 @@
     </row>
     <row r="235" spans="1:14">
       <c r="A235" s="0">
-        <v>49970648</v>
+        <v>49970662</v>
       </c>
       <c r="B235" s="0" t="inlineStr">
         <is>
-          <t>天知心</t>
+          <t>盈丰</t>
         </is>
       </c>
       <c r="C235" s="0" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="G235" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:11:08</t>
+          <t>2026-09-02 23:11:33</t>
         </is>
       </c>
       <c r="H235" s="0" t="inlineStr">
@@ -14185,11 +14185,11 @@
     </row>
     <row r="236" spans="1:14">
       <c r="A236" s="0">
-        <v>49970643</v>
+        <v>49970652</v>
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
-          <t>好运来</t>
+          <t>YAN</t>
         </is>
       </c>
       <c r="C236" s="0" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="G236" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 23:10:55</t>
+          <t>2026-09-02 23:11:15</t>
         </is>
       </c>
       <c r="H236" s="0" t="inlineStr">
@@ -14245,11 +14245,11 @@
     </row>
     <row r="237" spans="1:14">
       <c r="A237" s="0">
-        <v>49937566</v>
+        <v>49970649</v>
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
-          <t>简单sincerity</t>
+          <t>彩虹（宋荷娣）</t>
         </is>
       </c>
       <c r="C237" s="0" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="G237" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 10:10:33</t>
+          <t>2026-09-02 23:11:11</t>
         </is>
       </c>
       <c r="H237" s="0" t="inlineStr">
@@ -14305,11 +14305,11 @@
     </row>
     <row r="238" spans="1:14">
       <c r="A238" s="0">
-        <v>49937187</v>
+        <v>49970648</v>
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
-          <t>莲子</t>
+          <t>天知心</t>
         </is>
       </c>
       <c r="C238" s="0" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="G238" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:58:56</t>
+          <t>2026-09-02 23:11:08</t>
         </is>
       </c>
       <c r="H238" s="0" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="I238" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J238" s="0" t="inlineStr">
@@ -14365,11 +14365,11 @@
     </row>
     <row r="239" spans="1:14">
       <c r="A239" s="0">
-        <v>49937101</v>
+        <v>49970643</v>
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
-          <t>蓉儿</t>
+          <t>好运来</t>
         </is>
       </c>
       <c r="C239" s="0" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="G239" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:56:16</t>
+          <t>2026-09-02 23:10:55</t>
         </is>
       </c>
       <c r="H239" s="0" t="inlineStr">
@@ -14425,11 +14425,11 @@
     </row>
     <row r="240" spans="1:14">
       <c r="A240" s="0">
-        <v>49937098</v>
+        <v>49937566</v>
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
-          <t>瀚林2368</t>
+          <t>简单sincerity</t>
         </is>
       </c>
       <c r="C240" s="0" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="G240" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:56:15</t>
+          <t>2026-09-02 10:10:33</t>
         </is>
       </c>
       <c r="H240" s="0" t="inlineStr">
@@ -14485,11 +14485,11 @@
     </row>
     <row r="241" spans="1:14">
       <c r="A241" s="0">
-        <v>49937081</v>
+        <v>49937187</v>
       </c>
       <c r="B241" s="0" t="inlineStr">
         <is>
-          <t>🔱 花中之美</t>
+          <t>莲子</t>
         </is>
       </c>
       <c r="C241" s="0" t="inlineStr">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="G241" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:55:47</t>
+          <t>2026-09-02 09:58:56</t>
         </is>
       </c>
       <c r="H241" s="0" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="I241" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J241" s="0" t="inlineStr">
@@ -14545,11 +14545,11 @@
     </row>
     <row r="242" spans="1:14">
       <c r="A242" s="0">
-        <v>49937066</v>
+        <v>49937101</v>
       </c>
       <c r="B242" s="0" t="inlineStr">
         <is>
-          <t>雨情</t>
+          <t>蓉儿</t>
         </is>
       </c>
       <c r="C242" s="0" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G242" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:55:27</t>
+          <t>2026-09-02 09:56:16</t>
         </is>
       </c>
       <c r="H242" s="0" t="inlineStr">
@@ -14605,11 +14605,11 @@
     </row>
     <row r="243" spans="1:14">
       <c r="A243" s="0">
-        <v>49937061</v>
+        <v>49937098</v>
       </c>
       <c r="B243" s="0" t="inlineStr">
         <is>
-          <t>Sunny 🎈瑶</t>
+          <t>瀚林2368</t>
         </is>
       </c>
       <c r="C243" s="0" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="G243" s="0" t="inlineStr">
         <is>
-          <t>2026-09-02 09:55:23</t>
+          <t>2026-09-02 09:56:15</t>
         </is>
       </c>
       <c r="H243" s="0" t="inlineStr">
@@ -14665,11 +14665,11 @@
     </row>
     <row r="244" spans="1:14">
       <c r="A244" s="0">
-        <v>49887876</v>
+        <v>49937081</v>
       </c>
       <c r="B244" s="0" t="inlineStr">
         <is>
-          <t>鱼靖儿</t>
+          <t>🔱 花中之美</t>
         </is>
       </c>
       <c r="C244" s="0" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="G244" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:23:11</t>
+          <t>2026-09-02 09:55:47</t>
         </is>
       </c>
       <c r="H244" s="0" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="I244" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J244" s="0" t="inlineStr">
@@ -14725,11 +14725,11 @@
     </row>
     <row r="245" spans="1:14">
       <c r="A245" s="0">
-        <v>49887478</v>
+        <v>49937066</v>
       </c>
       <c r="B245" s="0" t="inlineStr">
         <is>
-          <t>风调雨顺</t>
+          <t>雨情</t>
         </is>
       </c>
       <c r="C245" s="0" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="G245" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:10:17</t>
+          <t>2026-09-02 09:55:27</t>
         </is>
       </c>
       <c r="H245" s="0" t="inlineStr">
@@ -14785,11 +14785,11 @@
     </row>
     <row r="246" spans="1:14">
       <c r="A246" s="0">
-        <v>49887447</v>
+        <v>49937061</v>
       </c>
       <c r="B246" s="0" t="inlineStr">
         <is>
-          <t>中国艺人</t>
+          <t>Sunny 🎈瑶</t>
         </is>
       </c>
       <c r="C246" s="0" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="G246" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:08:44</t>
+          <t>2026-09-02 09:55:23</t>
         </is>
       </c>
       <c r="H246" s="0" t="inlineStr">
@@ -14845,11 +14845,11 @@
     </row>
     <row r="247" spans="1:14">
       <c r="A247" s="0">
-        <v>49887439</v>
+        <v>49887876</v>
       </c>
       <c r="B247" s="0" t="inlineStr">
         <is>
-          <t>黄晓玲</t>
+          <t>鱼靖儿</t>
         </is>
       </c>
       <c r="C247" s="0" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="G247" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:08:17</t>
+          <t>2026-08-31 23:23:11</t>
         </is>
       </c>
       <c r="H247" s="0" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="I247" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J247" s="0" t="inlineStr">
@@ -14905,11 +14905,11 @@
     </row>
     <row r="248" spans="1:14">
       <c r="A248" s="0">
-        <v>49887437</v>
+        <v>49887478</v>
       </c>
       <c r="B248" s="0" t="inlineStr">
         <is>
-          <t>随缘</t>
+          <t>风调雨顺</t>
         </is>
       </c>
       <c r="C248" s="0" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="G248" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:08:07</t>
+          <t>2026-08-31 23:10:17</t>
         </is>
       </c>
       <c r="H248" s="0" t="inlineStr">
@@ -14965,11 +14965,11 @@
     </row>
     <row r="249" spans="1:14">
       <c r="A249" s="0">
-        <v>49887416</v>
+        <v>49887447</v>
       </c>
       <c r="B249" s="0" t="inlineStr">
         <is>
-          <t>刘秋红</t>
+          <t>中国艺人</t>
         </is>
       </c>
       <c r="C249" s="0" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="G249" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:07:31</t>
+          <t>2026-08-31 23:08:44</t>
         </is>
       </c>
       <c r="H249" s="0" t="inlineStr">
@@ -15025,11 +15025,11 @@
     </row>
     <row r="250" spans="1:14">
       <c r="A250" s="0">
-        <v>49887403</v>
+        <v>49887439</v>
       </c>
       <c r="B250" s="0" t="inlineStr">
         <is>
-          <t>Mr.</t>
+          <t>黄晓玲</t>
         </is>
       </c>
       <c r="C250" s="0" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="G250" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:07:05</t>
+          <t>2026-08-31 23:08:17</t>
         </is>
       </c>
       <c r="H250" s="0" t="inlineStr">
@@ -15085,11 +15085,11 @@
     </row>
     <row r="251" spans="1:14">
       <c r="A251" s="0">
-        <v>49887401</v>
+        <v>49887437</v>
       </c>
       <c r="B251" s="0" t="inlineStr">
         <is>
-          <t>万事如意</t>
+          <t>随缘</t>
         </is>
       </c>
       <c r="C251" s="0" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="G251" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:07:03</t>
+          <t>2026-08-31 23:08:07</t>
         </is>
       </c>
       <c r="H251" s="0" t="inlineStr">
@@ -15145,11 +15145,11 @@
     </row>
     <row r="252" spans="1:14">
       <c r="A252" s="0">
-        <v>49887400</v>
+        <v>49887416</v>
       </c>
       <c r="B252" s="0" t="inlineStr">
         <is>
-          <t>💋诺墨</t>
+          <t>刘秋红</t>
         </is>
       </c>
       <c r="C252" s="0" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="G252" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:07:01</t>
+          <t>2026-08-31 23:07:31</t>
         </is>
       </c>
       <c r="H252" s="0" t="inlineStr">
@@ -15205,11 +15205,11 @@
     </row>
     <row r="253" spans="1:14">
       <c r="A253" s="0">
-        <v>49887399</v>
+        <v>49887403</v>
       </c>
       <c r="B253" s="0" t="inlineStr">
         <is>
-          <t>听风</t>
+          <t>Mr.</t>
         </is>
       </c>
       <c r="C253" s="0" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="G253" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31 23:06:59</t>
+          <t>2026-08-31 23:07:05</t>
         </is>
       </c>
       <c r="H253" s="0" t="inlineStr">
@@ -15265,11 +15265,11 @@
     </row>
     <row r="254" spans="1:14">
       <c r="A254" s="0">
-        <v>49845584</v>
+        <v>49887401</v>
       </c>
       <c r="B254" s="0" t="inlineStr">
         <is>
-          <t>彭汉平13024282926</t>
+          <t>万事如意</t>
         </is>
       </c>
       <c r="C254" s="0" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="G254" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:18:55</t>
+          <t>2026-08-31 23:07:03</t>
         </is>
       </c>
       <c r="H254" s="0" t="inlineStr">
@@ -15325,11 +15325,11 @@
     </row>
     <row r="255" spans="1:14">
       <c r="A255" s="0">
-        <v>49845487</v>
+        <v>49887400</v>
       </c>
       <c r="B255" s="0" t="inlineStr">
         <is>
-          <t>Z国华</t>
+          <t>💋诺墨</t>
         </is>
       </c>
       <c r="C255" s="0" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G255" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:15:49</t>
+          <t>2026-08-31 23:07:01</t>
         </is>
       </c>
       <c r="H255" s="0" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="I255" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J255" s="0" t="inlineStr">
@@ -15385,11 +15385,11 @@
     </row>
     <row r="256" spans="1:14">
       <c r="A256" s="0">
-        <v>49845407</v>
+        <v>49887399</v>
       </c>
       <c r="B256" s="0" t="inlineStr">
         <is>
-          <t>月亮🌛</t>
+          <t>听风</t>
         </is>
       </c>
       <c r="C256" s="0" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="G256" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:12:33</t>
+          <t>2026-08-31 23:06:59</t>
         </is>
       </c>
       <c r="H256" s="0" t="inlineStr">
@@ -15445,11 +15445,11 @@
     </row>
     <row r="257" spans="1:14">
       <c r="A257" s="0">
-        <v>49845398</v>
+        <v>49845584</v>
       </c>
       <c r="B257" s="0" t="inlineStr">
         <is>
-          <t>老树</t>
+          <t>彭汉平13024282926</t>
         </is>
       </c>
       <c r="C257" s="0" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="G257" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:12:03</t>
+          <t>2026-08-30 23:18:55</t>
         </is>
       </c>
       <c r="H257" s="0" t="inlineStr">
@@ -15505,11 +15505,11 @@
     </row>
     <row r="258" spans="1:14">
       <c r="A258" s="0">
-        <v>49845391</v>
+        <v>49845487</v>
       </c>
       <c r="B258" s="0" t="inlineStr">
         <is>
-          <t>八哥</t>
+          <t>Z国华</t>
         </is>
       </c>
       <c r="C258" s="0" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="G258" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:11:45</t>
+          <t>2026-08-30 23:15:49</t>
         </is>
       </c>
       <c r="H258" s="0" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="I258" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J258" s="0" t="inlineStr">
@@ -15565,11 +15565,11 @@
     </row>
     <row r="259" spans="1:14">
       <c r="A259" s="0">
-        <v>49845380</v>
+        <v>49845407</v>
       </c>
       <c r="B259" s="0" t="inlineStr">
         <is>
-          <t>铲车主出租15352562068</t>
+          <t>月亮🌛</t>
         </is>
       </c>
       <c r="C259" s="0" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="G259" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:11:29</t>
+          <t>2026-08-30 23:12:33</t>
         </is>
       </c>
       <c r="H259" s="0" t="inlineStr">
@@ -15625,11 +15625,11 @@
     </row>
     <row r="260" spans="1:14">
       <c r="A260" s="0">
-        <v>49845376</v>
+        <v>49845398</v>
       </c>
       <c r="B260" s="0" t="inlineStr">
         <is>
-          <t>刘萍</t>
+          <t>老树</t>
         </is>
       </c>
       <c r="C260" s="0" t="inlineStr">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="G260" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:11:15</t>
+          <t>2026-08-30 23:12:03</t>
         </is>
       </c>
       <c r="H260" s="0" t="inlineStr">
@@ -15685,11 +15685,11 @@
     </row>
     <row r="261" spans="1:14">
       <c r="A261" s="0">
-        <v>49845374</v>
+        <v>49845391</v>
       </c>
       <c r="B261" s="0" t="inlineStr">
         <is>
-          <t>空谷幽兰</t>
+          <t>八哥</t>
         </is>
       </c>
       <c r="C261" s="0" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="G261" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:11:07</t>
+          <t>2026-08-30 23:11:45</t>
         </is>
       </c>
       <c r="H261" s="0" t="inlineStr">
@@ -15745,11 +15745,11 @@
     </row>
     <row r="262" spans="1:14">
       <c r="A262" s="0">
-        <v>49845373</v>
+        <v>49845380</v>
       </c>
       <c r="B262" s="0" t="inlineStr">
         <is>
-          <t>泽浩羊</t>
+          <t>铲车主出租15352562068</t>
         </is>
       </c>
       <c r="C262" s="0" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="G262" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:11:05</t>
+          <t>2026-08-30 23:11:29</t>
         </is>
       </c>
       <c r="H262" s="0" t="inlineStr">
@@ -15805,11 +15805,11 @@
     </row>
     <row r="263" spans="1:14">
       <c r="A263" s="0">
-        <v>49845367</v>
+        <v>49845376</v>
       </c>
       <c r="B263" s="0" t="inlineStr">
         <is>
-          <t>峰回路转</t>
+          <t>刘萍</t>
         </is>
       </c>
       <c r="C263" s="0" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="G263" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:10:55</t>
+          <t>2026-08-30 23:11:15</t>
         </is>
       </c>
       <c r="H263" s="0" t="inlineStr">
@@ -15865,11 +15865,11 @@
     </row>
     <row r="264" spans="1:14">
       <c r="A264" s="0">
-        <v>49845366</v>
+        <v>49845374</v>
       </c>
       <c r="B264" s="0" t="inlineStr">
         <is>
-          <t>超儿</t>
+          <t>空谷幽兰</t>
         </is>
       </c>
       <c r="C264" s="0" t="inlineStr">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="G264" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:10:51</t>
+          <t>2026-08-30 23:11:07</t>
         </is>
       </c>
       <c r="H264" s="0" t="inlineStr">
@@ -15925,11 +15925,11 @@
     </row>
     <row r="265" spans="1:14">
       <c r="A265" s="0">
-        <v>49845365</v>
+        <v>49845373</v>
       </c>
       <c r="B265" s="0" t="inlineStr">
         <is>
-          <t>传</t>
+          <t>泽浩羊</t>
         </is>
       </c>
       <c r="C265" s="0" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="G265" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:10:49</t>
+          <t>2026-08-30 23:11:05</t>
         </is>
       </c>
       <c r="H265" s="0" t="inlineStr">
@@ -15985,11 +15985,11 @@
     </row>
     <row r="266" spans="1:14">
       <c r="A266" s="0">
-        <v>49845360</v>
+        <v>49845367</v>
       </c>
       <c r="B266" s="0" t="inlineStr">
         <is>
-          <t>悟歌</t>
+          <t>峰回路转</t>
         </is>
       </c>
       <c r="C266" s="0" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="G266" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:10:43</t>
+          <t>2026-08-30 23:10:55</t>
         </is>
       </c>
       <c r="H266" s="0" t="inlineStr">
@@ -16045,11 +16045,11 @@
     </row>
     <row r="267" spans="1:14">
       <c r="A267" s="0">
-        <v>49845342</v>
+        <v>49845366</v>
       </c>
       <c r="B267" s="0" t="inlineStr">
         <is>
-          <t>丽丽</t>
+          <t>超儿</t>
         </is>
       </c>
       <c r="C267" s="0" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G267" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 23:10:15</t>
+          <t>2026-08-30 23:10:51</t>
         </is>
       </c>
       <c r="H267" s="0" t="inlineStr">
@@ -16105,11 +16105,11 @@
     </row>
     <row r="268" spans="1:14">
       <c r="A268" s="0">
-        <v>49826011</v>
+        <v>49845365</v>
       </c>
       <c r="B268" s="0" t="inlineStr">
         <is>
-          <t>王前卫</t>
+          <t>传</t>
         </is>
       </c>
       <c r="C268" s="0" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="G268" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:57:27</t>
+          <t>2026-08-30 23:10:49</t>
         </is>
       </c>
       <c r="H268" s="0" t="inlineStr">
@@ -16165,11 +16165,11 @@
     </row>
     <row r="269" spans="1:14">
       <c r="A269" s="0">
-        <v>49825720</v>
+        <v>49845360</v>
       </c>
       <c r="B269" s="0" t="inlineStr">
         <is>
-          <t>老A</t>
+          <t>悟歌</t>
         </is>
       </c>
       <c r="C269" s="0" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="G269" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:46:02</t>
+          <t>2026-08-30 23:10:43</t>
         </is>
       </c>
       <c r="H269" s="0" t="inlineStr">
@@ -16225,11 +16225,11 @@
     </row>
     <row r="270" spans="1:14">
       <c r="A270" s="0">
-        <v>49825676</v>
+        <v>49845342</v>
       </c>
       <c r="B270" s="0" t="inlineStr">
         <is>
-          <t>蓝天</t>
+          <t>丽丽</t>
         </is>
       </c>
       <c r="C270" s="0" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="G270" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:44:05</t>
+          <t>2026-08-30 23:10:15</t>
         </is>
       </c>
       <c r="H270" s="0" t="inlineStr">
@@ -16285,11 +16285,11 @@
     </row>
     <row r="271" spans="1:14">
       <c r="A271" s="0">
-        <v>49825650</v>
+        <v>49826011</v>
       </c>
       <c r="B271" s="0" t="inlineStr">
         <is>
-          <t>爱芳</t>
+          <t>王前卫</t>
         </is>
       </c>
       <c r="C271" s="0" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="G271" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:43:11</t>
+          <t>2026-08-30 12:57:27</t>
         </is>
       </c>
       <c r="H271" s="0" t="inlineStr">
@@ -16345,11 +16345,11 @@
     </row>
     <row r="272" spans="1:14">
       <c r="A272" s="0">
-        <v>49825642</v>
+        <v>49825720</v>
       </c>
       <c r="B272" s="0" t="inlineStr">
         <is>
-          <t>银杏树</t>
+          <t>老A</t>
         </is>
       </c>
       <c r="C272" s="0" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="G272" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:55</t>
+          <t>2026-08-30 12:46:02</t>
         </is>
       </c>
       <c r="H272" s="0" t="inlineStr">
@@ -16405,11 +16405,11 @@
     </row>
     <row r="273" spans="1:14">
       <c r="A273" s="0">
-        <v>49825640</v>
+        <v>49825676</v>
       </c>
       <c r="B273" s="0" t="inlineStr">
         <is>
-          <t>遵命有福（杨凤）</t>
+          <t>蓝天</t>
         </is>
       </c>
       <c r="C273" s="0" t="inlineStr">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="G273" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:49</t>
+          <t>2026-08-30 12:44:05</t>
         </is>
       </c>
       <c r="H273" s="0" t="inlineStr">
@@ -16465,11 +16465,11 @@
     </row>
     <row r="274" spans="1:14">
       <c r="A274" s="0">
-        <v>49825639</v>
+        <v>49825650</v>
       </c>
       <c r="B274" s="0" t="inlineStr">
         <is>
-          <t>申华</t>
+          <t>爱芳</t>
         </is>
       </c>
       <c r="C274" s="0" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="G274" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:49</t>
+          <t>2026-08-30 12:43:11</t>
         </is>
       </c>
       <c r="H274" s="0" t="inlineStr">
@@ -16525,11 +16525,11 @@
     </row>
     <row r="275" spans="1:14">
       <c r="A275" s="0">
-        <v>49825637</v>
+        <v>49825642</v>
       </c>
       <c r="B275" s="0" t="inlineStr">
         <is>
-          <t>陈月焓</t>
+          <t>银杏树</t>
         </is>
       </c>
       <c r="C275" s="0" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="G275" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:47</t>
+          <t>2026-08-30 12:42:55</t>
         </is>
       </c>
       <c r="H275" s="0" t="inlineStr">
@@ -16585,11 +16585,11 @@
     </row>
     <row r="276" spans="1:14">
       <c r="A276" s="0">
-        <v>49825635</v>
+        <v>49825640</v>
       </c>
       <c r="B276" s="0" t="inlineStr">
         <is>
-          <t>小镇生活&amp;&amp;杜震</t>
+          <t>遵命有福（杨凤）</t>
         </is>
       </c>
       <c r="C276" s="0" t="inlineStr">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="G276" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:43</t>
+          <t>2026-08-30 12:42:49</t>
         </is>
       </c>
       <c r="H276" s="0" t="inlineStr">
@@ -16645,11 +16645,11 @@
     </row>
     <row r="277" spans="1:14">
       <c r="A277" s="0">
-        <v>49825628</v>
+        <v>49825639</v>
       </c>
       <c r="B277" s="0" t="inlineStr">
         <is>
-          <t>Taᴗaoᥫᩣ</t>
+          <t>申华</t>
         </is>
       </c>
       <c r="C277" s="0" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="G277" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 12:42:35</t>
+          <t>2026-08-30 12:42:49</t>
         </is>
       </c>
       <c r="H277" s="0" t="inlineStr">
@@ -16705,11 +16705,11 @@
     </row>
     <row r="278" spans="1:14">
       <c r="A278" s="0">
-        <v>49782066</v>
+        <v>49825637</v>
       </c>
       <c r="B278" s="0" t="inlineStr">
         <is>
-          <t>前程似锦</t>
+          <t>陈月焓</t>
         </is>
       </c>
       <c r="C278" s="0" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="G278" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 09:07:29</t>
+          <t>2026-08-30 12:42:47</t>
         </is>
       </c>
       <c r="H278" s="0" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="I278" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J278" s="0" t="inlineStr">
@@ -16765,11 +16765,11 @@
     </row>
     <row r="279" spans="1:14">
       <c r="A279" s="0">
-        <v>49771027</v>
+        <v>49825635</v>
       </c>
       <c r="B279" s="0" t="inlineStr">
         <is>
-          <t>非比</t>
+          <t>小镇生活&amp;&amp;杜震</t>
         </is>
       </c>
       <c r="C279" s="0" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="G279" s="0" t="inlineStr">
         <is>
-          <t>2026-08-28 23:30:09</t>
+          <t>2026-08-30 12:42:43</t>
         </is>
       </c>
       <c r="H279" s="0" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="I279" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J279" s="0" t="inlineStr">
@@ -16825,11 +16825,11 @@
     </row>
     <row r="280" spans="1:14">
       <c r="A280" s="0">
-        <v>49673360</v>
+        <v>49825628</v>
       </c>
       <c r="B280" s="0" t="inlineStr">
         <is>
-          <t>德行天下</t>
+          <t>Taᴗaoᥫᩣ</t>
         </is>
       </c>
       <c r="C280" s="0" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="G280" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26 12:19:03</t>
+          <t>2026-08-30 12:42:35</t>
         </is>
       </c>
       <c r="H280" s="0" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="I280" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J280" s="0" t="inlineStr">
@@ -16885,11 +16885,11 @@
     </row>
     <row r="281" spans="1:14">
       <c r="A281" s="0">
-        <v>49673352</v>
+        <v>49782066</v>
       </c>
       <c r="B281" s="0" t="inlineStr">
         <is>
-          <t>余盛将至2026</t>
+          <t>前程似锦</t>
         </is>
       </c>
       <c r="C281" s="0" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="G281" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26 12:18:49</t>
+          <t>2026-08-29 09:07:29</t>
         </is>
       </c>
       <c r="H281" s="0" t="inlineStr">
@@ -16924,7 +16924,7 @@
       </c>
       <c r="I281" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J281" s="0" t="inlineStr">
@@ -16945,11 +16945,11 @@
     </row>
     <row r="282" spans="1:14">
       <c r="A282" s="0">
-        <v>49673350</v>
+        <v>49771027</v>
       </c>
       <c r="B282" s="0" t="inlineStr">
         <is>
-          <t>山居客</t>
+          <t>非比</t>
         </is>
       </c>
       <c r="C282" s="0" t="inlineStr">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="G282" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26 12:18:47</t>
+          <t>2026-08-28 23:30:09</t>
         </is>
       </c>
       <c r="H282" s="0" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="I282" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音02</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J282" s="0" t="inlineStr">
@@ -17005,11 +17005,11 @@
     </row>
     <row r="283" spans="1:14">
       <c r="A283" s="0">
-        <v>49673349</v>
+        <v>49673360</v>
       </c>
       <c r="B283" s="0" t="inlineStr">
         <is>
-          <t>白云</t>
+          <t>德行天下</t>
         </is>
       </c>
       <c r="C283" s="0" t="inlineStr">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="G283" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26 12:18:45</t>
+          <t>2026-08-26 12:19:03</t>
         </is>
       </c>
       <c r="H283" s="0" t="inlineStr">
@@ -17065,11 +17065,11 @@
     </row>
     <row r="284" spans="1:14">
       <c r="A284" s="0">
-        <v>49646935</v>
+        <v>49673352</v>
       </c>
       <c r="B284" s="0" t="inlineStr">
         <is>
-          <t>马跃荣</t>
+          <t>余盛将至2026</t>
         </is>
       </c>
       <c r="C284" s="0" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="G284" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 18:15:59</t>
+          <t>2026-08-26 12:18:49</t>
         </is>
       </c>
       <c r="H284" s="0" t="inlineStr">
@@ -17125,11 +17125,11 @@
     </row>
     <row r="285" spans="1:14">
       <c r="A285" s="0">
-        <v>49646933</v>
+        <v>49673350</v>
       </c>
       <c r="B285" s="0" t="inlineStr">
         <is>
-          <t>@吴</t>
+          <t>山居客</t>
         </is>
       </c>
       <c r="C285" s="0" t="inlineStr">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="G285" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 18:15:56</t>
+          <t>2026-08-26 12:18:47</t>
         </is>
       </c>
       <c r="H285" s="0" t="inlineStr">
@@ -17185,11 +17185,11 @@
     </row>
     <row r="286" spans="1:14">
       <c r="A286" s="0">
-        <v>49646901</v>
+        <v>49673349</v>
       </c>
       <c r="B286" s="0" t="inlineStr">
         <is>
-          <t>龙安：富华／</t>
+          <t>白云</t>
         </is>
       </c>
       <c r="C286" s="0" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="G286" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 18:14:28</t>
+          <t>2026-08-26 12:18:45</t>
         </is>
       </c>
       <c r="H286" s="0" t="inlineStr">
@@ -17245,11 +17245,11 @@
     </row>
     <row r="287" spans="1:14">
       <c r="A287" s="0">
-        <v>49646876</v>
+        <v>49646935</v>
       </c>
       <c r="B287" s="0" t="inlineStr">
         <is>
-          <t>冬日暖阳🌻</t>
+          <t>马跃荣</t>
         </is>
       </c>
       <c r="C287" s="0" t="inlineStr">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="G287" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 18:13:37</t>
+          <t>2026-08-25 18:15:59</t>
         </is>
       </c>
       <c r="H287" s="0" t="inlineStr">
@@ -17305,11 +17305,11 @@
     </row>
     <row r="288" spans="1:14">
       <c r="A288" s="0">
-        <v>49646867</v>
+        <v>49646933</v>
       </c>
       <c r="B288" s="0" t="inlineStr">
         <is>
-          <t>寒雨</t>
+          <t>@吴</t>
         </is>
       </c>
       <c r="C288" s="0" t="inlineStr">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="G288" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 18:13:15</t>
+          <t>2026-08-25 18:15:56</t>
         </is>
       </c>
       <c r="H288" s="0" t="inlineStr">
@@ -17365,11 +17365,11 @@
     </row>
     <row r="289" spans="1:14">
       <c r="A289" s="0">
-        <v>49636232</v>
+        <v>49646901</v>
       </c>
       <c r="B289" s="0" t="inlineStr">
         <is>
-          <t>平安</t>
+          <t>龙安：富华／</t>
         </is>
       </c>
       <c r="C289" s="0" t="inlineStr">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="G289" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 13:20:15</t>
+          <t>2026-08-25 18:14:28</t>
         </is>
       </c>
       <c r="H289" s="0" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="I289" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J289" s="0" t="inlineStr">
@@ -17425,11 +17425,11 @@
     </row>
     <row r="290" spans="1:14">
       <c r="A290" s="0">
-        <v>49636184</v>
+        <v>49646876</v>
       </c>
       <c r="B290" s="0" t="inlineStr">
         <is>
-          <t>古道西风</t>
+          <t>冬日暖阳🌻</t>
         </is>
       </c>
       <c r="C290" s="0" t="inlineStr">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="G290" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 13:18:55</t>
+          <t>2026-08-25 18:13:37</t>
         </is>
       </c>
       <c r="H290" s="0" t="inlineStr">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="I290" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J290" s="0" t="inlineStr">
@@ -17485,11 +17485,11 @@
     </row>
     <row r="291" spans="1:14">
       <c r="A291" s="0">
-        <v>49636170</v>
+        <v>49646867</v>
       </c>
       <c r="B291" s="0" t="inlineStr">
         <is>
-          <t>周海龙</t>
+          <t>寒雨</t>
         </is>
       </c>
       <c r="C291" s="0" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="G291" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 13:18:33</t>
+          <t>2026-08-25 18:13:15</t>
         </is>
       </c>
       <c r="H291" s="0" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="I291" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-抖音02</t>
         </is>
       </c>
       <c r="J291" s="0" t="inlineStr">
@@ -17545,11 +17545,11 @@
     </row>
     <row r="292" spans="1:14">
       <c r="A292" s="0">
-        <v>49636157</v>
+        <v>49636232</v>
       </c>
       <c r="B292" s="0" t="inlineStr">
         <is>
-          <t>锦妍</t>
+          <t>平安</t>
         </is>
       </c>
       <c r="C292" s="0" t="inlineStr">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="G292" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25 13:18:07</t>
+          <t>2026-08-25 13:20:15</t>
         </is>
       </c>
       <c r="H292" s="0" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="I292" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J292" s="0" t="inlineStr">
@@ -17605,11 +17605,11 @@
     </row>
     <row r="293" spans="1:14">
       <c r="A293" s="0">
-        <v>49593974</v>
+        <v>49636184</v>
       </c>
       <c r="B293" s="0" t="inlineStr">
         <is>
-          <t>兰兰</t>
+          <t>古道西风</t>
         </is>
       </c>
       <c r="C293" s="0" t="inlineStr">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="G293" s="0" t="inlineStr">
         <is>
-          <t>2026-08-24 12:59:53</t>
+          <t>2026-08-25 13:18:55</t>
         </is>
       </c>
       <c r="H293" s="0" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="I293" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J293" s="0" t="inlineStr">
@@ -17665,11 +17665,11 @@
     </row>
     <row r="294" spans="1:14">
       <c r="A294" s="0">
-        <v>49593671</v>
+        <v>49636170</v>
       </c>
       <c r="B294" s="0" t="inlineStr">
         <is>
-          <t>准备1号</t>
+          <t>周海龙</t>
         </is>
       </c>
       <c r="C294" s="0" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="G294" s="0" t="inlineStr">
         <is>
-          <t>2026-08-24 12:49:27</t>
+          <t>2026-08-25 13:18:33</t>
         </is>
       </c>
       <c r="H294" s="0" t="inlineStr">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="I294" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J294" s="0" t="inlineStr">
@@ -17725,11 +17725,11 @@
     </row>
     <row r="295" spans="1:14">
       <c r="A295" s="0">
-        <v>49535916</v>
+        <v>49636157</v>
       </c>
       <c r="B295" s="0" t="inlineStr">
         <is>
-          <t>真诚</t>
+          <t>锦妍</t>
         </is>
       </c>
       <c r="C295" s="0" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="G295" s="0" t="inlineStr">
         <is>
-          <t>2026-08-22 23:46:23</t>
+          <t>2026-08-25 13:18:07</t>
         </is>
       </c>
       <c r="H295" s="0" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="I295" s="0" t="inlineStr">
         <is>
-          <t>黄老师-视频号01</t>
+          <t>黄老师-抖音01</t>
         </is>
       </c>
       <c r="J295" s="0" t="inlineStr">
@@ -17785,11 +17785,11 @@
     </row>
     <row r="296" spans="1:14">
       <c r="A296" s="0">
-        <v>49535653</v>
+        <v>49593974</v>
       </c>
       <c r="B296" s="0" t="inlineStr">
         <is>
-          <t>如意家电13368134456维修</t>
+          <t>兰兰</t>
         </is>
       </c>
       <c r="C296" s="0" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="G296" s="0" t="inlineStr">
         <is>
-          <t>2026-08-22 23:28:25</t>
+          <t>2026-08-24 12:59:53</t>
         </is>
       </c>
       <c r="H296" s="0" t="inlineStr">
@@ -17845,11 +17845,11 @@
     </row>
     <row r="297" spans="1:14">
       <c r="A297" s="0">
-        <v>49535650</v>
+        <v>49593671</v>
       </c>
       <c r="B297" s="0" t="inlineStr">
         <is>
-          <t>莺莺</t>
+          <t>准备1号</t>
         </is>
       </c>
       <c r="C297" s="0" t="inlineStr">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="G297" s="0" t="inlineStr">
         <is>
-          <t>2026-08-22 23:27:55</t>
+          <t>2026-08-24 12:49:27</t>
         </is>
       </c>
       <c r="H297" s="0" t="inlineStr">
@@ -17900,21 +17900,16 @@
       <c r="L297" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N297" s="0" t="inlineStr">
-        <is>
-          <t>黄浦</t>
         </is>
       </c>
     </row>
     <row r="298" spans="1:14">
       <c r="A298" s="0">
-        <v>49508265</v>
+        <v>49535916</v>
       </c>
       <c r="B298" s="0" t="inlineStr">
         <is>
-          <t>爱猫🐱 咪</t>
+          <t>真诚</t>
         </is>
       </c>
       <c r="C298" s="0" t="inlineStr">
@@ -17939,7 +17934,7 @@
       </c>
       <c r="G298" s="0" t="inlineStr">
         <is>
-          <t>2026-08-22 09:53:41</t>
+          <t>2026-08-22 23:46:23</t>
         </is>
       </c>
       <c r="H298" s="0" t="inlineStr">
@@ -17970,11 +17965,11 @@
     </row>
     <row r="299" spans="1:14">
       <c r="A299" s="0">
-        <v>49493414</v>
+        <v>49535653</v>
       </c>
       <c r="B299" s="0" t="inlineStr">
         <is>
-          <t>惠平</t>
+          <t>如意家电13368134456维修</t>
         </is>
       </c>
       <c r="C299" s="0" t="inlineStr">
@@ -17999,7 +17994,7 @@
       </c>
       <c r="G299" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 22:53:02</t>
+          <t>2026-08-22 23:28:25</t>
         </is>
       </c>
       <c r="H299" s="0" t="inlineStr">
@@ -18030,11 +18025,11 @@
     </row>
     <row r="300" spans="1:14">
       <c r="A300" s="0">
-        <v>49493126</v>
+        <v>49535650</v>
       </c>
       <c r="B300" s="0" t="inlineStr">
         <is>
-          <t>刘盼昭</t>
+          <t>莺莺</t>
         </is>
       </c>
       <c r="C300" s="0" t="inlineStr">
@@ -18059,7 +18054,7 @@
       </c>
       <c r="G300" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 22:44:53</t>
+          <t>2026-08-22 23:27:55</t>
         </is>
       </c>
       <c r="H300" s="0" t="inlineStr">
@@ -18085,16 +18080,21 @@
       <c r="L300" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
+        </is>
+      </c>
+      <c r="N300" s="0" t="inlineStr">
+        <is>
+          <t>黄浦</t>
         </is>
       </c>
     </row>
     <row r="301" spans="1:14">
       <c r="A301" s="0">
-        <v>49492499</v>
+        <v>49508265</v>
       </c>
       <c r="B301" s="0" t="inlineStr">
         <is>
-          <t>红霞</t>
+          <t>爱猫🐱 咪</t>
         </is>
       </c>
       <c r="C301" s="0" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="G301" s="0" t="inlineStr">
         <is>
-          <t>2026-08-21 22:29:43</t>
+          <t>2026-08-22 09:53:41</t>
         </is>
       </c>
       <c r="H301" s="0" t="inlineStr">
@@ -18150,11 +18150,11 @@
     </row>
     <row r="302" spans="1:14">
       <c r="A302" s="0">
-        <v>49455301</v>
+        <v>49493414</v>
       </c>
       <c r="B302" s="0" t="inlineStr">
         <is>
-          <t>周开平</t>
+          <t>惠平</t>
         </is>
       </c>
       <c r="C302" s="0" t="inlineStr">
@@ -18179,7 +18179,7 @@
       </c>
       <c r="G302" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 22:46:59</t>
+          <t>2026-08-21 22:53:02</t>
         </is>
       </c>
       <c r="H302" s="0" t="inlineStr">
@@ -18210,11 +18210,11 @@
     </row>
     <row r="303" spans="1:14">
       <c r="A303" s="0">
-        <v>49432023</v>
+        <v>49493126</v>
       </c>
       <c r="B303" s="0" t="inlineStr">
         <is>
-          <t>花生米</t>
+          <t>刘盼昭</t>
         </is>
       </c>
       <c r="C303" s="0" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="G303" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:45</t>
+          <t>2026-08-21 22:44:53</t>
         </is>
       </c>
       <c r="H303" s="0" t="inlineStr">
@@ -18270,11 +18270,11 @@
     </row>
     <row r="304" spans="1:14">
       <c r="A304" s="0">
-        <v>49415939</v>
+        <v>49492499</v>
       </c>
       <c r="B304" s="0" t="inlineStr">
         <is>
-          <t>杨梅芳</t>
+          <t>红霞</t>
         </is>
       </c>
       <c r="C304" s="0" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="G304" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:48:58</t>
+          <t>2026-08-21 22:29:43</t>
         </is>
       </c>
       <c r="H304" s="0" t="inlineStr">
@@ -18309,17 +18309,17 @@
       </c>
       <c r="I304" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J304" s="0" t="inlineStr">
         <is>
-          <t>安迪钢琴-多个点击报名-0元</t>
+          <t>安迪钢琴-获客助手专用</t>
         </is>
       </c>
       <c r="K304" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L304" s="0" t="inlineStr">
@@ -18330,11 +18330,11 @@
     </row>
     <row r="305" spans="1:14">
       <c r="A305" s="0">
-        <v>49415918</v>
+        <v>49455301</v>
       </c>
       <c r="B305" s="0" t="inlineStr">
         <is>
-          <t>心语无言</t>
+          <t>周开平</t>
         </is>
       </c>
       <c r="C305" s="0" t="inlineStr">
@@ -18359,7 +18359,7 @@
       </c>
       <c r="G305" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:48:24</t>
+          <t>2026-08-20 22:46:59</t>
         </is>
       </c>
       <c r="H305" s="0" t="inlineStr">
@@ -18369,17 +18369,17 @@
       </c>
       <c r="I305" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J305" s="0" t="inlineStr">
         <is>
-          <t>安迪钢琴-多个点击报名-0元</t>
+          <t>安迪钢琴-获客助手专用</t>
         </is>
       </c>
       <c r="K305" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L305" s="0" t="inlineStr">
@@ -18390,11 +18390,11 @@
     </row>
     <row r="306" spans="1:14">
       <c r="A306" s="0">
-        <v>49415913</v>
+        <v>49432023</v>
       </c>
       <c r="B306" s="0" t="inlineStr">
         <is>
-          <t>安好</t>
+          <t>花生米</t>
         </is>
       </c>
       <c r="C306" s="0" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="G306" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:48:18</t>
+          <t>2026-08-20 11:55:45</t>
         </is>
       </c>
       <c r="H306" s="0" t="inlineStr">
@@ -18429,17 +18429,17 @@
       </c>
       <c r="I306" s="0" t="inlineStr">
         <is>
-          <t>黄老师-抖音01</t>
+          <t>黄老师-视频号01</t>
         </is>
       </c>
       <c r="J306" s="0" t="inlineStr">
         <is>
-          <t>安迪钢琴-多个点击报名-0元</t>
+          <t>安迪钢琴-获客助手专用</t>
         </is>
       </c>
       <c r="K306" s="0" t="inlineStr">
         <is>
-          <t>微信支付</t>
+          <t>获客助手加好友</t>
         </is>
       </c>
       <c r="L306" s="0" t="inlineStr">
@@ -18450,11 +18450,11 @@
     </row>
     <row r="307" spans="1:14">
       <c r="A307" s="0">
-        <v>49415890</v>
+        <v>49415939</v>
       </c>
       <c r="B307" s="0" t="inlineStr">
         <is>
-          <t>雨夜聆风</t>
+          <t>杨梅芳</t>
         </is>
       </c>
       <c r="C307" s="0" t="inlineStr">
@@ -18479,7 +18479,7 @@
       </c>
       <c r="G307" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:47:56</t>
+          <t>2026-08-19 22:48:58</t>
         </is>
       </c>
       <c r="H307" s="0" t="inlineStr">
@@ -18505,21 +18505,16 @@
       <c r="L307" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
-        </is>
-      </c>
-      <c r="N307" s="0" t="inlineStr">
-        <is>
-          <t>宜春</t>
         </is>
       </c>
     </row>
     <row r="308" spans="1:14">
       <c r="A308" s="0">
-        <v>49415874</v>
+        <v>49415918</v>
       </c>
       <c r="B308" s="0" t="inlineStr">
         <is>
-          <t>飘</t>
+          <t>心语无言</t>
         </is>
       </c>
       <c r="C308" s="0" t="inlineStr">
@@ -18544,7 +18539,7 @@
       </c>
       <c r="G308" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:47:40</t>
+          <t>2026-08-19 22:48:24</t>
         </is>
       </c>
       <c r="H308" s="0" t="inlineStr">
@@ -18575,11 +18570,11 @@
     </row>
     <row r="309" spans="1:14">
       <c r="A309" s="0">
-        <v>49415871</v>
+        <v>49415913</v>
       </c>
       <c r="B309" s="0" t="inlineStr">
         <is>
-          <t>庆</t>
+          <t>安好</t>
         </is>
       </c>
       <c r="C309" s="0" t="inlineStr">
@@ -18604,7 +18599,7 @@
       </c>
       <c r="G309" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19 22:47:36</t>
+          <t>2026-08-19 22:48:18</t>
         </is>
       </c>
       <c r="H309" s="0" t="inlineStr">
@@ -18635,59 +18630,244 @@
     </row>
     <row r="310" spans="1:14">
       <c r="A310" s="0">
+        <v>49415890</v>
+      </c>
+      <c r="B310" s="0" t="inlineStr">
+        <is>
+          <t>雨夜聆风</t>
+        </is>
+      </c>
+      <c r="C310" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D310" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E310" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F310" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G310" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:47:56</t>
+        </is>
+      </c>
+      <c r="H310" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I310" s="0" t="inlineStr">
+        <is>
+          <t>黄老师-抖音01</t>
+        </is>
+      </c>
+      <c r="J310" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-多个点击报名-0元</t>
+        </is>
+      </c>
+      <c r="K310" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L310" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="N310" s="0" t="inlineStr">
+        <is>
+          <t>宜春</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" spans="1:14">
+      <c r="A311" s="0">
+        <v>49415874</v>
+      </c>
+      <c r="B311" s="0" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="C311" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D311" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E311" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F311" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G311" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:47:40</t>
+        </is>
+      </c>
+      <c r="H311" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I311" s="0" t="inlineStr">
+        <is>
+          <t>黄老师-抖音01</t>
+        </is>
+      </c>
+      <c r="J311" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-多个点击报名-0元</t>
+        </is>
+      </c>
+      <c r="K311" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L311" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" spans="1:14">
+      <c r="A312" s="0">
+        <v>49415871</v>
+      </c>
+      <c r="B312" s="0" t="inlineStr">
+        <is>
+          <t>庆</t>
+        </is>
+      </c>
+      <c r="C312" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D312" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E312" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F312" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G312" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:47:36</t>
+        </is>
+      </c>
+      <c r="H312" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I312" s="0" t="inlineStr">
+        <is>
+          <t>黄老师-抖音01</t>
+        </is>
+      </c>
+      <c r="J312" s="0" t="inlineStr">
+        <is>
+          <t>安迪钢琴-多个点击报名-0元</t>
+        </is>
+      </c>
+      <c r="K312" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L312" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" spans="1:14">
+      <c r="A313" s="0">
         <v>49415867</v>
       </c>
-      <c r="B310" s="0" t="inlineStr">
+      <c r="B313" s="0" t="inlineStr">
         <is>
           <t>HYQ</t>
         </is>
       </c>
-      <c r="C310" s="0" t="inlineStr">
-        <is>
-          <t>6天0基础钢琴入门课</t>
-        </is>
-      </c>
-      <c r="D310" s="0" t="inlineStr">
-        <is>
-          <t>训练营</t>
-        </is>
-      </c>
-      <c r="E310" s="0" t="inlineStr">
-        <is>
-          <t>￥0</t>
-        </is>
-      </c>
-      <c r="F310" s="0" t="inlineStr">
-        <is>
-          <t>￥0</t>
-        </is>
-      </c>
-      <c r="G310" s="0" t="inlineStr">
+      <c r="C313" s="0" t="inlineStr">
+        <is>
+          <t>6天0基础钢琴入门课</t>
+        </is>
+      </c>
+      <c r="D313" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E313" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="F313" s="0" t="inlineStr">
+        <is>
+          <t>￥0</t>
+        </is>
+      </c>
+      <c r="G313" s="0" t="inlineStr">
         <is>
           <t>2026-08-19 22:47:33</t>
         </is>
       </c>
-      <c r="H310" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I310" s="0" t="inlineStr">
-        <is>
-          <t>黄老师-抖音01</t>
-        </is>
-      </c>
-      <c r="J310" s="0" t="inlineStr">
+      <c r="H313" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I313" s="0" t="inlineStr">
+        <is>
+          <t>黄老师-抖音01</t>
+        </is>
+      </c>
+      <c r="J313" s="0" t="inlineStr">
         <is>
           <t>安迪钢琴-多个点击报名-0元</t>
         </is>
       </c>
-      <c r="K310" s="0" t="inlineStr">
+      <c r="K313" s="0" t="inlineStr">
         <is>
           <t>微信支付</t>
         </is>
       </c>
-      <c r="L310" s="0" t="inlineStr">
+      <c r="L313" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
